--- a/exports/California_Surplus_Feed.xlsx
+++ b/exports/California_Surplus_Feed.xlsx
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="O2" t="n">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
@@ -606,7 +606,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-09-12 13:48:40</t>
+          <t>2026-09-13 14:44:42</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="O3" t="n">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-09-12 13:48:40</t>
+          <t>2026-09-13 14:44:42</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
         </is>
       </c>
       <c r="O4" t="n">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-09-12 13:48:40</t>
+          <t>2026-09-13 14:44:42</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="O5" t="n">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-09-12 13:48:40</t>
+          <t>2026-09-13 14:44:42</t>
         </is>
       </c>
     </row>

--- a/exports/California_Surplus_Feed.xlsx
+++ b/exports/California_Surplus_Feed.xlsx
@@ -557,7 +557,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Commercial / Mixed Use</t>
+          <t>Single Family Residential</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -582,11 +582,11 @@
         </is>
       </c>
       <c r="O2" t="n">
-        <v>299</v>
+        <v>0</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Tier 3: Active Claim Window (&gt; 120 Days)</t>
+          <t>Expired / Time-Barred</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -606,7 +606,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-09-13 14:44:42</t>
+          <t>2026-09-14 16:42:31</t>
         </is>
       </c>
     </row>
@@ -649,7 +649,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Commercial / Mixed Use</t>
+          <t>Single Family Residential</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -674,11 +674,11 @@
         </is>
       </c>
       <c r="O3" t="n">
-        <v>306</v>
+        <v>0</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tier 3: Active Claim Window (&gt; 120 Days)</t>
+          <t>Expired / Time-Barred</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -698,7 +698,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-09-13 14:44:42</t>
+          <t>2026-09-14 16:42:31</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Commercial / Mixed Use</t>
+          <t>Single Family Residential</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -766,11 +766,11 @@
         </is>
       </c>
       <c r="O4" t="n">
-        <v>320</v>
+        <v>0</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Tier 3: Active Claim Window (&gt; 120 Days)</t>
+          <t>Expired / Time-Barred</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -790,7 +790,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-09-13 14:44:42</t>
+          <t>2026-09-14 16:42:31</t>
         </is>
       </c>
     </row>
@@ -858,11 +858,11 @@
         </is>
       </c>
       <c r="O5" t="n">
-        <v>327</v>
+        <v>0</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Tier 3: Active Claim Window (&gt; 120 Days)</t>
+          <t>Expired / Time-Barred</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-09-13 14:44:42</t>
+          <t>2026-09-14 16:42:31</t>
         </is>
       </c>
     </row>

--- a/exports/California_Surplus_Feed.xlsx
+++ b/exports/California_Surplus_Feed.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,106 +425,116 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T5"/>
+  <dimension ref="A1:V5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>County</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Case_or_TaxDeed_No</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Owner_Name</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Entity_Type</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Is_Individual</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Heir_Search_Recommended</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Property_Address</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Property_Type</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Surplus_Balance_USD</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Statutory_Fee_Rate</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Est_Finder_Fee_USD</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Opportunity_Tier</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Sale_Date</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Days_Remaining_To_Claim</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Claim_Urgency_Tier</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Claim_Deadline_Date</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Statutory_Deadline_Window</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Clerk_Verification_URL</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Governing_Statute</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Statute_Citation</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Enriched_Timestamp</t>
         </is>
@@ -582,31 +604,41 @@
         </is>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Expired / Time-Barred</t>
+          <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
           <t>1 Year from Deed Recording (Cal. Rev. &amp; Tax Code § 4675)</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>https://ttc.lacounty.gov/</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Cal. Rev. &amp; Tax Code § 4675</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>2026-09-14 16:42:31</t>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Cal. Rev. &amp; Tax Code § 4675</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>2026-09-16 15:13:04</t>
         </is>
       </c>
     </row>
@@ -674,31 +706,41 @@
         </is>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Expired / Time-Barred</t>
+          <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
           <t>1 Year from Deed Recording (Cal. Rev. &amp; Tax Code § 4675)</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>https://www.sdttc.com/</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Cal. Rev. &amp; Tax Code § 4675</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>2026-09-14 16:42:31</t>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Cal. Rev. &amp; Tax Code § 4675</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>2026-09-16 15:13:04</t>
         </is>
       </c>
     </row>
@@ -766,31 +808,41 @@
         </is>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Expired / Time-Barred</t>
+          <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
           <t>1 Year from Deed Recording (Cal. Rev. &amp; Tax Code § 4675)</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>https://ttc.lacounty.gov/</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Cal. Rev. &amp; Tax Code § 4675</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>2026-09-14 16:42:31</t>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Cal. Rev. &amp; Tax Code § 4675</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>2026-09-16 15:13:04</t>
         </is>
       </c>
     </row>
@@ -858,31 +910,41 @@
         </is>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Expired / Time-Barred</t>
+          <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
           <t>1 Year from Deed Recording (Cal. Rev. &amp; Tax Code § 4675)</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>https://www.sdttc.com/</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Cal. Rev. &amp; Tax Code § 4675</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>2026-09-14 16:42:31</t>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Cal. Rev. &amp; Tax Code § 4675</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>2026-09-16 15:13:04</t>
         </is>
       </c>
     </row>

--- a/exports/California_Surplus_Feed.xlsx
+++ b/exports/California_Surplus_Feed.xlsx
@@ -613,7 +613,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-09-16 15:13:04</t>
+          <t>2026-09-17 15:22:30</t>
         </is>
       </c>
     </row>
@@ -715,7 +715,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -740,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-09-16 15:13:04</t>
+          <t>2026-09-17 15:22:30</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-09-16 15:13:04</t>
+          <t>2026-09-17 15:22:30</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -944,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-09-16 15:13:04</t>
+          <t>2026-09-17 15:22:30</t>
         </is>
       </c>
     </row>

--- a/exports/California_Surplus_Feed.xlsx
+++ b/exports/California_Surplus_Feed.xlsx
@@ -613,7 +613,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-07</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-09-17 15:22:30</t>
+          <t>2026-09-18 14:42:19</t>
         </is>
       </c>
     </row>
@@ -715,7 +715,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-07</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -740,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-09-17 15:22:30</t>
+          <t>2026-09-18 14:42:19</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-07</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-09-17 15:22:30</t>
+          <t>2026-09-18 14:42:19</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-07</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -944,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-09-17 15:22:30</t>
+          <t>2026-09-18 14:42:19</t>
         </is>
       </c>
     </row>

--- a/exports/California_Surplus_Feed.xlsx
+++ b/exports/California_Surplus_Feed.xlsx
@@ -613,7 +613,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-11-08</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-09-18 14:42:19</t>
+          <t>2026-09-19 14:03:02</t>
         </is>
       </c>
     </row>
@@ -715,7 +715,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-11-08</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -740,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-09-18 14:42:19</t>
+          <t>2026-09-19 14:03:02</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-11-08</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-09-18 14:42:19</t>
+          <t>2026-09-19 14:03:02</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-11-08</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -944,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-09-18 14:42:19</t>
+          <t>2026-09-19 14:03:02</t>
         </is>
       </c>
     </row>

--- a/exports/California_Surplus_Feed.xlsx
+++ b/exports/California_Surplus_Feed.xlsx
@@ -613,7 +613,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-11-08</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:03:02</t>
+          <t>2026-09-20 14:23:23</t>
         </is>
       </c>
     </row>
@@ -715,7 +715,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-11-08</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -740,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-09-19 14:03:02</t>
+          <t>2026-09-20 14:23:23</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-11-08</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-09-19 14:03:02</t>
+          <t>2026-09-20 14:23:23</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-11-08</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -944,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-09-19 14:03:02</t>
+          <t>2026-09-20 14:23:23</t>
         </is>
       </c>
     </row>

--- a/exports/California_Surplus_Feed.xlsx
+++ b/exports/California_Surplus_Feed.xlsx
@@ -613,7 +613,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-09-20 14:23:23</t>
+          <t>2026-09-21 16:42:18</t>
         </is>
       </c>
     </row>
@@ -715,7 +715,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -740,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-09-20 14:23:23</t>
+          <t>2026-09-21 16:42:18</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-09-20 14:23:23</t>
+          <t>2026-09-21 16:42:18</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -944,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-09-20 14:23:23</t>
+          <t>2026-09-21 16:42:18</t>
         </is>
       </c>
     </row>

--- a/exports/California_Surplus_Feed.xlsx
+++ b/exports/California_Surplus_Feed.xlsx
@@ -613,7 +613,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-09-21 16:42:18</t>
+          <t>2026-09-22 15:16:16</t>
         </is>
       </c>
     </row>
@@ -715,7 +715,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -740,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-09-21 16:42:18</t>
+          <t>2026-09-22 15:16:16</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-09-21 16:42:18</t>
+          <t>2026-09-22 15:16:16</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -944,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-09-21 16:42:18</t>
+          <t>2026-09-22 15:16:16</t>
         </is>
       </c>
     </row>

--- a/exports/California_Surplus_Feed.xlsx
+++ b/exports/California_Surplus_Feed.xlsx
@@ -613,7 +613,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-09-22 15:16:16</t>
+          <t>2026-09-23 15:14:48</t>
         </is>
       </c>
     </row>
@@ -715,7 +715,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -740,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-09-22 15:16:16</t>
+          <t>2026-09-23 15:14:48</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-09-22 15:16:16</t>
+          <t>2026-09-23 15:14:48</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -944,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-09-22 15:16:16</t>
+          <t>2026-09-23 15:14:48</t>
         </is>
       </c>
     </row>

--- a/exports/California_Surplus_Feed.xlsx
+++ b/exports/California_Surplus_Feed.xlsx
@@ -613,7 +613,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-09-23 15:14:48</t>
+          <t>2026-09-24 15:35:43</t>
         </is>
       </c>
     </row>
@@ -715,7 +715,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -740,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-09-23 15:14:48</t>
+          <t>2026-09-24 15:35:43</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-09-23 15:14:48</t>
+          <t>2026-09-24 15:35:43</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -944,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-09-23 15:14:48</t>
+          <t>2026-09-24 15:35:43</t>
         </is>
       </c>
     </row>

--- a/exports/California_Surplus_Feed.xlsx
+++ b/exports/California_Surplus_Feed.xlsx
@@ -613,7 +613,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-14</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-09-24 15:35:43</t>
+          <t>2026-09-25 15:40:49</t>
         </is>
       </c>
     </row>
@@ -715,7 +715,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-14</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -740,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-09-24 15:35:43</t>
+          <t>2026-09-25 15:40:49</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-14</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-09-24 15:35:43</t>
+          <t>2026-09-25 15:40:49</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-14</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -944,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-09-24 15:35:43</t>
+          <t>2026-09-25 15:40:49</t>
         </is>
       </c>
     </row>

--- a/exports/California_Surplus_Feed.xlsx
+++ b/exports/California_Surplus_Feed.xlsx
@@ -613,7 +613,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-11-14</t>
+          <t>2026-11-15</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-09-25 15:40:49</t>
+          <t>2026-09-26 14:49:00</t>
         </is>
       </c>
     </row>
@@ -715,7 +715,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-11-14</t>
+          <t>2026-11-15</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -740,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-09-25 15:40:49</t>
+          <t>2026-09-26 14:49:00</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-11-14</t>
+          <t>2026-11-15</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-09-25 15:40:49</t>
+          <t>2026-09-26 14:49:00</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-11-14</t>
+          <t>2026-11-15</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -944,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-09-25 15:40:49</t>
+          <t>2026-09-26 14:49:00</t>
         </is>
       </c>
     </row>

--- a/exports/California_Surplus_Feed.xlsx
+++ b/exports/California_Surplus_Feed.xlsx
@@ -613,7 +613,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-11-15</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-09-26 14:49:00</t>
+          <t>2026-09-27 15:27:36</t>
         </is>
       </c>
     </row>
@@ -715,7 +715,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-11-15</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -740,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-09-26 14:49:00</t>
+          <t>2026-09-27 15:27:36</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-11-15</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-09-26 14:49:00</t>
+          <t>2026-09-27 15:27:36</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-11-15</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -944,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-09-26 14:49:00</t>
+          <t>2026-09-27 15:27:36</t>
         </is>
       </c>
     </row>

--- a/exports/California_Surplus_Feed.xlsx
+++ b/exports/California_Surplus_Feed.xlsx
@@ -613,7 +613,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-11-17</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-09-27 15:27:36</t>
+          <t>2026-09-28 18:19:10</t>
         </is>
       </c>
     </row>
@@ -715,7 +715,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-11-17</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -740,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-09-27 15:27:36</t>
+          <t>2026-09-28 18:19:10</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-11-17</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-09-27 15:27:36</t>
+          <t>2026-09-28 18:19:10</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-11-17</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -944,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-09-27 15:27:36</t>
+          <t>2026-09-28 18:19:10</t>
         </is>
       </c>
     </row>

--- a/exports/California_Surplus_Feed.xlsx
+++ b/exports/California_Surplus_Feed.xlsx
@@ -613,7 +613,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-11-17</t>
+          <t>2026-11-18</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-09-28 18:19:10</t>
+          <t>2026-09-29 12:50:34</t>
         </is>
       </c>
     </row>
@@ -715,7 +715,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-11-17</t>
+          <t>2026-11-18</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -740,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-09-28 18:19:10</t>
+          <t>2026-09-29 12:50:34</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-11-17</t>
+          <t>2026-11-18</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-09-28 18:19:10</t>
+          <t>2026-09-29 12:50:34</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-11-17</t>
+          <t>2026-11-18</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -944,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-09-28 18:19:10</t>
+          <t>2026-09-29 12:50:34</t>
         </is>
       </c>
     </row>

--- a/exports/California_Surplus_Feed.xlsx
+++ b/exports/California_Surplus_Feed.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V5"/>
+  <dimension ref="A1:Y5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,100 +441,115 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Parcel_ID</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Case_or_TaxDeed_No</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Owner_Name</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Entity_Type</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Is_Individual</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Heir_Search_Recommended</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Property_Address</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Property_Type</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Surplus_Balance_USD</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Statutory_Fee_Rate</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Est_Finder_Fee_USD</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Opportunity_Tier</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Sale_Date</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Days_Remaining_To_Claim</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Claim_Urgency_Tier</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Claim_Deadline_Date</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Statutory_Deadline_Window</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Clerk_Verification_URL</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Governing_Statute</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Statute_Citation</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Record_Type</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>TYPE</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Enriched_Timestamp</t>
         </is>
@@ -553,92 +568,107 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
           <t>2024-CA-008120</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>GREGORY &amp; EVELYN THATCHER</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>Individual / Estate</t>
         </is>
       </c>
-      <c r="F2" t="b">
+      <c r="G2" t="b">
         <v>1</v>
       </c>
-      <c r="G2" t="b">
+      <c r="H2" t="b">
         <v>0</v>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>1420 WILSHIRE BLVD LOS ANGELES CA 90017</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>Single Family Residential</t>
         </is>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>215000</v>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>43000</v>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>2024-07-09</t>
         </is>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>50</v>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>2026-11-18</t>
-        </is>
-      </c>
       <c r="R2" t="inlineStr">
         <is>
+          <t>2026-11-19</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
           <t>1 Year from Deed Recording (Cal. Rev. &amp; Tax Code § 4675)</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>https://ttc.lacounty.gov/</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>Cal. Rev. &amp; Tax Code § 4675</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>Cal. Rev. &amp; Tax Code § 4675</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>2026-09-29 12:50:34</t>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Tax Deed Surplus</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>TAX_DEED</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:32:16</t>
         </is>
       </c>
     </row>
@@ -655,92 +685,107 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
           <t>2024-CA-005210</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>VICTOR &amp; MONICA REYES</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Individual / Estate</t>
         </is>
       </c>
-      <c r="F3" t="b">
+      <c r="G3" t="b">
         <v>1</v>
       </c>
-      <c r="G3" t="b">
+      <c r="H3" t="b">
         <v>0</v>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>4910 LA JOLLA BLVD SAN DIEGO CA 92037</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>Single Family Residential</t>
         </is>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>184000</v>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>36800</v>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>2024-07-16</t>
         </is>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>50</v>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>2026-11-18</t>
-        </is>
-      </c>
       <c r="R3" t="inlineStr">
         <is>
+          <t>2026-11-19</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
           <t>1 Year from Deed Recording (Cal. Rev. &amp; Tax Code § 4675)</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>https://www.sdttc.com/</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>Cal. Rev. &amp; Tax Code § 4675</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>Cal. Rev. &amp; Tax Code § 4675</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>2026-09-29 12:50:34</t>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Tax Deed Surplus</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>TAX_DEED</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:32:16</t>
         </is>
       </c>
     </row>
@@ -757,92 +802,107 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
           <t>2024-CA-008640</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>ESTATE OF CAROLINE DELGADO</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>Estate / Deceased</t>
         </is>
-      </c>
-      <c r="F4" t="b">
-        <v>1</v>
       </c>
       <c r="G4" t="b">
         <v>1</v>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H4" t="b">
+        <v>1</v>
+      </c>
+      <c r="I4" t="inlineStr">
         <is>
           <t>3820 SUNSET BLVD LOS ANGELES CA 90026</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>Single Family Residential</t>
         </is>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>168000</v>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>33600</v>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>2024-07-30</t>
         </is>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>50</v>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>2026-11-18</t>
-        </is>
-      </c>
       <c r="R4" t="inlineStr">
         <is>
+          <t>2026-11-19</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
           <t>1 Year from Deed Recording (Cal. Rev. &amp; Tax Code § 4675)</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>https://ttc.lacounty.gov/</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>Cal. Rev. &amp; Tax Code § 4675</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>Cal. Rev. &amp; Tax Code § 4675</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>2026-09-29 12:50:34</t>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Tax Deed Surplus</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>TAX_DEED</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:32:16</t>
         </is>
       </c>
     </row>
@@ -859,92 +919,107 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
           <t>2024-CA-005780</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>ESTATE OF DOUGLAS WINSLOW</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>Estate / Deceased</t>
         </is>
-      </c>
-      <c r="F5" t="b">
-        <v>1</v>
       </c>
       <c r="G5" t="b">
         <v>1</v>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H5" t="b">
+        <v>1</v>
+      </c>
+      <c r="I5" t="inlineStr">
         <is>
           <t>2104 CORONADO AVE SAN DIEGO CA 92154</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>Single Family Residential</t>
         </is>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>119500</v>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>23900</v>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>2024-08-06</t>
         </is>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>50</v>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>2026-11-18</t>
-        </is>
-      </c>
       <c r="R5" t="inlineStr">
         <is>
+          <t>2026-11-19</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
           <t>1 Year from Deed Recording (Cal. Rev. &amp; Tax Code § 4675)</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>https://www.sdttc.com/</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>Cal. Rev. &amp; Tax Code § 4675</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>Cal. Rev. &amp; Tax Code § 4675</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>2026-09-29 12:50:34</t>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Tax Deed Surplus</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>TAX_DEED</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:32:16</t>
         </is>
       </c>
     </row>

--- a/exports/California_Surplus_Feed.xlsx
+++ b/exports/California_Surplus_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:16</t>
+          <t>2026-10-01 13:10:51</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:16</t>
+          <t>2026-10-01 13:10:51</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:16</t>
+          <t>2026-10-01 13:10:51</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:16</t>
+          <t>2026-10-01 13:10:51</t>
         </is>
       </c>
     </row>

--- a/exports/California_Surplus_Feed.xlsx
+++ b/exports/California_Surplus_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-01 13:10:51</t>
+          <t>2026-10-02 12:32:01</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-01 13:10:51</t>
+          <t>2026-10-02 12:32:01</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-01 13:10:51</t>
+          <t>2026-10-02 12:32:01</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-01 13:10:51</t>
+          <t>2026-10-02 12:32:01</t>
         </is>
       </c>
     </row>

--- a/exports/California_Surplus_Feed.xlsx
+++ b/exports/California_Surplus_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2026-11-22</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:32:01</t>
+          <t>2026-10-03 11:37:45</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2026-11-22</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-02 12:32:01</t>
+          <t>2026-10-03 11:37:45</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2026-11-22</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-02 12:32:01</t>
+          <t>2026-10-03 11:37:45</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2026-11-22</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-02 12:32:01</t>
+          <t>2026-10-03 11:37:45</t>
         </is>
       </c>
     </row>

--- a/exports/California_Surplus_Feed.xlsx
+++ b/exports/California_Surplus_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-11-22</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-03 11:37:45</t>
+          <t>2026-10-04 12:19:33</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-11-22</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-03 11:37:45</t>
+          <t>2026-10-04 12:19:33</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-11-22</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-03 11:37:45</t>
+          <t>2026-10-04 12:19:33</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-11-22</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-03 11:37:45</t>
+          <t>2026-10-04 12:19:33</t>
         </is>
       </c>
     </row>

--- a/exports/California_Surplus_Feed.xlsx
+++ b/exports/California_Surplus_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-11-23</t>
+          <t>2026-11-24</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-04 12:19:33</t>
+          <t>2026-10-05 14:34:20</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-11-23</t>
+          <t>2026-11-24</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-04 12:19:33</t>
+          <t>2026-10-05 14:34:20</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-11-23</t>
+          <t>2026-11-24</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-04 12:19:33</t>
+          <t>2026-10-05 14:34:20</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-11-23</t>
+          <t>2026-11-24</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-04 12:19:33</t>
+          <t>2026-10-05 14:34:20</t>
         </is>
       </c>
     </row>

--- a/exports/California_Surplus_Feed.xlsx
+++ b/exports/California_Surplus_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-11-24</t>
+          <t>2026-11-25</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-05 14:34:20</t>
+          <t>2026-10-06 13:16:59</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-11-24</t>
+          <t>2026-11-25</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-05 14:34:20</t>
+          <t>2026-10-06 13:16:59</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-11-24</t>
+          <t>2026-11-25</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-05 14:34:20</t>
+          <t>2026-10-06 13:16:59</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-11-24</t>
+          <t>2026-11-25</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-05 14:34:20</t>
+          <t>2026-10-06 13:16:59</t>
         </is>
       </c>
     </row>

--- a/exports/California_Surplus_Feed.xlsx
+++ b/exports/California_Surplus_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-11-25</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-06 13:16:59</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-11-25</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-06 13:16:59</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-11-25</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-06 13:16:59</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-11-25</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-06 13:16:59</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>

--- a/exports/California_Surplus_Feed.xlsx
+++ b/exports/California_Surplus_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>

--- a/exports/California_Surplus_Feed.xlsx
+++ b/exports/California_Surplus_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>

--- a/exports/California_Surplus_Feed.xlsx
+++ b/exports/California_Surplus_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-28</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -643,7 +643,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>https://ttc.lacounty.gov/</t>
+          <t>https://ttc.lacounty.gov/tax-defaulted-property-sales/?docket=2024-CA-008120</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-28</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>https://www.sdttc.com/</t>
+          <t>https://www.sdttc.com/content/ttc/en/tax-collection/tax-sale.html?docket=2024-CA-005210</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-28</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>https://ttc.lacounty.gov/</t>
+          <t>https://ttc.lacounty.gov/tax-defaulted-property-sales/?docket=2024-CA-008640</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-28</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>https://www.sdttc.com/</t>
+          <t>https://www.sdttc.com/content/ttc/en/tax-collection/tax-sale.html?docket=2024-CA-005780</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>

--- a/exports/California_Surplus_Feed.xlsx
+++ b/exports/California_Surplus_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-11-28</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -643,7 +643,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>https://ttc.lacounty.gov/tax-defaulted-property-sales/?docket=2024-CA-008120</t>
+          <t>https://ttc.lacounty.gov/</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-11-28</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>https://www.sdttc.com/content/ttc/en/tax-collection/tax-sale.html?docket=2024-CA-005210</t>
+          <t>https://www.sdttc.com/</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-11-28</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>https://ttc.lacounty.gov/tax-defaulted-property-sales/?docket=2024-CA-008640</t>
+          <t>https://ttc.lacounty.gov/</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-11-28</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>https://www.sdttc.com/content/ttc/en/tax-collection/tax-sale.html?docket=2024-CA-005780</t>
+          <t>https://www.sdttc.com/</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>

--- a/exports/California_Surplus_Feed.xlsx
+++ b/exports/California_Surplus_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-29</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -643,7 +643,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>https://ttc.lacounty.gov/</t>
+          <t>https://ttc.lacounty.gov/notice-of-excess-proceeds/?docket=2024-CA-008120</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-29</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>https://www.sdttc.com/</t>
+          <t>https://www.sdttc.com/content/ttc/en/tax-collection/property-tax-sales.html?docket=2024-CA-005210</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-29</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>https://ttc.lacounty.gov/</t>
+          <t>https://ttc.lacounty.gov/notice-of-excess-proceeds/?docket=2024-CA-008640</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-29</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>https://www.sdttc.com/</t>
+          <t>https://www.sdttc.com/content/ttc/en/tax-collection/property-tax-sales.html?docket=2024-CA-005780</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>

--- a/exports/California_Surplus_Feed.xlsx
+++ b/exports/California_Surplus_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-11-29</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-11-29</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-11-29</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-11-29</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>

--- a/exports/California_Surplus_Feed.xlsx
+++ b/exports/California_Surplus_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>

--- a/exports/California_Surplus_Feed.xlsx
+++ b/exports/California_Surplus_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>

--- a/exports/California_Surplus_Feed.xlsx
+++ b/exports/California_Surplus_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>

--- a/exports/California_Surplus_Feed.xlsx
+++ b/exports/California_Surplus_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>

--- a/exports/California_Surplus_Feed.xlsx
+++ b/exports/California_Surplus_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>

--- a/exports/California_Surplus_Feed.xlsx
+++ b/exports/California_Surplus_Feed.xlsx
@@ -686,7 +686,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -818,7 +818,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -950,7 +950,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -1346,7 +1346,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -1610,7 +1610,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -1742,7 +1742,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -2006,7 +2006,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -2138,7 +2138,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -2270,7 +2270,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -2534,7 +2534,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -2798,7 +2798,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -3062,7 +3062,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -3194,7 +3194,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -3326,7 +3326,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -3458,7 +3458,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -3590,7 +3590,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -3722,7 +3722,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -3854,7 +3854,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -3986,7 +3986,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -4250,7 +4250,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -4778,7 +4778,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -4910,7 +4910,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -5042,7 +5042,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -5174,7 +5174,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -5306,7 +5306,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -5438,7 +5438,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -5570,7 +5570,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -5702,7 +5702,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -5834,7 +5834,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -5966,7 +5966,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -6098,7 +6098,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -6230,7 +6230,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -6362,7 +6362,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -6494,7 +6494,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -6626,7 +6626,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -6758,7 +6758,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -6890,7 +6890,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -7022,7 +7022,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -7154,7 +7154,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -7286,7 +7286,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -7418,7 +7418,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -7550,7 +7550,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -7682,7 +7682,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -7814,7 +7814,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -7946,7 +7946,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -8078,7 +8078,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -8210,7 +8210,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -8342,7 +8342,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -8474,7 +8474,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -8606,7 +8606,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -8738,7 +8738,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -8870,7 +8870,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -9002,7 +9002,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -9266,7 +9266,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -9398,7 +9398,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -9530,7 +9530,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -9662,7 +9662,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -9794,7 +9794,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -9926,7 +9926,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -10058,7 +10058,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -10190,7 +10190,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -10322,7 +10322,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -10454,7 +10454,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -10586,7 +10586,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -10718,7 +10718,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -10850,7 +10850,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -10982,7 +10982,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -11114,7 +11114,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -11246,7 +11246,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -11378,7 +11378,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -11510,7 +11510,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -11642,7 +11642,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -11774,7 +11774,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -11906,7 +11906,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -12038,7 +12038,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -12170,7 +12170,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -12302,7 +12302,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -12434,7 +12434,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -12566,7 +12566,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -12698,7 +12698,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -12830,7 +12830,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -12962,7 +12962,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -13094,7 +13094,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -13226,7 +13226,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -13358,7 +13358,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -13490,7 +13490,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -13622,7 +13622,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -13886,7 +13886,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -14018,7 +14018,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -14150,7 +14150,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -14282,7 +14282,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -14414,7 +14414,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -14546,7 +14546,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -14678,7 +14678,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -14810,7 +14810,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -14942,7 +14942,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -15074,7 +15074,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -15206,7 +15206,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -15338,7 +15338,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -15470,7 +15470,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -15602,7 +15602,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -15734,7 +15734,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>

--- a/exports/California_Surplus_Feed.xlsx
+++ b/exports/California_Surplus_Feed.xlsx
@@ -686,7 +686,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -818,7 +818,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -950,7 +950,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -1346,7 +1346,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -1610,7 +1610,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -1742,7 +1742,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -2006,7 +2006,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -2138,7 +2138,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -2270,7 +2270,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -2534,7 +2534,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -2798,7 +2798,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -3062,7 +3062,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -3194,7 +3194,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -3326,7 +3326,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -3458,7 +3458,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -3590,7 +3590,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -3722,7 +3722,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -3854,7 +3854,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -3986,7 +3986,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -4250,7 +4250,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -4778,7 +4778,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -4910,7 +4910,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -5042,7 +5042,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -5174,7 +5174,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -5306,7 +5306,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -5438,7 +5438,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -5570,7 +5570,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -5702,7 +5702,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -5834,7 +5834,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -5966,7 +5966,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -6098,7 +6098,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -6230,7 +6230,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -6362,7 +6362,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -6494,7 +6494,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -6626,7 +6626,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -6758,7 +6758,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -6890,7 +6890,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -7022,7 +7022,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -7154,7 +7154,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -7286,7 +7286,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -7418,7 +7418,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -7550,7 +7550,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -7682,7 +7682,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -7814,7 +7814,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -7946,7 +7946,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -8078,7 +8078,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -8210,7 +8210,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -8342,7 +8342,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -8474,7 +8474,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -8606,7 +8606,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -8738,7 +8738,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -8870,7 +8870,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -9002,7 +9002,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -9266,7 +9266,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -9398,7 +9398,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -9530,7 +9530,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -9662,7 +9662,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -9794,7 +9794,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -9926,7 +9926,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -10058,7 +10058,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -10190,7 +10190,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -10322,7 +10322,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -10454,7 +10454,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -10586,7 +10586,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -10718,7 +10718,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -10850,7 +10850,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -10982,7 +10982,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -11114,7 +11114,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -11246,7 +11246,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -11378,7 +11378,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -11510,7 +11510,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -11642,7 +11642,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -11774,7 +11774,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -11906,7 +11906,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -12038,7 +12038,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -12170,7 +12170,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -12302,7 +12302,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -12434,7 +12434,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -12566,7 +12566,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -12698,7 +12698,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -12830,7 +12830,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -12962,7 +12962,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -13094,7 +13094,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -13226,7 +13226,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -13358,7 +13358,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -13490,7 +13490,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -13622,7 +13622,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -13886,7 +13886,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -14018,7 +14018,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -14150,7 +14150,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -14282,7 +14282,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -14414,7 +14414,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -14546,7 +14546,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -14678,7 +14678,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -14810,7 +14810,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -14942,7 +14942,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -15074,7 +15074,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -15206,7 +15206,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -15338,7 +15338,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -15470,7 +15470,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -15602,7 +15602,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -15734,7 +15734,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>

--- a/exports/California_Surplus_Feed.xlsx
+++ b/exports/California_Surplus_Feed.xlsx
@@ -686,7 +686,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -818,7 +818,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -950,7 +950,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -1346,7 +1346,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -1610,7 +1610,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -1742,7 +1742,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -2006,7 +2006,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -2138,7 +2138,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -2270,7 +2270,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -2534,7 +2534,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -2798,7 +2798,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -3062,7 +3062,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -3194,7 +3194,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -3326,7 +3326,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -3458,7 +3458,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -3590,7 +3590,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -3722,7 +3722,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -3854,7 +3854,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -3986,7 +3986,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -4250,7 +4250,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -4778,7 +4778,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -4910,7 +4910,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -5042,7 +5042,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -5174,7 +5174,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -5306,7 +5306,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -5438,7 +5438,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -5570,7 +5570,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -5702,7 +5702,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -5834,7 +5834,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -5966,7 +5966,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -6098,7 +6098,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -6230,7 +6230,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -6362,7 +6362,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -6494,7 +6494,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -6626,7 +6626,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -6758,7 +6758,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -6890,7 +6890,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -7022,7 +7022,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -7154,7 +7154,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -7286,7 +7286,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -7418,7 +7418,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -7550,7 +7550,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -7682,7 +7682,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -7814,7 +7814,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -7946,7 +7946,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -8078,7 +8078,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -8210,7 +8210,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -8342,7 +8342,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -8474,7 +8474,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -8606,7 +8606,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -8738,7 +8738,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -8870,7 +8870,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -9002,7 +9002,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -9266,7 +9266,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -9398,7 +9398,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -9530,7 +9530,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -9662,7 +9662,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -9794,7 +9794,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -9926,7 +9926,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -10058,7 +10058,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -10190,7 +10190,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -10322,7 +10322,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -10454,7 +10454,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -10586,7 +10586,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -10718,7 +10718,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -10850,7 +10850,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -10982,7 +10982,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -11114,7 +11114,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -11246,7 +11246,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -11378,7 +11378,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -11510,7 +11510,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -11642,7 +11642,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -11774,7 +11774,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -11906,7 +11906,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -12038,7 +12038,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -12170,7 +12170,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -12302,7 +12302,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -12434,7 +12434,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -12566,7 +12566,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -12698,7 +12698,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -12830,7 +12830,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -12962,7 +12962,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -13094,7 +13094,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -13226,7 +13226,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -13358,7 +13358,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -13490,7 +13490,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -13622,7 +13622,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -13886,7 +13886,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -14018,7 +14018,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -14150,7 +14150,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -14282,7 +14282,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -14414,7 +14414,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -14546,7 +14546,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -14678,7 +14678,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -14810,7 +14810,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -14942,7 +14942,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -15074,7 +15074,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -15206,7 +15206,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -15338,7 +15338,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -15470,7 +15470,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -15602,7 +15602,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -15734,7 +15734,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>

--- a/exports/California_Surplus_Feed.xlsx
+++ b/exports/California_Surplus_Feed.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,142 +429,142 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>County</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Parcel_ID</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Case_or_TaxDeed_No</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Owner_Name</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Entity_Type</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Is_Individual</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Heir_Search_Recommended</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Property_Address</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Property_Type</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Surplus_Balance_USD</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Statutory_Fee_Rate</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Est_Finder_Fee_USD</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Opportunity_Tier</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Sale_Date</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Days_Remaining_To_Claim</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Claim_Urgency_Tier</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Claim_Deadline_Date</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Statutory_Deadline_Window</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Clerk_Verification_URL</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Verify_Note</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Source_URL</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Governing_Statute</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Statute_Citation</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Record_Type</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>TYPE</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Retrieved_At</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Enriched_Timestamp</t>
         </is>
@@ -627,7 +639,7 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -681,12 +693,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:57Z</t>
+          <t>2026-10-17T10:41:39Z</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -759,7 +771,7 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -813,12 +825,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:57Z</t>
+          <t>2026-10-17T10:41:39Z</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -891,7 +903,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -945,12 +957,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:57Z</t>
+          <t>2026-10-17T10:41:39Z</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -1023,7 +1035,7 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -1077,12 +1089,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:57Z</t>
+          <t>2026-10-17T10:41:39Z</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -1155,7 +1167,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1209,12 +1221,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:55Z</t>
+          <t>2026-10-17T10:41:36Z</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -1287,7 +1299,7 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -1341,12 +1353,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:55Z</t>
+          <t>2026-10-17T10:41:36Z</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -1419,7 +1431,7 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -1473,12 +1485,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:57Z</t>
+          <t>2026-10-17T10:41:39Z</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1563,7 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -1605,12 +1617,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:57Z</t>
+          <t>2026-10-17T10:41:39Z</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -1683,7 +1695,7 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>-101</v>
+        <v>-102</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -1737,12 +1749,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:56Z</t>
+          <t>2026-10-17T10:41:38Z</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -1815,7 +1827,7 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -1869,12 +1881,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:57Z</t>
+          <t>2026-10-17T10:41:39Z</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -1947,7 +1959,7 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -2001,12 +2013,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:57Z</t>
+          <t>2026-10-17T10:41:39Z</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -2079,7 +2091,7 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>-101</v>
+        <v>-102</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -2133,12 +2145,12 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:56Z</t>
+          <t>2026-10-17T10:41:38Z</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -2211,7 +2223,7 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -2265,12 +2277,12 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:57Z</t>
+          <t>2026-10-17T10:41:39Z</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -2343,7 +2355,7 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -2397,12 +2409,12 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:55Z</t>
+          <t>2026-10-17T10:41:36Z</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -2475,7 +2487,7 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
@@ -2529,12 +2541,12 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:57Z</t>
+          <t>2026-10-17T10:41:39Z</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -2607,7 +2619,7 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -2661,12 +2673,12 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:55Z</t>
+          <t>2026-10-17T10:41:36Z</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -2739,7 +2751,7 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>-101</v>
+        <v>-102</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -2793,12 +2805,12 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:56Z</t>
+          <t>2026-10-17T10:41:38Z</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -2871,7 +2883,7 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -2925,12 +2937,12 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:55Z</t>
+          <t>2026-10-17T10:41:36Z</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -3003,7 +3015,7 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>-101</v>
+        <v>-102</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -3057,12 +3069,12 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:56Z</t>
+          <t>2026-10-17T10:41:38Z</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -3135,7 +3147,7 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -3189,12 +3201,12 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:55Z</t>
+          <t>2026-10-17T10:41:36Z</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -3267,7 +3279,7 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -3321,12 +3333,12 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:57Z</t>
+          <t>2026-10-17T10:41:39Z</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -3399,7 +3411,7 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -3453,12 +3465,12 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:55Z</t>
+          <t>2026-10-17T10:41:36Z</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -3531,7 +3543,7 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -3585,12 +3597,12 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:55Z</t>
+          <t>2026-10-17T10:41:36Z</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3675,7 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -3717,12 +3729,12 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:55Z</t>
+          <t>2026-10-17T10:41:36Z</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -3795,7 +3807,7 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -3849,12 +3861,12 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:55Z</t>
+          <t>2026-10-17T10:41:36Z</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -3927,7 +3939,7 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -3981,12 +3993,12 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:55Z</t>
+          <t>2026-10-17T10:41:36Z</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -4059,7 +4071,7 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>-101</v>
+        <v>-102</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
@@ -4113,12 +4125,12 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:56Z</t>
+          <t>2026-10-17T10:41:38Z</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -4191,7 +4203,7 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
@@ -4245,12 +4257,12 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:57Z</t>
+          <t>2026-10-17T10:41:39Z</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -4323,7 +4335,7 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
@@ -4377,12 +4389,12 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:55Z</t>
+          <t>2026-10-17T10:41:36Z</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -4455,7 +4467,7 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
@@ -4509,12 +4521,12 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:57Z</t>
+          <t>2026-10-17T10:41:39Z</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -4587,7 +4599,7 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
@@ -4641,12 +4653,12 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:57Z</t>
+          <t>2026-10-17T10:41:39Z</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -4719,7 +4731,7 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
@@ -4773,12 +4785,12 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:57Z</t>
+          <t>2026-10-17T10:41:39Z</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -4851,7 +4863,7 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
@@ -4905,12 +4917,12 @@
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:57Z</t>
+          <t>2026-10-17T10:41:39Z</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -4983,7 +4995,7 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
@@ -5037,12 +5049,12 @@
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:55Z</t>
+          <t>2026-10-17T10:41:36Z</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -5115,7 +5127,7 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
@@ -5169,12 +5181,12 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:57Z</t>
+          <t>2026-10-17T10:41:39Z</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -5247,7 +5259,7 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
@@ -5301,12 +5313,12 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:55Z</t>
+          <t>2026-10-17T10:41:36Z</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -5379,7 +5391,7 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
@@ -5433,12 +5445,12 @@
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:55Z</t>
+          <t>2026-10-17T10:41:36Z</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -5511,7 +5523,7 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
@@ -5565,12 +5577,12 @@
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:55Z</t>
+          <t>2026-10-17T10:41:36Z</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -5643,7 +5655,7 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
@@ -5697,12 +5709,12 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:55Z</t>
+          <t>2026-10-17T10:41:36Z</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -5775,7 +5787,7 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
@@ -5829,12 +5841,12 @@
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:55Z</t>
+          <t>2026-10-17T10:41:36Z</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -5907,7 +5919,7 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>-101</v>
+        <v>-102</v>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
@@ -5961,12 +5973,12 @@
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:56Z</t>
+          <t>2026-10-17T10:41:38Z</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -6039,7 +6051,7 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
@@ -6093,12 +6105,12 @@
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:55Z</t>
+          <t>2026-10-17T10:41:36Z</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -6171,7 +6183,7 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
@@ -6225,12 +6237,12 @@
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:55Z</t>
+          <t>2026-10-17T10:41:36Z</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -6303,7 +6315,7 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
@@ -6357,12 +6369,12 @@
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:57Z</t>
+          <t>2026-10-17T10:41:39Z</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -6435,7 +6447,7 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
@@ -6489,12 +6501,12 @@
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:55Z</t>
+          <t>2026-10-17T10:41:36Z</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -6567,7 +6579,7 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
@@ -6621,12 +6633,12 @@
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:55Z</t>
+          <t>2026-10-17T10:41:36Z</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -6699,7 +6711,7 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
@@ -6753,12 +6765,12 @@
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:55Z</t>
+          <t>2026-10-17T10:41:36Z</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -6831,7 +6843,7 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
@@ -6885,12 +6897,12 @@
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:55Z</t>
+          <t>2026-10-17T10:41:36Z</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -6963,7 +6975,7 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
@@ -7017,12 +7029,12 @@
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:55Z</t>
+          <t>2026-10-17T10:41:36Z</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -7095,7 +7107,7 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
@@ -7149,12 +7161,12 @@
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:55Z</t>
+          <t>2026-10-17T10:41:36Z</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -7227,7 +7239,7 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
@@ -7281,12 +7293,12 @@
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:55Z</t>
+          <t>2026-10-17T10:41:36Z</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -7359,7 +7371,7 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
@@ -7413,12 +7425,12 @@
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:55Z</t>
+          <t>2026-10-17T10:41:36Z</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -7491,7 +7503,7 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
@@ -7545,12 +7557,12 @@
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:57Z</t>
+          <t>2026-10-17T10:41:39Z</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -7623,7 +7635,7 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
@@ -7677,12 +7689,12 @@
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:55Z</t>
+          <t>2026-10-17T10:41:36Z</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -7755,7 +7767,7 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
@@ -7809,12 +7821,12 @@
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:55Z</t>
+          <t>2026-10-17T10:41:36Z</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -7887,7 +7899,7 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
@@ -7941,12 +7953,12 @@
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:55Z</t>
+          <t>2026-10-17T10:41:36Z</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -8019,7 +8031,7 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
@@ -8073,12 +8085,12 @@
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:55Z</t>
+          <t>2026-10-17T10:41:36Z</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -8151,7 +8163,7 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
@@ -8205,12 +8217,12 @@
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:55Z</t>
+          <t>2026-10-17T10:41:36Z</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -8283,7 +8295,7 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
@@ -8337,12 +8349,12 @@
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:57Z</t>
+          <t>2026-10-17T10:41:39Z</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -8415,7 +8427,7 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
@@ -8469,12 +8481,12 @@
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:55Z</t>
+          <t>2026-10-17T10:41:36Z</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -8547,7 +8559,7 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
@@ -8601,12 +8613,12 @@
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:57Z</t>
+          <t>2026-10-17T10:41:39Z</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -8679,7 +8691,7 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
@@ -8733,12 +8745,12 @@
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:55Z</t>
+          <t>2026-10-17T10:41:36Z</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -8811,7 +8823,7 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
@@ -8865,12 +8877,12 @@
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:57Z</t>
+          <t>2026-10-17T10:41:39Z</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -8943,7 +8955,7 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
@@ -8997,12 +9009,12 @@
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:55Z</t>
+          <t>2026-10-17T10:41:36Z</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -9075,7 +9087,7 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
@@ -9129,12 +9141,12 @@
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:55Z</t>
+          <t>2026-10-17T10:41:36Z</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -9207,7 +9219,7 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
@@ -9261,12 +9273,12 @@
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:55Z</t>
+          <t>2026-10-17T10:41:36Z</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -9339,7 +9351,7 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
@@ -9393,12 +9405,12 @@
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:57Z</t>
+          <t>2026-10-17T10:41:39Z</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -9471,7 +9483,7 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
@@ -9525,12 +9537,12 @@
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:55Z</t>
+          <t>2026-10-17T10:41:36Z</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -9603,7 +9615,7 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
@@ -9657,12 +9669,12 @@
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:55Z</t>
+          <t>2026-10-17T10:41:36Z</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -9735,7 +9747,7 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
@@ -9789,12 +9801,12 @@
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:57Z</t>
+          <t>2026-10-17T10:41:39Z</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -9867,7 +9879,7 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>-101</v>
+        <v>-102</v>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
@@ -9921,12 +9933,12 @@
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:56Z</t>
+          <t>2026-10-17T10:41:38Z</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -9999,7 +10011,7 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
@@ -10053,12 +10065,12 @@
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:55Z</t>
+          <t>2026-10-17T10:41:36Z</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -10131,7 +10143,7 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
@@ -10185,12 +10197,12 @@
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:55Z</t>
+          <t>2026-10-17T10:41:36Z</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -10263,7 +10275,7 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
@@ -10317,12 +10329,12 @@
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:55Z</t>
+          <t>2026-10-17T10:41:36Z</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -10395,7 +10407,7 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
@@ -10449,12 +10461,12 @@
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:55Z</t>
+          <t>2026-10-17T10:41:36Z</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -10527,7 +10539,7 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
@@ -10581,12 +10593,12 @@
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:55Z</t>
+          <t>2026-10-17T10:41:36Z</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -10659,7 +10671,7 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
@@ -10713,12 +10725,12 @@
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:55Z</t>
+          <t>2026-10-17T10:41:36Z</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -10791,7 +10803,7 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
@@ -10845,12 +10857,12 @@
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:55Z</t>
+          <t>2026-10-17T10:41:36Z</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -10923,7 +10935,7 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
@@ -10977,12 +10989,12 @@
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:57Z</t>
+          <t>2026-10-17T10:41:39Z</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -11055,7 +11067,7 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
@@ -11109,12 +11121,12 @@
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:57Z</t>
+          <t>2026-10-17T10:41:39Z</t>
         </is>
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -11187,7 +11199,7 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
@@ -11241,12 +11253,12 @@
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:57Z</t>
+          <t>2026-10-17T10:41:39Z</t>
         </is>
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -11319,7 +11331,7 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q83" t="inlineStr">
         <is>
@@ -11373,12 +11385,12 @@
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:55Z</t>
+          <t>2026-10-17T10:41:36Z</t>
         </is>
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -11451,7 +11463,7 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
@@ -11505,12 +11517,12 @@
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:57Z</t>
+          <t>2026-10-17T10:41:39Z</t>
         </is>
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -11583,7 +11595,7 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
@@ -11637,12 +11649,12 @@
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:55Z</t>
+          <t>2026-10-17T10:41:36Z</t>
         </is>
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -11715,7 +11727,7 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="Q86" t="inlineStr">
         <is>
@@ -11769,12 +11781,12 @@
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:57Z</t>
+          <t>2026-10-17T10:41:39Z</t>
         </is>
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -11847,7 +11859,7 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
@@ -11901,12 +11913,12 @@
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:57Z</t>
+          <t>2026-10-17T10:41:39Z</t>
         </is>
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -11979,7 +11991,7 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
@@ -12033,12 +12045,12 @@
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:55Z</t>
+          <t>2026-10-17T10:41:36Z</t>
         </is>
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -12111,7 +12123,7 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
@@ -12165,12 +12177,12 @@
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:55Z</t>
+          <t>2026-10-17T10:41:36Z</t>
         </is>
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -12243,7 +12255,7 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
@@ -12297,12 +12309,12 @@
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:55Z</t>
+          <t>2026-10-17T10:41:36Z</t>
         </is>
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -12375,7 +12387,7 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
@@ -12429,12 +12441,12 @@
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:55Z</t>
+          <t>2026-10-17T10:41:36Z</t>
         </is>
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -12507,7 +12519,7 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q92" t="inlineStr">
         <is>
@@ -12561,12 +12573,12 @@
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:55Z</t>
+          <t>2026-10-17T10:41:36Z</t>
         </is>
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -12639,7 +12651,7 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
@@ -12693,12 +12705,12 @@
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:55Z</t>
+          <t>2026-10-17T10:41:36Z</t>
         </is>
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -12771,7 +12783,7 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q94" t="inlineStr">
         <is>
@@ -12825,12 +12837,12 @@
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:55Z</t>
+          <t>2026-10-17T10:41:36Z</t>
         </is>
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -12903,7 +12915,7 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q95" t="inlineStr">
         <is>
@@ -12957,12 +12969,12 @@
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:55Z</t>
+          <t>2026-10-17T10:41:36Z</t>
         </is>
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -13035,7 +13047,7 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
@@ -13089,12 +13101,12 @@
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:55Z</t>
+          <t>2026-10-17T10:41:36Z</t>
         </is>
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -13167,7 +13179,7 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q97" t="inlineStr">
         <is>
@@ -13221,12 +13233,12 @@
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:55Z</t>
+          <t>2026-10-17T10:41:36Z</t>
         </is>
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -13299,7 +13311,7 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q98" t="inlineStr">
         <is>
@@ -13353,12 +13365,12 @@
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:55Z</t>
+          <t>2026-10-17T10:41:36Z</t>
         </is>
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -13431,7 +13443,7 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q99" t="inlineStr">
         <is>
@@ -13485,12 +13497,12 @@
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:55Z</t>
+          <t>2026-10-17T10:41:36Z</t>
         </is>
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -13563,7 +13575,7 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q100" t="inlineStr">
         <is>
@@ -13617,12 +13629,12 @@
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:55Z</t>
+          <t>2026-10-17T10:41:36Z</t>
         </is>
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -13695,7 +13707,7 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q101" t="inlineStr">
         <is>
@@ -13749,12 +13761,12 @@
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:55Z</t>
+          <t>2026-10-17T10:41:36Z</t>
         </is>
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -13827,7 +13839,7 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="Q102" t="inlineStr">
         <is>
@@ -13881,12 +13893,12 @@
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:57Z</t>
+          <t>2026-10-17T10:41:39Z</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -13959,7 +13971,7 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
@@ -14013,12 +14025,12 @@
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:55Z</t>
+          <t>2026-10-17T10:41:36Z</t>
         </is>
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -14091,7 +14103,7 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q104" t="inlineStr">
         <is>
@@ -14145,12 +14157,12 @@
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:55Z</t>
+          <t>2026-10-17T10:41:36Z</t>
         </is>
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -14223,7 +14235,7 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q105" t="inlineStr">
         <is>
@@ -14277,12 +14289,12 @@
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:55Z</t>
+          <t>2026-10-17T10:41:36Z</t>
         </is>
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -14355,7 +14367,7 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q106" t="inlineStr">
         <is>
@@ -14409,12 +14421,12 @@
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:55Z</t>
+          <t>2026-10-17T10:41:36Z</t>
         </is>
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -14487,7 +14499,7 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q107" t="inlineStr">
         <is>
@@ -14541,12 +14553,12 @@
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:55Z</t>
+          <t>2026-10-17T10:41:36Z</t>
         </is>
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -14619,7 +14631,7 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q108" t="inlineStr">
         <is>
@@ -14673,12 +14685,12 @@
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:55Z</t>
+          <t>2026-10-17T10:41:36Z</t>
         </is>
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -14751,7 +14763,7 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q109" t="inlineStr">
         <is>
@@ -14805,12 +14817,12 @@
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:55Z</t>
+          <t>2026-10-17T10:41:36Z</t>
         </is>
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -14883,7 +14895,7 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q110" t="inlineStr">
         <is>
@@ -14937,12 +14949,12 @@
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:55Z</t>
+          <t>2026-10-17T10:41:36Z</t>
         </is>
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -15015,7 +15027,7 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="Q111" t="inlineStr">
         <is>
@@ -15069,12 +15081,12 @@
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:57Z</t>
+          <t>2026-10-17T10:41:39Z</t>
         </is>
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -15147,7 +15159,7 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q112" t="inlineStr">
         <is>
@@ -15201,12 +15213,12 @@
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:55Z</t>
+          <t>2026-10-17T10:41:36Z</t>
         </is>
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -15279,7 +15291,7 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q113" t="inlineStr">
         <is>
@@ -15333,12 +15345,12 @@
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:55Z</t>
+          <t>2026-10-17T10:41:36Z</t>
         </is>
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -15411,7 +15423,7 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q114" t="inlineStr">
         <is>
@@ -15465,12 +15477,12 @@
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:55Z</t>
+          <t>2026-10-17T10:41:36Z</t>
         </is>
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -15543,7 +15555,7 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q115" t="inlineStr">
         <is>
@@ -15597,12 +15609,12 @@
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:55Z</t>
+          <t>2026-10-17T10:41:36Z</t>
         </is>
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -15675,7 +15687,7 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q116" t="inlineStr">
         <is>
@@ -15729,12 +15741,12 @@
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:55Z</t>
+          <t>2026-10-17T10:41:36Z</t>
         </is>
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>

--- a/exports/California_Surplus_Feed.xlsx
+++ b/exports/California_Surplus_Feed.xlsx
@@ -586,11 +586,7 @@
           <t>360-150-12-00</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>SD-7102-0263</t>
-        </is>
-      </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>DISE LEONARD L 1999 TRUST ET AL</t>
@@ -639,7 +635,7 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -693,12 +689,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:39Z</t>
+          <t>2026-10-18T11:01:50Z</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -718,11 +714,7 @@
           <t>583-810-27-00</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>SD-7102-0395</t>
-        </is>
-      </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>SPARKS FREDERICK V JR</t>
@@ -771,7 +763,7 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -825,12 +817,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:39Z</t>
+          <t>2026-10-18T11:01:50Z</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -850,11 +842,7 @@
           <t>646-150-44-06</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>SD-7102-0450</t>
-        </is>
-      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>HERMOSILLO VICTOR M G S</t>
@@ -903,7 +891,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -957,12 +945,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:39Z</t>
+          <t>2026-10-18T11:01:50Z</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -982,11 +970,7 @@
           <t>666-130-09-00</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>SD-7102-0462</t>
-        </is>
-      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>SANTA BARBARA HOUSING ASSISTANCE</t>
@@ -1035,7 +1019,7 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -1089,12 +1073,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:39Z</t>
+          <t>2026-10-18T11:01:50Z</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -1114,11 +1098,7 @@
           <t>7206-005-014</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>LA-ITEM-3686-7206-005-014</t>
-        </is>
-      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>Assessed Titleholder of Record (APN 7206-005-014)</t>
@@ -1167,7 +1147,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1221,12 +1201,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:36Z</t>
+          <t>2026-10-18T11:01:49Z</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -1246,11 +1226,7 @@
           <t>4335-008-104</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>LA-ITEM-1748-4335-008-104</t>
-        </is>
-      </c>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>Assessed Titleholder of Record (APN 4335-008-104)</t>
@@ -1299,7 +1275,7 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -1353,12 +1329,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:36Z</t>
+          <t>2026-10-18T11:01:49Z</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -1378,11 +1354,7 @@
           <t>666-130-06-00</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>SD-7102-0459</t>
-        </is>
-      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>SANTA BARBARA HOUSING ASSISTANCE</t>
@@ -1431,7 +1403,7 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -1485,12 +1457,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:39Z</t>
+          <t>2026-10-18T11:01:50Z</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -1510,11 +1482,7 @@
           <t>283-111-28-00</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>SD-7102-0208</t>
-        </is>
-      </c>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t>MYERS M JOYCE TRUST 08-14-03 ET AL</t>
@@ -1563,7 +1531,7 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -1617,12 +1585,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:39Z</t>
+          <t>2026-10-18T11:01:50Z</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -1642,11 +1610,7 @@
           <t>105-152-16</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>OC-13-001473</t>
-        </is>
-      </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>STOUGHTON, SAMUEL C</t>
@@ -1695,7 +1659,7 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>-102</v>
+        <v>-103</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -1749,12 +1713,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:38Z</t>
+          <t>2026-10-18T11:01:49Z</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -1774,11 +1738,7 @@
           <t>666-130-04-00</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>SD-7102-0457</t>
-        </is>
-      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>SANTA BARBARA HOUSING ASSISTANCE</t>
@@ -1827,7 +1787,7 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -1881,12 +1841,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:39Z</t>
+          <t>2026-10-18T11:01:50Z</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -1906,11 +1866,7 @@
           <t>158-190-31-36</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>SD-7102-0061</t>
-        </is>
-      </c>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t>GEOFFREY CADY ET AL</t>
@@ -1959,7 +1915,7 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -2013,12 +1969,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:39Z</t>
+          <t>2026-10-18T11:01:50Z</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -2038,11 +1994,7 @@
           <t>656-124-20</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>OC-19-004452</t>
-        </is>
-      </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>MALONEY, MICHAEL G TR LANGTON W G</t>
@@ -2091,7 +2043,7 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>-102</v>
+        <v>-103</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -2145,12 +2097,12 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:38Z</t>
+          <t>2026-10-18T11:01:49Z</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -2170,11 +2122,7 @@
           <t>321-080-51-00</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>SD-7102-0245</t>
-        </is>
-      </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>NGUYEN ANH ET AL</t>
@@ -2223,7 +2171,7 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -2277,12 +2225,12 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:39Z</t>
+          <t>2026-10-18T11:01:50Z</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -2302,11 +2250,7 @@
           <t>5454-019-029</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>LA-ITEM-2297-5454-019-029</t>
-        </is>
-      </c>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>Assessed Titleholder of Record (APN 5454-019-029)</t>
@@ -2355,7 +2299,7 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -2409,12 +2353,12 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:36Z</t>
+          <t>2026-10-18T11:01:49Z</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -2434,11 +2378,7 @@
           <t>666-130-05-00</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>SD-7102-0458</t>
-        </is>
-      </c>
+      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
           <t>SANTA BARBARA HOUSING ASSISTANCE</t>
@@ -2487,7 +2427,7 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
@@ -2541,12 +2481,12 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:39Z</t>
+          <t>2026-10-18T11:01:50Z</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -2566,11 +2506,7 @@
           <t>5132-011-088</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>LA-ITEM-3600-5132-011-088</t>
-        </is>
-      </c>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>Assessed Titleholder of Record (APN 5132-011-088)</t>
@@ -2619,7 +2555,7 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -2673,12 +2609,12 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:36Z</t>
+          <t>2026-10-18T11:01:49Z</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -2698,11 +2634,7 @@
           <t>105-222-71</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>OC-19-001093</t>
-        </is>
-      </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>SLATE, PHILIP</t>
@@ -2751,7 +2683,7 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>-102</v>
+        <v>-103</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -2805,12 +2737,12 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:38Z</t>
+          <t>2026-10-18T11:01:49Z</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -2830,11 +2762,7 @@
           <t>7524-014-147</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>LA-ITEM-3096-7524-014-147</t>
-        </is>
-      </c>
+      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
           <t>Assessed Titleholder of Record (APN 7524-014-147)</t>
@@ -2883,7 +2811,7 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -2937,12 +2865,12 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:36Z</t>
+          <t>2026-10-18T11:01:49Z</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -2962,11 +2890,7 @@
           <t>644-426-08</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>OC-19-004356</t>
-        </is>
-      </c>
+      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
           <t>ESTRADA, KAREN TR THE K ESTRADA F</t>
@@ -3015,7 +2939,7 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>-102</v>
+        <v>-103</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -3069,12 +2993,12 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:38Z</t>
+          <t>2026-10-18T11:01:49Z</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -3094,11 +3018,7 @@
           <t>7524-014-139</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>LA-ITEM-3095-7524-014-139</t>
-        </is>
-      </c>
+      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
           <t>Assessed Titleholder of Record (APN 7524-014-139)</t>
@@ -3147,7 +3067,7 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -3201,12 +3121,12 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:36Z</t>
+          <t>2026-10-18T11:01:49Z</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -3226,11 +3146,7 @@
           <t>113-060-02-00</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>SD-7102-0034</t>
-        </is>
-      </c>
+      <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
           <t>TATE EVELYN W E EST OF</t>
@@ -3279,7 +3195,7 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -3333,12 +3249,12 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:39Z</t>
+          <t>2026-10-18T11:01:50Z</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -3358,11 +3274,7 @@
           <t>6030-026-017</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>LA-ITEM-2579-6030-026-017</t>
-        </is>
-      </c>
+      <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
           <t>Assessed Titleholder of Record (APN 6030-026-017)</t>
@@ -3411,7 +3323,7 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -3465,12 +3377,12 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:36Z</t>
+          <t>2026-10-18T11:01:49Z</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -3490,11 +3402,7 @@
           <t>4115-008-038</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>LA-ITEM-1663-4115-008-038</t>
-        </is>
-      </c>
+      <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
           <t>Assessed Titleholder of Record (APN 4115-008-038)</t>
@@ -3543,7 +3451,7 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -3597,12 +3505,12 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:36Z</t>
+          <t>2026-10-18T11:01:49Z</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -3622,11 +3530,7 @@
           <t>3128-008-022</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>LA-ITEM-1017-3128-008-022</t>
-        </is>
-      </c>
+      <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
           <t>Assessed Titleholder of Record (APN 3128-008-022)</t>
@@ -3675,7 +3579,7 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -3729,12 +3633,12 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:36Z</t>
+          <t>2026-10-18T11:01:49Z</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -3754,11 +3658,7 @@
           <t>4462-013-011</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>LA-ITEM-1873-4462-013-011</t>
-        </is>
-      </c>
+      <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
           <t>Assessed Titleholder of Record (APN 4462-013-011)</t>
@@ -3807,7 +3707,7 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -3861,12 +3761,12 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:36Z</t>
+          <t>2026-10-18T11:01:49Z</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -3886,11 +3786,7 @@
           <t>3247-041-013</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>LA-ITEM-1234-3247-041-013</t>
-        </is>
-      </c>
+      <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
           <t>Assessed Titleholder of Record (APN 3247-041-013)</t>
@@ -3939,7 +3835,7 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -3993,12 +3889,12 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:36Z</t>
+          <t>2026-10-18T11:01:49Z</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -4018,11 +3914,7 @@
           <t>121-254-30</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>OC-17-001130</t>
-        </is>
-      </c>
+      <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
           <t>THE LUI FAMILY TRUST</t>
@@ -4071,7 +3963,7 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>-102</v>
+        <v>-103</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
@@ -4125,12 +4017,12 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:38Z</t>
+          <t>2026-10-18T11:01:49Z</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -4150,11 +4042,7 @@
           <t>666-130-07-00</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>SD-7102-0460</t>
-        </is>
-      </c>
+      <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
           <t>SANTA BARBARA HOUSING ASSISTANCE</t>
@@ -4203,7 +4091,7 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
@@ -4257,12 +4145,12 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:39Z</t>
+          <t>2026-10-18T11:01:50Z</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -4282,11 +4170,7 @@
           <t>5224-013-015</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>LA-ITEM-3607-5224-013-015</t>
-        </is>
-      </c>
+      <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
           <t>Assessed Titleholder of Record (APN 5224-013-015)</t>
@@ -4335,7 +4219,7 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
@@ -4389,12 +4273,12 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:36Z</t>
+          <t>2026-10-18T11:01:49Z</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -4414,11 +4298,7 @@
           <t>609-172-48-00</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>SD-7102-0429</t>
-        </is>
-      </c>
+      <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
           <t>ALLERGY ABETEMENT&amp;RELIEFME DICAL ET AL</t>
@@ -4467,7 +4347,7 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
@@ -4521,12 +4401,12 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:39Z</t>
+          <t>2026-10-18T11:01:50Z</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -4546,11 +4426,7 @@
           <t>188-223-24-00</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>SD-7102-0091</t>
-        </is>
-      </c>
+      <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
           <t>HEINTSCHEL CHARLES E ROTH IRA NO3543 ET AL</t>
@@ -4599,7 +4475,7 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
@@ -4653,12 +4529,12 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:39Z</t>
+          <t>2026-10-18T11:01:50Z</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -4678,11 +4554,7 @@
           <t>666-130-08-00</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>SD-7102-0461</t>
-        </is>
-      </c>
+      <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
           <t>SANTA BARBARA HOUSING ASSISTANCE</t>
@@ -4731,7 +4603,7 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
@@ -4785,12 +4657,12 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:39Z</t>
+          <t>2026-10-18T11:01:50Z</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -4810,11 +4682,7 @@
           <t>212-192-01-00</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>SD-7102-0120</t>
-        </is>
-      </c>
+      <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
           <t>CHIDELLA NAGA R ET AL</t>
@@ -4863,7 +4731,7 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
@@ -4917,12 +4785,12 @@
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:39Z</t>
+          <t>2026-10-18T11:01:50Z</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -4942,11 +4810,7 @@
           <t>3046-026-013</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>LA-ITEM-712-3046-026-013</t>
-        </is>
-      </c>
+      <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
           <t>Assessed Titleholder of Record (APN 3046-026-013)</t>
@@ -4995,7 +4859,7 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
@@ -5049,12 +4913,12 @@
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:36Z</t>
+          <t>2026-10-18T11:01:49Z</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -5074,11 +4938,7 @@
           <t>399-160-12-00</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>SD-7102-0275</t>
-        </is>
-      </c>
+      <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
           <t>DELBIANCO BRUNO&amp;BEATRICETRUS T 08 ET AL</t>
@@ -5127,7 +4987,7 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
@@ -5181,12 +5041,12 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:39Z</t>
+          <t>2026-10-18T11:01:50Z</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -5206,11 +5066,7 @@
           <t>3012-025-019</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>LA-ITEM-3481-3012-025-019</t>
-        </is>
-      </c>
+      <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
           <t>Assessed Titleholder of Record (APN 3012-025-019)</t>
@@ -5259,7 +5115,7 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
@@ -5313,12 +5169,12 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:36Z</t>
+          <t>2026-10-18T11:01:49Z</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -5338,11 +5194,7 @@
           <t>2061-018-063</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>LA-ITEM-27-2061-018-063</t>
-        </is>
-      </c>
+      <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
           <t>Assessed Titleholder of Record (APN 2061-018-063)</t>
@@ -5391,7 +5243,7 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
@@ -5445,12 +5297,12 @@
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:36Z</t>
+          <t>2026-10-18T11:01:49Z</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -5470,11 +5322,7 @@
           <t>3243-023-024</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>LA-ITEM-1229-3243-023-024</t>
-        </is>
-      </c>
+      <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
           <t>Assessed Titleholder of Record (APN 3243-023-024)</t>
@@ -5523,7 +5371,7 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
@@ -5577,12 +5425,12 @@
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:36Z</t>
+          <t>2026-10-18T11:01:49Z</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -5602,11 +5450,7 @@
           <t>5556-002-012</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>LA-ITEM-2401-5556-002-012</t>
-        </is>
-      </c>
+      <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
           <t>Assessed Titleholder of Record (APN 5556-002-012)</t>
@@ -5655,7 +5499,7 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
@@ -5709,12 +5553,12 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:36Z</t>
+          <t>2026-10-18T11:01:49Z</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -5734,11 +5578,7 @@
           <t>4462-006-012</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>LA-ITEM-1870-4462-006-012</t>
-        </is>
-      </c>
+      <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
           <t>Assessed Titleholder of Record (APN 4462-006-012)</t>
@@ -5787,7 +5627,7 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
@@ -5841,12 +5681,12 @@
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:36Z</t>
+          <t>2026-10-18T11:01:49Z</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -5866,11 +5706,7 @@
           <t>105-101-10</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>OC-14-001188</t>
-        </is>
-      </c>
+      <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
           <t>BAKER, RONALD HOWARD</t>
@@ -5919,7 +5755,7 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>-102</v>
+        <v>-103</v>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
@@ -5973,12 +5809,12 @@
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:38Z</t>
+          <t>2026-10-18T11:01:49Z</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -5998,11 +5834,7 @@
           <t>3030-003-093</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>LA-ITEM-3486-3030-003-093</t>
-        </is>
-      </c>
+      <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
           <t>Assessed Titleholder of Record (APN 3030-003-093)</t>
@@ -6051,7 +5883,7 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
@@ -6105,12 +5937,12 @@
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:36Z</t>
+          <t>2026-10-18T11:01:49Z</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -6130,11 +5962,7 @@
           <t>3052-018-021</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>LA-ITEM-747-3052-018-021</t>
-        </is>
-      </c>
+      <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
           <t>Assessed Titleholder of Record (APN 3052-018-021)</t>
@@ -6183,7 +6011,7 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
@@ -6237,12 +6065,12 @@
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:36Z</t>
+          <t>2026-10-18T11:01:49Z</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -6262,11 +6090,7 @@
           <t>225-800-23-00</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>SD-7102-0134</t>
-        </is>
-      </c>
+      <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
           <t>EUREKA SPRINGS HOMEOWNERS ASSOCIA</t>
@@ -6315,7 +6139,7 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
@@ -6369,12 +6193,12 @@
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:39Z</t>
+          <t>2026-10-18T11:01:50Z</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -6394,11 +6218,7 @@
           <t>3057-005-046</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>LA-ITEM-3519-3057-005-046</t>
-        </is>
-      </c>
+      <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
           <t>Assessed Titleholder of Record (APN 3057-005-046)</t>
@@ -6447,7 +6267,7 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
@@ -6501,12 +6321,12 @@
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:36Z</t>
+          <t>2026-10-18T11:01:49Z</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -6526,11 +6346,7 @@
           <t>3046-026-014</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>LA-ITEM-713-3046-026-014</t>
-        </is>
-      </c>
+      <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
           <t>Assessed Titleholder of Record (APN 3046-026-014)</t>
@@ -6579,7 +6395,7 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
@@ -6633,12 +6449,12 @@
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:36Z</t>
+          <t>2026-10-18T11:01:49Z</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -6658,11 +6474,7 @@
           <t>5462-022-009</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>LA-ITEM-2322-5462-022-009</t>
-        </is>
-      </c>
+      <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
           <t>Assessed Titleholder of Record (APN 5462-022-009)</t>
@@ -6711,7 +6523,7 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
@@ -6765,12 +6577,12 @@
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:36Z</t>
+          <t>2026-10-18T11:01:49Z</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -6790,11 +6602,7 @@
           <t>3041-034-017</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>LA-ITEM-3505-3041-034-017</t>
-        </is>
-      </c>
+      <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
           <t>Assessed Titleholder of Record (APN 3041-034-017)</t>
@@ -6843,7 +6651,7 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
@@ -6897,12 +6705,12 @@
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:36Z</t>
+          <t>2026-10-18T11:01:49Z</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -6922,11 +6730,7 @@
           <t>3053-031-012</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>LA-ITEM-3513-3053-031-012</t>
-        </is>
-      </c>
+      <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
           <t>Assessed Titleholder of Record (APN 3053-031-012)</t>
@@ -6975,7 +6779,7 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
@@ -7029,12 +6833,12 @@
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:36Z</t>
+          <t>2026-10-18T11:01:49Z</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -7054,11 +6858,7 @@
           <t>3206-062-039</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>LA-ITEM-1130-3206-062-039</t>
-        </is>
-      </c>
+      <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
           <t>Assessed Titleholder of Record (APN 3206-062-039)</t>
@@ -7107,7 +6907,7 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
@@ -7161,12 +6961,12 @@
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:36Z</t>
+          <t>2026-10-18T11:01:49Z</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -7186,11 +6986,7 @@
           <t>5462-022-010</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>LA-ITEM-2323-5462-022-010</t>
-        </is>
-      </c>
+      <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
           <t>Assessed Titleholder of Record (APN 5462-022-010)</t>
@@ -7239,7 +7035,7 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
@@ -7293,12 +7089,12 @@
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:36Z</t>
+          <t>2026-10-18T11:01:49Z</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -7318,11 +7114,7 @@
           <t>6271-031-015</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>LA-ITEM-3673-6271-031-015</t>
-        </is>
-      </c>
+      <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
           <t>Assessed Titleholder of Record (APN 6271-031-015)</t>
@@ -7371,7 +7163,7 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
@@ -7425,12 +7217,12 @@
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:36Z</t>
+          <t>2026-10-18T11:01:49Z</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -7450,11 +7242,7 @@
           <t>253-390-53-00</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>SD-7102-0146</t>
-        </is>
-      </c>
+      <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
           <t>TEURMAN DIANNE D ET AL</t>
@@ -7503,7 +7291,7 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
@@ -7557,12 +7345,12 @@
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:39Z</t>
+          <t>2026-10-18T11:01:50Z</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -7582,11 +7370,7 @@
           <t>3084-017-020</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>LA-ITEM-912-3084-017-020</t>
-        </is>
-      </c>
+      <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
           <t>Assessed Titleholder of Record (APN 3084-017-020)</t>
@@ -7635,7 +7419,7 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
@@ -7689,12 +7473,12 @@
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:36Z</t>
+          <t>2026-10-18T11:01:49Z</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -7714,11 +7498,7 @@
           <t>3211-013-082</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>LA-ITEM-1135-3211-013-082</t>
-        </is>
-      </c>
+      <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
           <t>Assessed Titleholder of Record (APN 3211-013-082)</t>
@@ -7767,7 +7547,7 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
@@ -7821,12 +7601,12 @@
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:36Z</t>
+          <t>2026-10-18T11:01:49Z</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -7846,11 +7626,7 @@
           <t>3027-012-066</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>LA-ITEM-604-3027-012-066</t>
-        </is>
-      </c>
+      <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
           <t>Assessed Titleholder of Record (APN 3027-012-066)</t>
@@ -7899,7 +7675,7 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
@@ -7953,12 +7729,12 @@
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:36Z</t>
+          <t>2026-10-18T11:01:49Z</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -7978,11 +7754,7 @@
           <t>5306-017-024</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>LA-ITEM-2226-5306-017-024</t>
-        </is>
-      </c>
+      <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
           <t>Assessed Titleholder of Record (APN 5306-017-024)</t>
@@ -8031,7 +7803,7 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
@@ -8085,12 +7857,12 @@
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:36Z</t>
+          <t>2026-10-18T11:01:49Z</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -8110,11 +7882,7 @@
           <t>3053-028-009</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>LA-ITEM-763-3053-028-009</t>
-        </is>
-      </c>
+      <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
           <t>Assessed Titleholder of Record (APN 3053-028-009)</t>
@@ -8163,7 +7931,7 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
@@ -8217,12 +7985,12 @@
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:36Z</t>
+          <t>2026-10-18T11:01:49Z</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -8242,11 +8010,7 @@
           <t>295-254-09-00</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>SD-7102-0224</t>
-        </is>
-      </c>
+      <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
           <t>MATTHEWS THOMAS</t>
@@ -8295,7 +8059,7 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
@@ -8349,12 +8113,12 @@
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:39Z</t>
+          <t>2026-10-18T11:01:50Z</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -8374,11 +8138,7 @@
           <t>3024-004-043</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>LA-ITEM-3482-3024-004-043</t>
-        </is>
-      </c>
+      <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
           <t>Assessed Titleholder of Record (APN 3024-004-043)</t>
@@ -8427,7 +8187,7 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
@@ -8481,12 +8241,12 @@
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:36Z</t>
+          <t>2026-10-18T11:01:49Z</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -8506,11 +8266,7 @@
           <t>295-210-46-00</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>SD-7102-0222</t>
-        </is>
-      </c>
+      <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
           <t>KESSNER HAROLD W EST OF ET AL</t>
@@ -8559,7 +8315,7 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
@@ -8613,12 +8369,12 @@
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:39Z</t>
+          <t>2026-10-18T11:01:50Z</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -8638,11 +8394,7 @@
           <t>3039-013-001</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>LA-ITEM-3497-3039-013-001</t>
-        </is>
-      </c>
+      <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
           <t>Assessed Titleholder of Record (APN 3039-013-001)</t>
@@ -8691,7 +8443,7 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
@@ -8745,12 +8497,12 @@
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:36Z</t>
+          <t>2026-10-18T11:01:49Z</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -8770,11 +8522,7 @@
           <t>199-140-02-00</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>SD-7102-0111</t>
-        </is>
-      </c>
+      <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
           <t>NAGY BARBARA S EST OF</t>
@@ -8823,7 +8571,7 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
@@ -8877,12 +8625,12 @@
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:39Z</t>
+          <t>2026-10-18T11:01:50Z</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -8902,11 +8650,7 @@
           <t>3030-023-054</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>LA-ITEM-626-3030-023-054</t>
-        </is>
-      </c>
+      <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
           <t>Assessed Titleholder of Record (APN 3030-023-054)</t>
@@ -8955,7 +8699,7 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
@@ -9009,12 +8753,12 @@
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:36Z</t>
+          <t>2026-10-18T11:01:49Z</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -9034,11 +8778,7 @@
           <t>4380-033-004</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>LA-ITEM-1808-4380-033-004</t>
-        </is>
-      </c>
+      <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
           <t>Assessed Titleholder of Record (APN 4380-033-004)</t>
@@ -9087,7 +8827,7 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
@@ -9141,12 +8881,12 @@
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:36Z</t>
+          <t>2026-10-18T11:01:49Z</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -9166,11 +8906,7 @@
           <t>3118-002-030</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>LA-ITEM-997-3118-002-030</t>
-        </is>
-      </c>
+      <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
           <t>Assessed Titleholder of Record (APN 3118-002-030)</t>
@@ -9219,7 +8955,7 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
@@ -9273,12 +9009,12 @@
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:36Z</t>
+          <t>2026-10-18T11:01:49Z</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -9298,11 +9034,7 @@
           <t>141-350-39-00</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>SD-7102-0055</t>
-        </is>
-      </c>
+      <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
           <t>SCOTT DARLENE A ET AL</t>
@@ -9351,7 +9083,7 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
@@ -9405,12 +9137,12 @@
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:39Z</t>
+          <t>2026-10-18T11:01:50Z</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -9430,11 +9162,7 @@
           <t>3086-009-015</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>LA-ITEM-919-3086-009-015</t>
-        </is>
-      </c>
+      <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
           <t>Assessed Titleholder of Record (APN 3086-009-015)</t>
@@ -9483,7 +9211,7 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
@@ -9537,12 +9265,12 @@
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:36Z</t>
+          <t>2026-10-18T11:01:49Z</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -9562,11 +9290,7 @@
           <t>2428-028-037</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>LA-ITEM-236-2428-028-037</t>
-        </is>
-      </c>
+      <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
           <t>Assessed Titleholder of Record (APN 2428-028-037)</t>
@@ -9615,7 +9339,7 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
@@ -9669,12 +9393,12 @@
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:36Z</t>
+          <t>2026-10-18T11:01:49Z</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -9694,11 +9418,7 @@
           <t>198-093-22-00</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>SD-7102-0100</t>
-        </is>
-      </c>
+      <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
           <t>SEIM ALLAN C ET AL</t>
@@ -9747,7 +9467,7 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
@@ -9801,12 +9521,12 @@
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:39Z</t>
+          <t>2026-10-18T11:01:50Z</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -9826,11 +9546,7 @@
           <t>105-101-11</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>OC-14-001189</t>
-        </is>
-      </c>
+      <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
           <t>BAKER, RONALD HOWARD</t>
@@ -9879,7 +9595,7 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>-102</v>
+        <v>-103</v>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
@@ -9933,12 +9649,12 @@
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:38Z</t>
+          <t>2026-10-18T11:01:49Z</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -9958,11 +9674,7 @@
           <t>3037-014-008</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>LA-ITEM-3493-3037-014-008</t>
-        </is>
-      </c>
+      <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
           <t>Assessed Titleholder of Record (APN 3037-014-008)</t>
@@ -10011,7 +9723,7 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
@@ -10065,12 +9777,12 @@
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:36Z</t>
+          <t>2026-10-18T11:01:49Z</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -10090,11 +9802,7 @@
           <t>3040-003-026</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>LA-ITEM-3500-3040-003-026</t>
-        </is>
-      </c>
+      <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
           <t>Assessed Titleholder of Record (APN 3040-003-026)</t>
@@ -10143,7 +9851,7 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
@@ -10197,12 +9905,12 @@
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:36Z</t>
+          <t>2026-10-18T11:01:49Z</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -10222,11 +9930,7 @@
           <t>3040-021-028</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>LA-ITEM-674-3040-021-028</t>
-        </is>
-      </c>
+      <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
           <t>Assessed Titleholder of Record (APN 3040-021-028)</t>
@@ -10275,7 +9979,7 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
@@ -10329,12 +10033,12 @@
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:36Z</t>
+          <t>2026-10-18T11:01:49Z</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -10354,11 +10058,7 @@
           <t>3040-008-016</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>LA-ITEM-3501-3040-008-016</t>
-        </is>
-      </c>
+      <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
           <t>Assessed Titleholder of Record (APN 3040-008-016)</t>
@@ -10407,7 +10107,7 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
@@ -10461,12 +10161,12 @@
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:36Z</t>
+          <t>2026-10-18T11:01:49Z</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -10486,11 +10186,7 @@
           <t>3037-014-010</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>LA-ITEM-3495-3037-014-010</t>
-        </is>
-      </c>
+      <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
           <t>Assessed Titleholder of Record (APN 3037-014-010)</t>
@@ -10539,7 +10235,7 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
@@ -10593,12 +10289,12 @@
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:36Z</t>
+          <t>2026-10-18T11:01:49Z</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -10618,11 +10314,7 @@
           <t>3076-011-005</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>LA-ITEM-3530-3076-011-005</t>
-        </is>
-      </c>
+      <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
           <t>Assessed Titleholder of Record (APN 3076-011-005)</t>
@@ -10671,7 +10363,7 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
@@ -10725,12 +10417,12 @@
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:36Z</t>
+          <t>2026-10-18T11:01:49Z</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -10750,11 +10442,7 @@
           <t>3028-015-008</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>LA-ITEM-3483-3028-015-008</t>
-        </is>
-      </c>
+      <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
           <t>Assessed Titleholder of Record (APN 3028-015-008)</t>
@@ -10803,7 +10491,7 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
@@ -10857,12 +10545,12 @@
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:36Z</t>
+          <t>2026-10-18T11:01:49Z</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -10882,11 +10570,7 @@
           <t>295-210-47-00</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>SD-7102-0223</t>
-        </is>
-      </c>
+      <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
           <t>KESSNER HAROLD W EST OF ET AL</t>
@@ -10935,7 +10619,7 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
@@ -10989,12 +10673,12 @@
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:39Z</t>
+          <t>2026-10-18T11:01:50Z</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -11014,11 +10698,7 @@
           <t>299-242-26-21</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>SD-7102-2397</t>
-        </is>
-      </c>
+      <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
           <t>BUSH 1987 TRUST ET AL</t>
@@ -11067,7 +10747,7 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
@@ -11121,12 +10801,12 @@
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:39Z</t>
+          <t>2026-10-18T11:01:50Z</t>
         </is>
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -11146,11 +10826,7 @@
           <t>198-262-04-00</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>SD-7102-0106</t>
-        </is>
-      </c>
+      <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr">
         <is>
           <t>THOMASSET MARY K</t>
@@ -11199,7 +10875,7 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
@@ -11253,12 +10929,12 @@
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:39Z</t>
+          <t>2026-10-18T11:01:50Z</t>
         </is>
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -11278,11 +10954,7 @@
           <t>3082-001-015</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>LA-ITEM-3539-3082-001-015</t>
-        </is>
-      </c>
+      <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr">
         <is>
           <t>Assessed Titleholder of Record (APN 3082-001-015)</t>
@@ -11331,7 +11003,7 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q83" t="inlineStr">
         <is>
@@ -11385,12 +11057,12 @@
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:36Z</t>
+          <t>2026-10-18T11:01:49Z</t>
         </is>
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -11410,11 +11082,7 @@
           <t>198-351-19-00</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>SD-7102-0108</t>
-        </is>
-      </c>
+      <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr">
         <is>
           <t>ROBSHAW FREDERICK H ET AL</t>
@@ -11463,7 +11131,7 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
@@ -11517,12 +11185,12 @@
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:39Z</t>
+          <t>2026-10-18T11:01:50Z</t>
         </is>
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -11542,11 +11210,7 @@
           <t>4106-018-016</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>LA-ITEM-1585-4106-018-016</t>
-        </is>
-      </c>
+      <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr">
         <is>
           <t>Assessed Titleholder of Record (APN 4106-018-016)</t>
@@ -11595,7 +11259,7 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
@@ -11649,12 +11313,12 @@
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:36Z</t>
+          <t>2026-10-18T11:01:49Z</t>
         </is>
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -11674,11 +11338,7 @@
           <t>238-152-26-00</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>SD-7102-0141</t>
-        </is>
-      </c>
+      <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr">
         <is>
           <t>CITRON COMMUNITY ASSN</t>
@@ -11727,7 +11387,7 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q86" t="inlineStr">
         <is>
@@ -11781,12 +11441,12 @@
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:39Z</t>
+          <t>2026-10-18T11:01:50Z</t>
         </is>
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -11806,11 +11466,7 @@
           <t>198-230-40-00</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>SD-7102-0101</t>
-        </is>
-      </c>
+      <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr">
         <is>
           <t>SIMONS CECILE M</t>
@@ -11859,7 +11515,7 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
@@ -11913,12 +11569,12 @@
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:39Z</t>
+          <t>2026-10-18T11:01:50Z</t>
         </is>
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -11938,11 +11594,7 @@
           <t>3040-030-013</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>LA-ITEM-684-3040-030-013</t>
-        </is>
-      </c>
+      <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr">
         <is>
           <t>Assessed Titleholder of Record (APN 3040-030-013)</t>
@@ -11991,7 +11643,7 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
@@ -12045,12 +11697,12 @@
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:36Z</t>
+          <t>2026-10-18T11:01:49Z</t>
         </is>
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -12070,11 +11722,7 @@
           <t>3227-008-026</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>LA-ITEM-1206-3227-008-026</t>
-        </is>
-      </c>
+      <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr">
         <is>
           <t>Assessed Titleholder of Record (APN 3227-008-026)</t>
@@ -12123,7 +11771,7 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
@@ -12177,12 +11825,12 @@
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:36Z</t>
+          <t>2026-10-18T11:01:49Z</t>
         </is>
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -12202,11 +11850,7 @@
           <t>3030-023-064</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>LA-ITEM-627-3030-023-064</t>
-        </is>
-      </c>
+      <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr">
         <is>
           <t>Assessed Titleholder of Record (APN 3030-023-064)</t>
@@ -12255,7 +11899,7 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
@@ -12309,12 +11953,12 @@
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:36Z</t>
+          <t>2026-10-18T11:01:49Z</t>
         </is>
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -12334,11 +11978,7 @@
           <t>3040-030-012</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>LA-ITEM-683-3040-030-012</t>
-        </is>
-      </c>
+      <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr">
         <is>
           <t>Assessed Titleholder of Record (APN 3040-030-012)</t>
@@ -12387,7 +12027,7 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
@@ -12441,12 +12081,12 @@
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:36Z</t>
+          <t>2026-10-18T11:01:49Z</t>
         </is>
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -12466,11 +12106,7 @@
           <t>3078-018-040</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>LA-ITEM-872-3078-018-040</t>
-        </is>
-      </c>
+      <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr">
         <is>
           <t>Assessed Titleholder of Record (APN 3078-018-040)</t>
@@ -12519,7 +12155,7 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q92" t="inlineStr">
         <is>
@@ -12573,12 +12209,12 @@
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:36Z</t>
+          <t>2026-10-18T11:01:49Z</t>
         </is>
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -12598,11 +12234,7 @@
           <t>3082-010-033</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>LA-ITEM-3540-3082-010-033</t>
-        </is>
-      </c>
+      <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr">
         <is>
           <t>Assessed Titleholder of Record (APN 3082-010-033)</t>
@@ -12651,7 +12283,7 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
@@ -12705,12 +12337,12 @@
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:36Z</t>
+          <t>2026-10-18T11:01:49Z</t>
         </is>
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -12730,11 +12362,7 @@
           <t>5585-001-006</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>LA-ITEM-2428-5585-001-006</t>
-        </is>
-      </c>
+      <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr">
         <is>
           <t>Assessed Titleholder of Record (APN 5585-001-006)</t>
@@ -12783,7 +12411,7 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q94" t="inlineStr">
         <is>
@@ -12837,12 +12465,12 @@
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:36Z</t>
+          <t>2026-10-18T11:01:49Z</t>
         </is>
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -12862,11 +12490,7 @@
           <t>3091-020-016</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>LA-ITEM-933-3091-020-016</t>
-        </is>
-      </c>
+      <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr">
         <is>
           <t>Assessed Titleholder of Record (APN 3091-020-016)</t>
@@ -12915,7 +12539,7 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q95" t="inlineStr">
         <is>
@@ -12969,12 +12593,12 @@
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:36Z</t>
+          <t>2026-10-18T11:01:49Z</t>
         </is>
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -12994,11 +12618,7 @@
           <t>3084-019-018</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>LA-ITEM-913-3084-019-018</t>
-        </is>
-      </c>
+      <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr">
         <is>
           <t>Assessed Titleholder of Record (APN 3084-019-018)</t>
@@ -13047,7 +12667,7 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
@@ -13101,12 +12721,12 @@
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:36Z</t>
+          <t>2026-10-18T11:01:49Z</t>
         </is>
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -13126,11 +12746,7 @@
           <t>3116-010-054</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>LA-ITEM-987-3116-010-054</t>
-        </is>
-      </c>
+      <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr">
         <is>
           <t>Assessed Titleholder of Record (APN 3116-010-054)</t>
@@ -13179,7 +12795,7 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q97" t="inlineStr">
         <is>
@@ -13233,12 +12849,12 @@
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:36Z</t>
+          <t>2026-10-18T11:01:49Z</t>
         </is>
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -13258,11 +12874,7 @@
           <t>3083-018-008</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>LA-ITEM-908-3083-018-008</t>
-        </is>
-      </c>
+      <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr">
         <is>
           <t>Assessed Titleholder of Record (APN 3083-018-008)</t>
@@ -13311,7 +12923,7 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q98" t="inlineStr">
         <is>
@@ -13365,12 +12977,12 @@
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:36Z</t>
+          <t>2026-10-18T11:01:49Z</t>
         </is>
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -13390,11 +13002,7 @@
           <t>3116-011-022</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>LA-ITEM-988-3116-011-022</t>
-        </is>
-      </c>
+      <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr">
         <is>
           <t>Assessed Titleholder of Record (APN 3116-011-022)</t>
@@ -13443,7 +13051,7 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q99" t="inlineStr">
         <is>
@@ -13497,12 +13105,12 @@
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:36Z</t>
+          <t>2026-10-18T11:01:49Z</t>
         </is>
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -13522,11 +13130,7 @@
           <t>2526-013-024</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>LA-ITEM-3462-2526-013-024</t>
-        </is>
-      </c>
+      <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr">
         <is>
           <t>Assessed Titleholder of Record (APN 2526-013-024)</t>
@@ -13575,7 +13179,7 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q100" t="inlineStr">
         <is>
@@ -13629,12 +13233,12 @@
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:36Z</t>
+          <t>2026-10-18T11:01:49Z</t>
         </is>
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -13654,11 +13258,7 @@
           <t>3225-004-019</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>LA-ITEM-1196-3225-004-019</t>
-        </is>
-      </c>
+      <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr">
         <is>
           <t>Assessed Titleholder of Record (APN 3225-004-019)</t>
@@ -13707,7 +13307,7 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q101" t="inlineStr">
         <is>
@@ -13761,12 +13361,12 @@
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:36Z</t>
+          <t>2026-10-18T11:01:49Z</t>
         </is>
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -13786,11 +13386,7 @@
           <t>293-093-16-00</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>SD-7102-0212</t>
-        </is>
-      </c>
+      <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr">
         <is>
           <t>BIRDSONG BILLY G 2003 TRUST 09-05 ET AL</t>
@@ -13839,7 +13435,7 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q102" t="inlineStr">
         <is>
@@ -13893,12 +13489,12 @@
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:39Z</t>
+          <t>2026-10-18T11:01:50Z</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -13918,11 +13514,7 @@
           <t>3386-023-003</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>LA-ITEM-3559-3386-023-003</t>
-        </is>
-      </c>
+      <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr">
         <is>
           <t>Assessed Titleholder of Record (APN 3386-023-003)</t>
@@ -13971,7 +13563,7 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
@@ -14025,12 +13617,12 @@
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:36Z</t>
+          <t>2026-10-18T11:01:49Z</t>
         </is>
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -14050,11 +13642,7 @@
           <t>5607-021-006</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>LA-ITEM-2436-5607-021-006</t>
-        </is>
-      </c>
+      <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr">
         <is>
           <t>Assessed Titleholder of Record (APN 5607-021-006)</t>
@@ -14103,7 +13691,7 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q104" t="inlineStr">
         <is>
@@ -14157,12 +13745,12 @@
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:36Z</t>
+          <t>2026-10-18T11:01:49Z</t>
         </is>
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -14182,11 +13770,7 @@
           <t>3063-016-007</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>LA-ITEM-812-3063-016-007</t>
-        </is>
-      </c>
+      <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr">
         <is>
           <t>Assessed Titleholder of Record (APN 3063-016-007)</t>
@@ -14235,7 +13819,7 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q105" t="inlineStr">
         <is>
@@ -14289,12 +13873,12 @@
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:36Z</t>
+          <t>2026-10-18T11:01:49Z</t>
         </is>
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -14314,11 +13898,7 @@
           <t>3030-010-025</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>LA-ITEM-620-3030-010-025</t>
-        </is>
-      </c>
+      <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr">
         <is>
           <t>Assessed Titleholder of Record (APN 3030-010-025)</t>
@@ -14367,7 +13947,7 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q106" t="inlineStr">
         <is>
@@ -14421,12 +14001,12 @@
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:36Z</t>
+          <t>2026-10-18T11:01:49Z</t>
         </is>
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -14446,11 +14026,7 @@
           <t>5607-021-007</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>LA-ITEM-2437-5607-021-007</t>
-        </is>
-      </c>
+      <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr">
         <is>
           <t>Assessed Titleholder of Record (APN 5607-021-007)</t>
@@ -14499,7 +14075,7 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q107" t="inlineStr">
         <is>
@@ -14553,12 +14129,12 @@
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:36Z</t>
+          <t>2026-10-18T11:01:49Z</t>
         </is>
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -14578,11 +14154,7 @@
           <t>3064-025-026</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>LA-ITEM-819-3064-025-026</t>
-        </is>
-      </c>
+      <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr">
         <is>
           <t>Assessed Titleholder of Record (APN 3064-025-026)</t>
@@ -14631,7 +14203,7 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q108" t="inlineStr">
         <is>
@@ -14685,12 +14257,12 @@
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:36Z</t>
+          <t>2026-10-18T11:01:49Z</t>
         </is>
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -14710,11 +14282,7 @@
           <t>3270-003-058</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>LA-ITEM-1318-3270-003-058</t>
-        </is>
-      </c>
+      <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr">
         <is>
           <t>Assessed Titleholder of Record (APN 3270-003-058)</t>
@@ -14763,7 +14331,7 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q109" t="inlineStr">
         <is>
@@ -14817,12 +14385,12 @@
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:36Z</t>
+          <t>2026-10-18T11:01:49Z</t>
         </is>
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -14842,11 +14410,7 @@
           <t>5003-023-018</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>LA-ITEM-2572-5003-023-018</t>
-        </is>
-      </c>
+      <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr">
         <is>
           <t>Assessed Titleholder of Record (APN 5003-023-018)</t>
@@ -14895,7 +14459,7 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q110" t="inlineStr">
         <is>
@@ -14949,12 +14513,12 @@
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:36Z</t>
+          <t>2026-10-18T11:01:49Z</t>
         </is>
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -14974,11 +14538,7 @@
           <t>253-314-19-00</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>SD-7102-0145</t>
-        </is>
-      </c>
+      <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr">
         <is>
           <t>WIEDENHEFT MAVIS R ET AL</t>
@@ -15027,7 +14587,7 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q111" t="inlineStr">
         <is>
@@ -15081,12 +14641,12 @@
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:39Z</t>
+          <t>2026-10-18T11:01:50Z</t>
         </is>
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -15106,11 +14666,7 @@
           <t>3064-026-008</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>LA-ITEM-820-3064-026-008</t>
-        </is>
-      </c>
+      <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
           <t>Assessed Titleholder of Record (APN 3064-026-008)</t>
@@ -15159,7 +14715,7 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q112" t="inlineStr">
         <is>
@@ -15213,12 +14769,12 @@
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:36Z</t>
+          <t>2026-10-18T11:01:49Z</t>
         </is>
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -15238,11 +14794,7 @@
           <t>5467-025-019</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>LA-ITEM-3626-5467-025-019</t>
-        </is>
-      </c>
+      <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr">
         <is>
           <t>Assessed Titleholder of Record (APN 5467-025-019)</t>
@@ -15291,7 +14843,7 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q113" t="inlineStr">
         <is>
@@ -15345,12 +14897,12 @@
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:36Z</t>
+          <t>2026-10-18T11:01:49Z</t>
         </is>
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -15370,11 +14922,7 @@
           <t>3063-016-003</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>LA-ITEM-810-3063-016-003</t>
-        </is>
-      </c>
+      <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr">
         <is>
           <t>Assessed Titleholder of Record (APN 3063-016-003)</t>
@@ -15423,7 +14971,7 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q114" t="inlineStr">
         <is>
@@ -15477,12 +15025,12 @@
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:36Z</t>
+          <t>2026-10-18T11:01:49Z</t>
         </is>
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -15502,11 +15050,7 @@
           <t>4371-042-023</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>LA-ITEM-1795-4371-042-023</t>
-        </is>
-      </c>
+      <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr">
         <is>
           <t>Assessed Titleholder of Record (APN 4371-042-023)</t>
@@ -15555,7 +15099,7 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q115" t="inlineStr">
         <is>
@@ -15609,12 +15153,12 @@
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:36Z</t>
+          <t>2026-10-18T11:01:49Z</t>
         </is>
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -15634,11 +15178,7 @@
           <t>3063-005-027</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>LA-ITEM-3525-3063-005-027</t>
-        </is>
-      </c>
+      <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr">
         <is>
           <t>Assessed Titleholder of Record (APN 3063-005-027)</t>
@@ -15687,7 +15227,7 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q116" t="inlineStr">
         <is>
@@ -15741,12 +15281,12 @@
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:36Z</t>
+          <t>2026-10-18T11:01:49Z</t>
         </is>
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>

--- a/exports/California_Surplus_Feed.xlsx
+++ b/exports/California_Surplus_Feed.xlsx
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -689,12 +689,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:50Z</t>
+          <t>2026-10-19T13:10:41Z</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -763,7 +763,7 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -817,12 +817,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:50Z</t>
+          <t>2026-10-19T13:10:41Z</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -945,12 +945,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:50Z</t>
+          <t>2026-10-19T13:10:41Z</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:50Z</t>
+          <t>2026-10-19T13:10:41Z</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -1147,7 +1147,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1201,12 +1201,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:49Z</t>
+          <t>2026-10-19T13:10:40Z</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -1275,7 +1275,7 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:49Z</t>
+          <t>2026-10-19T13:10:40Z</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -1403,7 +1403,7 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -1457,12 +1457,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:50Z</t>
+          <t>2026-10-19T13:10:41Z</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:50Z</t>
+          <t>2026-10-19T13:10:41Z</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>-103</v>
+        <v>-104</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -1713,12 +1713,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:49Z</t>
+          <t>2026-10-19T13:10:41Z</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -1787,7 +1787,7 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -1841,12 +1841,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:50Z</t>
+          <t>2026-10-19T13:10:41Z</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -1915,7 +1915,7 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -1969,12 +1969,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:50Z</t>
+          <t>2026-10-19T13:10:41Z</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -2043,7 +2043,7 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>-103</v>
+        <v>-104</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:49Z</t>
+          <t>2026-10-19T13:10:41Z</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -2225,12 +2225,12 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:50Z</t>
+          <t>2026-10-19T13:10:41Z</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -2299,7 +2299,7 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -2353,12 +2353,12 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:49Z</t>
+          <t>2026-10-19T13:10:40Z</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -2427,7 +2427,7 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
@@ -2481,12 +2481,12 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:50Z</t>
+          <t>2026-10-19T13:10:41Z</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -2609,12 +2609,12 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:49Z</t>
+          <t>2026-10-19T13:10:40Z</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>-103</v>
+        <v>-104</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -2737,12 +2737,12 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:49Z</t>
+          <t>2026-10-19T13:10:41Z</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2811,7 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -2865,12 +2865,12 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:49Z</t>
+          <t>2026-10-19T13:10:40Z</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -2939,7 +2939,7 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>-103</v>
+        <v>-104</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -2993,12 +2993,12 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:49Z</t>
+          <t>2026-10-19T13:10:41Z</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -3067,7 +3067,7 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -3121,12 +3121,12 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:49Z</t>
+          <t>2026-10-19T13:10:40Z</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -3195,7 +3195,7 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -3249,12 +3249,12 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:50Z</t>
+          <t>2026-10-19T13:10:41Z</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -3323,7 +3323,7 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -3377,12 +3377,12 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:49Z</t>
+          <t>2026-10-19T13:10:40Z</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -3505,12 +3505,12 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:49Z</t>
+          <t>2026-10-19T13:10:40Z</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -3579,7 +3579,7 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -3633,12 +3633,12 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:49Z</t>
+          <t>2026-10-19T13:10:40Z</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -3707,7 +3707,7 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -3761,12 +3761,12 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:49Z</t>
+          <t>2026-10-19T13:10:40Z</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -3835,7 +3835,7 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -3889,12 +3889,12 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:49Z</t>
+          <t>2026-10-19T13:10:40Z</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -3963,7 +3963,7 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>-103</v>
+        <v>-104</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
@@ -4017,12 +4017,12 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:49Z</t>
+          <t>2026-10-19T13:10:41Z</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -4091,7 +4091,7 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
@@ -4145,12 +4145,12 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:50Z</t>
+          <t>2026-10-19T13:10:41Z</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -4219,7 +4219,7 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
@@ -4273,12 +4273,12 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:49Z</t>
+          <t>2026-10-19T13:10:40Z</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
@@ -4401,12 +4401,12 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:50Z</t>
+          <t>2026-10-19T13:10:41Z</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -4475,7 +4475,7 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
@@ -4529,12 +4529,12 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:50Z</t>
+          <t>2026-10-19T13:10:41Z</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -4603,7 +4603,7 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
@@ -4657,12 +4657,12 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:50Z</t>
+          <t>2026-10-19T13:10:41Z</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
@@ -4785,12 +4785,12 @@
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:50Z</t>
+          <t>2026-10-19T13:10:41Z</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -4859,7 +4859,7 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
@@ -4913,12 +4913,12 @@
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:49Z</t>
+          <t>2026-10-19T13:10:40Z</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -4987,7 +4987,7 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
@@ -5041,12 +5041,12 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:50Z</t>
+          <t>2026-10-19T13:10:41Z</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -5115,7 +5115,7 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:49Z</t>
+          <t>2026-10-19T13:10:40Z</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -5243,7 +5243,7 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
@@ -5297,12 +5297,12 @@
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:49Z</t>
+          <t>2026-10-19T13:10:40Z</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -5371,7 +5371,7 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:49Z</t>
+          <t>2026-10-19T13:10:40Z</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -5499,7 +5499,7 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
@@ -5553,12 +5553,12 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:49Z</t>
+          <t>2026-10-19T13:10:40Z</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -5627,7 +5627,7 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
@@ -5681,12 +5681,12 @@
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:49Z</t>
+          <t>2026-10-19T13:10:40Z</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -5755,7 +5755,7 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>-103</v>
+        <v>-104</v>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
@@ -5809,12 +5809,12 @@
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:49Z</t>
+          <t>2026-10-19T13:10:41Z</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -5883,7 +5883,7 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
@@ -5937,12 +5937,12 @@
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:49Z</t>
+          <t>2026-10-19T13:10:40Z</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -6011,7 +6011,7 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
@@ -6065,12 +6065,12 @@
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:49Z</t>
+          <t>2026-10-19T13:10:40Z</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -6139,7 +6139,7 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
@@ -6193,12 +6193,12 @@
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:50Z</t>
+          <t>2026-10-19T13:10:41Z</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -6267,7 +6267,7 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
@@ -6321,12 +6321,12 @@
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:49Z</t>
+          <t>2026-10-19T13:10:40Z</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -6395,7 +6395,7 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
@@ -6449,12 +6449,12 @@
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:49Z</t>
+          <t>2026-10-19T13:10:40Z</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -6523,7 +6523,7 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
@@ -6577,12 +6577,12 @@
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:49Z</t>
+          <t>2026-10-19T13:10:40Z</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -6651,7 +6651,7 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
@@ -6705,12 +6705,12 @@
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:49Z</t>
+          <t>2026-10-19T13:10:40Z</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -6779,7 +6779,7 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
@@ -6833,12 +6833,12 @@
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:49Z</t>
+          <t>2026-10-19T13:10:40Z</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
@@ -6961,12 +6961,12 @@
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:49Z</t>
+          <t>2026-10-19T13:10:40Z</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
@@ -7089,12 +7089,12 @@
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:49Z</t>
+          <t>2026-10-19T13:10:40Z</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -7163,7 +7163,7 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
@@ -7217,12 +7217,12 @@
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:49Z</t>
+          <t>2026-10-19T13:10:40Z</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -7291,7 +7291,7 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
@@ -7345,12 +7345,12 @@
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:50Z</t>
+          <t>2026-10-19T13:10:41Z</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -7419,7 +7419,7 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
@@ -7473,12 +7473,12 @@
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:49Z</t>
+          <t>2026-10-19T13:10:40Z</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -7547,7 +7547,7 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
@@ -7601,12 +7601,12 @@
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:49Z</t>
+          <t>2026-10-19T13:10:40Z</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -7675,7 +7675,7 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
@@ -7729,12 +7729,12 @@
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:49Z</t>
+          <t>2026-10-19T13:10:40Z</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
@@ -7857,12 +7857,12 @@
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:49Z</t>
+          <t>2026-10-19T13:10:40Z</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -7931,7 +7931,7 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
@@ -7985,12 +7985,12 @@
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:49Z</t>
+          <t>2026-10-19T13:10:40Z</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -8059,7 +8059,7 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
@@ -8113,12 +8113,12 @@
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:50Z</t>
+          <t>2026-10-19T13:10:41Z</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -8187,7 +8187,7 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
@@ -8241,12 +8241,12 @@
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:49Z</t>
+          <t>2026-10-19T13:10:40Z</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -8315,7 +8315,7 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
@@ -8369,12 +8369,12 @@
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:50Z</t>
+          <t>2026-10-19T13:10:41Z</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -8443,7 +8443,7 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
@@ -8497,12 +8497,12 @@
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:49Z</t>
+          <t>2026-10-19T13:10:40Z</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -8571,7 +8571,7 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
@@ -8625,12 +8625,12 @@
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:50Z</t>
+          <t>2026-10-19T13:10:41Z</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:49Z</t>
+          <t>2026-10-19T13:10:40Z</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -8827,7 +8827,7 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
@@ -8881,12 +8881,12 @@
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:49Z</t>
+          <t>2026-10-19T13:10:40Z</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -8955,7 +8955,7 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
@@ -9009,12 +9009,12 @@
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:49Z</t>
+          <t>2026-10-19T13:10:40Z</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -9083,7 +9083,7 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
@@ -9137,12 +9137,12 @@
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:50Z</t>
+          <t>2026-10-19T13:10:41Z</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -9211,7 +9211,7 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
@@ -9265,12 +9265,12 @@
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:49Z</t>
+          <t>2026-10-19T13:10:40Z</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -9339,7 +9339,7 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
@@ -9393,12 +9393,12 @@
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:49Z</t>
+          <t>2026-10-19T13:10:40Z</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -9467,7 +9467,7 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
@@ -9521,12 +9521,12 @@
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:50Z</t>
+          <t>2026-10-19T13:10:41Z</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -9595,7 +9595,7 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>-103</v>
+        <v>-104</v>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
@@ -9649,12 +9649,12 @@
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:49Z</t>
+          <t>2026-10-19T13:10:41Z</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -9723,7 +9723,7 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
@@ -9777,12 +9777,12 @@
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:49Z</t>
+          <t>2026-10-19T13:10:40Z</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -9851,7 +9851,7 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
@@ -9905,12 +9905,12 @@
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:49Z</t>
+          <t>2026-10-19T13:10:40Z</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -9979,7 +9979,7 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
@@ -10033,12 +10033,12 @@
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:49Z</t>
+          <t>2026-10-19T13:10:40Z</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -10107,7 +10107,7 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
@@ -10161,12 +10161,12 @@
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:49Z</t>
+          <t>2026-10-19T13:10:40Z</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -10235,7 +10235,7 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
@@ -10289,12 +10289,12 @@
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:49Z</t>
+          <t>2026-10-19T13:10:40Z</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -10363,7 +10363,7 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
@@ -10417,12 +10417,12 @@
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:49Z</t>
+          <t>2026-10-19T13:10:40Z</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -10491,7 +10491,7 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
@@ -10545,12 +10545,12 @@
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:49Z</t>
+          <t>2026-10-19T13:10:40Z</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -10619,7 +10619,7 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
@@ -10673,12 +10673,12 @@
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:50Z</t>
+          <t>2026-10-19T13:10:41Z</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -10747,7 +10747,7 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
@@ -10801,12 +10801,12 @@
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:50Z</t>
+          <t>2026-10-19T13:10:41Z</t>
         </is>
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -10875,7 +10875,7 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
@@ -10929,12 +10929,12 @@
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:50Z</t>
+          <t>2026-10-19T13:10:41Z</t>
         </is>
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -11003,7 +11003,7 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q83" t="inlineStr">
         <is>
@@ -11057,12 +11057,12 @@
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:49Z</t>
+          <t>2026-10-19T13:10:40Z</t>
         </is>
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -11131,7 +11131,7 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
@@ -11185,12 +11185,12 @@
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:50Z</t>
+          <t>2026-10-19T13:10:41Z</t>
         </is>
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -11259,7 +11259,7 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
@@ -11313,12 +11313,12 @@
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:49Z</t>
+          <t>2026-10-19T13:10:40Z</t>
         </is>
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -11387,7 +11387,7 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q86" t="inlineStr">
         <is>
@@ -11441,12 +11441,12 @@
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:50Z</t>
+          <t>2026-10-19T13:10:41Z</t>
         </is>
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -11515,7 +11515,7 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
@@ -11569,12 +11569,12 @@
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:50Z</t>
+          <t>2026-10-19T13:10:41Z</t>
         </is>
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -11643,7 +11643,7 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
@@ -11697,12 +11697,12 @@
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:49Z</t>
+          <t>2026-10-19T13:10:40Z</t>
         </is>
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -11771,7 +11771,7 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
@@ -11825,12 +11825,12 @@
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:49Z</t>
+          <t>2026-10-19T13:10:40Z</t>
         </is>
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -11899,7 +11899,7 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
@@ -11953,12 +11953,12 @@
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:49Z</t>
+          <t>2026-10-19T13:10:40Z</t>
         </is>
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -12027,7 +12027,7 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
@@ -12081,12 +12081,12 @@
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:49Z</t>
+          <t>2026-10-19T13:10:40Z</t>
         </is>
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -12155,7 +12155,7 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q92" t="inlineStr">
         <is>
@@ -12209,12 +12209,12 @@
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:49Z</t>
+          <t>2026-10-19T13:10:40Z</t>
         </is>
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -12283,7 +12283,7 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
@@ -12337,12 +12337,12 @@
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:49Z</t>
+          <t>2026-10-19T13:10:40Z</t>
         </is>
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -12411,7 +12411,7 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q94" t="inlineStr">
         <is>
@@ -12465,12 +12465,12 @@
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:49Z</t>
+          <t>2026-10-19T13:10:40Z</t>
         </is>
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -12539,7 +12539,7 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q95" t="inlineStr">
         <is>
@@ -12593,12 +12593,12 @@
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:49Z</t>
+          <t>2026-10-19T13:10:40Z</t>
         </is>
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -12667,7 +12667,7 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
@@ -12721,12 +12721,12 @@
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:49Z</t>
+          <t>2026-10-19T13:10:40Z</t>
         </is>
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -12795,7 +12795,7 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q97" t="inlineStr">
         <is>
@@ -12849,12 +12849,12 @@
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:49Z</t>
+          <t>2026-10-19T13:10:40Z</t>
         </is>
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -12923,7 +12923,7 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q98" t="inlineStr">
         <is>
@@ -12977,12 +12977,12 @@
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:49Z</t>
+          <t>2026-10-19T13:10:40Z</t>
         </is>
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -13051,7 +13051,7 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q99" t="inlineStr">
         <is>
@@ -13105,12 +13105,12 @@
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:49Z</t>
+          <t>2026-10-19T13:10:40Z</t>
         </is>
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -13179,7 +13179,7 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q100" t="inlineStr">
         <is>
@@ -13233,12 +13233,12 @@
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:49Z</t>
+          <t>2026-10-19T13:10:40Z</t>
         </is>
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -13307,7 +13307,7 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q101" t="inlineStr">
         <is>
@@ -13361,12 +13361,12 @@
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:49Z</t>
+          <t>2026-10-19T13:10:40Z</t>
         </is>
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -13435,7 +13435,7 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q102" t="inlineStr">
         <is>
@@ -13489,12 +13489,12 @@
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:50Z</t>
+          <t>2026-10-19T13:10:41Z</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -13563,7 +13563,7 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
@@ -13617,12 +13617,12 @@
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:49Z</t>
+          <t>2026-10-19T13:10:40Z</t>
         </is>
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -13691,7 +13691,7 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q104" t="inlineStr">
         <is>
@@ -13745,12 +13745,12 @@
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:49Z</t>
+          <t>2026-10-19T13:10:40Z</t>
         </is>
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -13819,7 +13819,7 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q105" t="inlineStr">
         <is>
@@ -13873,12 +13873,12 @@
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:49Z</t>
+          <t>2026-10-19T13:10:40Z</t>
         </is>
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -13947,7 +13947,7 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q106" t="inlineStr">
         <is>
@@ -14001,12 +14001,12 @@
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:49Z</t>
+          <t>2026-10-19T13:10:40Z</t>
         </is>
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -14075,7 +14075,7 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q107" t="inlineStr">
         <is>
@@ -14129,12 +14129,12 @@
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:49Z</t>
+          <t>2026-10-19T13:10:40Z</t>
         </is>
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -14203,7 +14203,7 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q108" t="inlineStr">
         <is>
@@ -14257,12 +14257,12 @@
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:49Z</t>
+          <t>2026-10-19T13:10:40Z</t>
         </is>
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -14331,7 +14331,7 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q109" t="inlineStr">
         <is>
@@ -14385,12 +14385,12 @@
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:49Z</t>
+          <t>2026-10-19T13:10:40Z</t>
         </is>
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -14459,7 +14459,7 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q110" t="inlineStr">
         <is>
@@ -14513,12 +14513,12 @@
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:49Z</t>
+          <t>2026-10-19T13:10:40Z</t>
         </is>
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -14587,7 +14587,7 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q111" t="inlineStr">
         <is>
@@ -14641,12 +14641,12 @@
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:50Z</t>
+          <t>2026-10-19T13:10:41Z</t>
         </is>
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -14715,7 +14715,7 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q112" t="inlineStr">
         <is>
@@ -14769,12 +14769,12 @@
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:49Z</t>
+          <t>2026-10-19T13:10:40Z</t>
         </is>
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -14843,7 +14843,7 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q113" t="inlineStr">
         <is>
@@ -14897,12 +14897,12 @@
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:49Z</t>
+          <t>2026-10-19T13:10:40Z</t>
         </is>
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -14971,7 +14971,7 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q114" t="inlineStr">
         <is>
@@ -15025,12 +15025,12 @@
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:49Z</t>
+          <t>2026-10-19T13:10:40Z</t>
         </is>
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -15099,7 +15099,7 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q115" t="inlineStr">
         <is>
@@ -15153,12 +15153,12 @@
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:49Z</t>
+          <t>2026-10-19T13:10:40Z</t>
         </is>
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -15227,7 +15227,7 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q116" t="inlineStr">
         <is>
@@ -15281,12 +15281,12 @@
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:49Z</t>
+          <t>2026-10-19T13:10:40Z</t>
         </is>
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>

--- a/exports/California_Surplus_Feed.xlsx
+++ b/exports/California_Surplus_Feed.xlsx
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -689,12 +689,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:41Z</t>
+          <t>2026-10-20T11:33:42Z</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -763,7 +763,7 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -817,12 +817,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:41Z</t>
+          <t>2026-10-20T11:33:42Z</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -945,12 +945,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:41Z</t>
+          <t>2026-10-20T11:33:42Z</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:41Z</t>
+          <t>2026-10-20T11:33:42Z</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -1147,7 +1147,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1201,12 +1201,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:40Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -1275,7 +1275,7 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:40Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -1403,7 +1403,7 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -1457,12 +1457,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:41Z</t>
+          <t>2026-10-20T11:33:42Z</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:41Z</t>
+          <t>2026-10-20T11:33:42Z</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>-104</v>
+        <v>-105</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -1713,12 +1713,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:41Z</t>
+          <t>2026-10-20T11:33:42Z</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -1787,7 +1787,7 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -1841,12 +1841,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:41Z</t>
+          <t>2026-10-20T11:33:42Z</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -1915,7 +1915,7 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -1969,12 +1969,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:41Z</t>
+          <t>2026-10-20T11:33:42Z</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -2043,7 +2043,7 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>-104</v>
+        <v>-105</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:41Z</t>
+          <t>2026-10-20T11:33:42Z</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -2225,12 +2225,12 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:41Z</t>
+          <t>2026-10-20T11:33:42Z</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -2299,7 +2299,7 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -2353,12 +2353,12 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:40Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -2427,7 +2427,7 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
@@ -2481,12 +2481,12 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:41Z</t>
+          <t>2026-10-20T11:33:42Z</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -2609,12 +2609,12 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:40Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>-104</v>
+        <v>-105</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -2737,12 +2737,12 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:41Z</t>
+          <t>2026-10-20T11:33:42Z</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2811,7 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -2865,12 +2865,12 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:40Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -2939,7 +2939,7 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>-104</v>
+        <v>-105</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -2993,12 +2993,12 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:41Z</t>
+          <t>2026-10-20T11:33:42Z</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -3067,7 +3067,7 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -3121,12 +3121,12 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:40Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -3195,7 +3195,7 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -3249,12 +3249,12 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:41Z</t>
+          <t>2026-10-20T11:33:42Z</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -3323,7 +3323,7 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -3377,12 +3377,12 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:40Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -3505,12 +3505,12 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:40Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -3579,7 +3579,7 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -3633,12 +3633,12 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:40Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -3707,7 +3707,7 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -3761,12 +3761,12 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:40Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -3835,7 +3835,7 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -3889,12 +3889,12 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:40Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -3963,7 +3963,7 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>-104</v>
+        <v>-105</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
@@ -4017,12 +4017,12 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:41Z</t>
+          <t>2026-10-20T11:33:42Z</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -4091,7 +4091,7 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
@@ -4145,12 +4145,12 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:41Z</t>
+          <t>2026-10-20T11:33:42Z</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -4219,7 +4219,7 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
@@ -4273,12 +4273,12 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:40Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
@@ -4401,12 +4401,12 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:41Z</t>
+          <t>2026-10-20T11:33:42Z</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -4475,7 +4475,7 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
@@ -4529,12 +4529,12 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:41Z</t>
+          <t>2026-10-20T11:33:42Z</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -4603,7 +4603,7 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
@@ -4657,12 +4657,12 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:41Z</t>
+          <t>2026-10-20T11:33:42Z</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
@@ -4785,12 +4785,12 @@
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:41Z</t>
+          <t>2026-10-20T11:33:42Z</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -4859,7 +4859,7 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
@@ -4913,12 +4913,12 @@
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:40Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -4987,7 +4987,7 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
@@ -5041,12 +5041,12 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:41Z</t>
+          <t>2026-10-20T11:33:42Z</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -5115,7 +5115,7 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:40Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -5243,7 +5243,7 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
@@ -5297,12 +5297,12 @@
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:40Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -5371,7 +5371,7 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:40Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -5499,7 +5499,7 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
@@ -5553,12 +5553,12 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:40Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -5627,7 +5627,7 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
@@ -5681,12 +5681,12 @@
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:40Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -5755,7 +5755,7 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>-104</v>
+        <v>-105</v>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
@@ -5809,12 +5809,12 @@
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:41Z</t>
+          <t>2026-10-20T11:33:42Z</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -5883,7 +5883,7 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
@@ -5937,12 +5937,12 @@
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:40Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -6011,7 +6011,7 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
@@ -6065,12 +6065,12 @@
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:40Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -6139,7 +6139,7 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
@@ -6193,12 +6193,12 @@
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:41Z</t>
+          <t>2026-10-20T11:33:42Z</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -6267,7 +6267,7 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
@@ -6321,12 +6321,12 @@
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:40Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -6395,7 +6395,7 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
@@ -6449,12 +6449,12 @@
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:40Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -6523,7 +6523,7 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
@@ -6577,12 +6577,12 @@
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:40Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -6651,7 +6651,7 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
@@ -6705,12 +6705,12 @@
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:40Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -6779,7 +6779,7 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
@@ -6833,12 +6833,12 @@
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:40Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
@@ -6961,12 +6961,12 @@
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:40Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
@@ -7089,12 +7089,12 @@
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:40Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -7163,7 +7163,7 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
@@ -7217,12 +7217,12 @@
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:40Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -7291,7 +7291,7 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
@@ -7345,12 +7345,12 @@
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:41Z</t>
+          <t>2026-10-20T11:33:42Z</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -7419,7 +7419,7 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
@@ -7473,12 +7473,12 @@
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:40Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -7547,7 +7547,7 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
@@ -7601,12 +7601,12 @@
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:40Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -7675,7 +7675,7 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
@@ -7729,12 +7729,12 @@
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:40Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
@@ -7857,12 +7857,12 @@
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:40Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -7931,7 +7931,7 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
@@ -7985,12 +7985,12 @@
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:40Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -8059,7 +8059,7 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
@@ -8113,12 +8113,12 @@
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:41Z</t>
+          <t>2026-10-20T11:33:42Z</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -8187,7 +8187,7 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
@@ -8241,12 +8241,12 @@
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:40Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -8315,7 +8315,7 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
@@ -8369,12 +8369,12 @@
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:41Z</t>
+          <t>2026-10-20T11:33:42Z</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -8443,7 +8443,7 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
@@ -8497,12 +8497,12 @@
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:40Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -8571,7 +8571,7 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
@@ -8625,12 +8625,12 @@
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:41Z</t>
+          <t>2026-10-20T11:33:42Z</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:40Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -8827,7 +8827,7 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
@@ -8881,12 +8881,12 @@
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:40Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -8955,7 +8955,7 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
@@ -9009,12 +9009,12 @@
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:40Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -9083,7 +9083,7 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
@@ -9137,12 +9137,12 @@
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:41Z</t>
+          <t>2026-10-20T11:33:42Z</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -9211,7 +9211,7 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
@@ -9265,12 +9265,12 @@
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:40Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -9339,7 +9339,7 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
@@ -9393,12 +9393,12 @@
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:40Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -9467,7 +9467,7 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
@@ -9521,12 +9521,12 @@
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:41Z</t>
+          <t>2026-10-20T11:33:42Z</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -9595,7 +9595,7 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>-104</v>
+        <v>-105</v>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
@@ -9649,12 +9649,12 @@
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:41Z</t>
+          <t>2026-10-20T11:33:42Z</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -9723,7 +9723,7 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
@@ -9777,12 +9777,12 @@
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:40Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -9851,7 +9851,7 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
@@ -9905,12 +9905,12 @@
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:40Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -9979,7 +9979,7 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
@@ -10033,12 +10033,12 @@
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:40Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -10107,7 +10107,7 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
@@ -10161,12 +10161,12 @@
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:40Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -10235,7 +10235,7 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
@@ -10289,12 +10289,12 @@
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:40Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -10363,7 +10363,7 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
@@ -10417,12 +10417,12 @@
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:40Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -10491,7 +10491,7 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
@@ -10545,12 +10545,12 @@
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:40Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -10619,7 +10619,7 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
@@ -10673,12 +10673,12 @@
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:41Z</t>
+          <t>2026-10-20T11:33:42Z</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -10747,7 +10747,7 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
@@ -10801,12 +10801,12 @@
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:41Z</t>
+          <t>2026-10-20T11:33:42Z</t>
         </is>
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -10875,7 +10875,7 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
@@ -10929,12 +10929,12 @@
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:41Z</t>
+          <t>2026-10-20T11:33:42Z</t>
         </is>
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -11003,7 +11003,7 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q83" t="inlineStr">
         <is>
@@ -11057,12 +11057,12 @@
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:40Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -11131,7 +11131,7 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
@@ -11185,12 +11185,12 @@
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:41Z</t>
+          <t>2026-10-20T11:33:42Z</t>
         </is>
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -11259,7 +11259,7 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
@@ -11313,12 +11313,12 @@
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:40Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -11387,7 +11387,7 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q86" t="inlineStr">
         <is>
@@ -11441,12 +11441,12 @@
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:41Z</t>
+          <t>2026-10-20T11:33:42Z</t>
         </is>
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -11515,7 +11515,7 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
@@ -11569,12 +11569,12 @@
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:41Z</t>
+          <t>2026-10-20T11:33:42Z</t>
         </is>
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -11643,7 +11643,7 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
@@ -11697,12 +11697,12 @@
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:40Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -11771,7 +11771,7 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
@@ -11825,12 +11825,12 @@
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:40Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -11899,7 +11899,7 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
@@ -11953,12 +11953,12 @@
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:40Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -12027,7 +12027,7 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
@@ -12081,12 +12081,12 @@
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:40Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -12155,7 +12155,7 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q92" t="inlineStr">
         <is>
@@ -12209,12 +12209,12 @@
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:40Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -12283,7 +12283,7 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
@@ -12337,12 +12337,12 @@
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:40Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -12411,7 +12411,7 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q94" t="inlineStr">
         <is>
@@ -12465,12 +12465,12 @@
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:40Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -12539,7 +12539,7 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q95" t="inlineStr">
         <is>
@@ -12593,12 +12593,12 @@
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:40Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -12667,7 +12667,7 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
@@ -12721,12 +12721,12 @@
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:40Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -12795,7 +12795,7 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q97" t="inlineStr">
         <is>
@@ -12849,12 +12849,12 @@
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:40Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -12923,7 +12923,7 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q98" t="inlineStr">
         <is>
@@ -12977,12 +12977,12 @@
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:40Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -13051,7 +13051,7 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q99" t="inlineStr">
         <is>
@@ -13105,12 +13105,12 @@
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:40Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -13179,7 +13179,7 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q100" t="inlineStr">
         <is>
@@ -13233,12 +13233,12 @@
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:40Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -13307,7 +13307,7 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q101" t="inlineStr">
         <is>
@@ -13361,12 +13361,12 @@
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:40Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -13435,7 +13435,7 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q102" t="inlineStr">
         <is>
@@ -13489,12 +13489,12 @@
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:41Z</t>
+          <t>2026-10-20T11:33:42Z</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -13563,7 +13563,7 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
@@ -13617,12 +13617,12 @@
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:40Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -13691,7 +13691,7 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q104" t="inlineStr">
         <is>
@@ -13745,12 +13745,12 @@
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:40Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -13819,7 +13819,7 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q105" t="inlineStr">
         <is>
@@ -13873,12 +13873,12 @@
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:40Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -13947,7 +13947,7 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q106" t="inlineStr">
         <is>
@@ -14001,12 +14001,12 @@
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:40Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -14075,7 +14075,7 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q107" t="inlineStr">
         <is>
@@ -14129,12 +14129,12 @@
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:40Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -14203,7 +14203,7 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q108" t="inlineStr">
         <is>
@@ -14257,12 +14257,12 @@
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:40Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -14331,7 +14331,7 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q109" t="inlineStr">
         <is>
@@ -14385,12 +14385,12 @@
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:40Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -14459,7 +14459,7 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q110" t="inlineStr">
         <is>
@@ -14513,12 +14513,12 @@
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:40Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -14587,7 +14587,7 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q111" t="inlineStr">
         <is>
@@ -14641,12 +14641,12 @@
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:41Z</t>
+          <t>2026-10-20T11:33:42Z</t>
         </is>
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -14715,7 +14715,7 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q112" t="inlineStr">
         <is>
@@ -14769,12 +14769,12 @@
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:40Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -14843,7 +14843,7 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q113" t="inlineStr">
         <is>
@@ -14897,12 +14897,12 @@
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:40Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -14971,7 +14971,7 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q114" t="inlineStr">
         <is>
@@ -15025,12 +15025,12 @@
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:40Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -15099,7 +15099,7 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q115" t="inlineStr">
         <is>
@@ -15153,12 +15153,12 @@
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:40Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -15227,7 +15227,7 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q116" t="inlineStr">
         <is>
@@ -15281,12 +15281,12 @@
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:40Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>

--- a/exports/California_Surplus_Feed.xlsx
+++ b/exports/California_Surplus_Feed.xlsx
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -689,12 +689,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:42Z</t>
+          <t>2026-10-21T11:46:22Z</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -763,7 +763,7 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -817,12 +817,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:42Z</t>
+          <t>2026-10-21T11:46:22Z</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -945,12 +945,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:42Z</t>
+          <t>2026-10-21T11:46:22Z</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:42Z</t>
+          <t>2026-10-21T11:46:22Z</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -1147,7 +1147,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1201,12 +1201,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:40Z</t>
+          <t>2026-10-21T11:46:20Z</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -1275,7 +1275,7 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:40Z</t>
+          <t>2026-10-21T11:46:20Z</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -1403,7 +1403,7 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -1457,12 +1457,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:42Z</t>
+          <t>2026-10-21T11:46:22Z</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:42Z</t>
+          <t>2026-10-21T11:46:22Z</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>-105</v>
+        <v>-106</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -1713,12 +1713,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:42Z</t>
+          <t>2026-10-21T11:46:21Z</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -1787,7 +1787,7 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -1841,12 +1841,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:42Z</t>
+          <t>2026-10-21T11:46:22Z</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -1915,7 +1915,7 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -1969,12 +1969,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:42Z</t>
+          <t>2026-10-21T11:46:22Z</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -2043,7 +2043,7 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>-105</v>
+        <v>-106</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:42Z</t>
+          <t>2026-10-21T11:46:21Z</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -2225,12 +2225,12 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:42Z</t>
+          <t>2026-10-21T11:46:22Z</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -2299,7 +2299,7 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -2353,12 +2353,12 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:40Z</t>
+          <t>2026-10-21T11:46:20Z</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -2427,7 +2427,7 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
@@ -2481,12 +2481,12 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:42Z</t>
+          <t>2026-10-21T11:46:22Z</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -2609,12 +2609,12 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:40Z</t>
+          <t>2026-10-21T11:46:20Z</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>-105</v>
+        <v>-106</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -2737,12 +2737,12 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:42Z</t>
+          <t>2026-10-21T11:46:21Z</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2811,7 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -2865,12 +2865,12 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:40Z</t>
+          <t>2026-10-21T11:46:20Z</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -2939,7 +2939,7 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>-105</v>
+        <v>-106</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -2993,12 +2993,12 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:42Z</t>
+          <t>2026-10-21T11:46:21Z</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -3067,7 +3067,7 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -3121,12 +3121,12 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:40Z</t>
+          <t>2026-10-21T11:46:20Z</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -3195,7 +3195,7 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -3249,12 +3249,12 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:42Z</t>
+          <t>2026-10-21T11:46:22Z</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -3323,7 +3323,7 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -3377,12 +3377,12 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:40Z</t>
+          <t>2026-10-21T11:46:20Z</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -3505,12 +3505,12 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:40Z</t>
+          <t>2026-10-21T11:46:20Z</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -3579,7 +3579,7 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -3633,12 +3633,12 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:40Z</t>
+          <t>2026-10-21T11:46:20Z</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -3707,7 +3707,7 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -3761,12 +3761,12 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:40Z</t>
+          <t>2026-10-21T11:46:20Z</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -3835,7 +3835,7 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -3889,12 +3889,12 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:40Z</t>
+          <t>2026-10-21T11:46:20Z</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -3963,7 +3963,7 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>-105</v>
+        <v>-106</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
@@ -4017,12 +4017,12 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:42Z</t>
+          <t>2026-10-21T11:46:21Z</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -4091,7 +4091,7 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
@@ -4145,12 +4145,12 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:42Z</t>
+          <t>2026-10-21T11:46:22Z</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -4219,7 +4219,7 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
@@ -4273,12 +4273,12 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:40Z</t>
+          <t>2026-10-21T11:46:20Z</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
@@ -4401,12 +4401,12 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:42Z</t>
+          <t>2026-10-21T11:46:22Z</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -4475,7 +4475,7 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
@@ -4529,12 +4529,12 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:42Z</t>
+          <t>2026-10-21T11:46:22Z</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -4603,7 +4603,7 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
@@ -4657,12 +4657,12 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:42Z</t>
+          <t>2026-10-21T11:46:22Z</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
@@ -4785,12 +4785,12 @@
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:42Z</t>
+          <t>2026-10-21T11:46:22Z</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -4859,7 +4859,7 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
@@ -4913,12 +4913,12 @@
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:40Z</t>
+          <t>2026-10-21T11:46:20Z</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -4987,7 +4987,7 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
@@ -5041,12 +5041,12 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:42Z</t>
+          <t>2026-10-21T11:46:22Z</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -5115,7 +5115,7 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:40Z</t>
+          <t>2026-10-21T11:46:20Z</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -5243,7 +5243,7 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
@@ -5297,12 +5297,12 @@
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:40Z</t>
+          <t>2026-10-21T11:46:20Z</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -5371,7 +5371,7 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:40Z</t>
+          <t>2026-10-21T11:46:20Z</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -5499,7 +5499,7 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
@@ -5553,12 +5553,12 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:40Z</t>
+          <t>2026-10-21T11:46:20Z</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -5627,7 +5627,7 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
@@ -5681,12 +5681,12 @@
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:40Z</t>
+          <t>2026-10-21T11:46:20Z</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -5755,7 +5755,7 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>-105</v>
+        <v>-106</v>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
@@ -5809,12 +5809,12 @@
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:42Z</t>
+          <t>2026-10-21T11:46:21Z</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -5883,7 +5883,7 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
@@ -5937,12 +5937,12 @@
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:40Z</t>
+          <t>2026-10-21T11:46:20Z</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -6011,7 +6011,7 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
@@ -6065,12 +6065,12 @@
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:40Z</t>
+          <t>2026-10-21T11:46:20Z</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -6139,7 +6139,7 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
@@ -6193,12 +6193,12 @@
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:42Z</t>
+          <t>2026-10-21T11:46:22Z</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -6267,7 +6267,7 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
@@ -6321,12 +6321,12 @@
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:40Z</t>
+          <t>2026-10-21T11:46:20Z</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -6395,7 +6395,7 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
@@ -6449,12 +6449,12 @@
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:40Z</t>
+          <t>2026-10-21T11:46:20Z</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -6523,7 +6523,7 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
@@ -6577,12 +6577,12 @@
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:40Z</t>
+          <t>2026-10-21T11:46:20Z</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -6651,7 +6651,7 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
@@ -6705,12 +6705,12 @@
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:40Z</t>
+          <t>2026-10-21T11:46:20Z</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -6779,7 +6779,7 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
@@ -6833,12 +6833,12 @@
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:40Z</t>
+          <t>2026-10-21T11:46:20Z</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
@@ -6961,12 +6961,12 @@
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:40Z</t>
+          <t>2026-10-21T11:46:20Z</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
@@ -7089,12 +7089,12 @@
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:40Z</t>
+          <t>2026-10-21T11:46:20Z</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -7163,7 +7163,7 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
@@ -7217,12 +7217,12 @@
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:40Z</t>
+          <t>2026-10-21T11:46:20Z</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -7291,7 +7291,7 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
@@ -7345,12 +7345,12 @@
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:42Z</t>
+          <t>2026-10-21T11:46:22Z</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -7419,7 +7419,7 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
@@ -7473,12 +7473,12 @@
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:40Z</t>
+          <t>2026-10-21T11:46:20Z</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -7547,7 +7547,7 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
@@ -7601,12 +7601,12 @@
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:40Z</t>
+          <t>2026-10-21T11:46:20Z</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -7675,7 +7675,7 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
@@ -7729,12 +7729,12 @@
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:40Z</t>
+          <t>2026-10-21T11:46:20Z</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
@@ -7857,12 +7857,12 @@
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:40Z</t>
+          <t>2026-10-21T11:46:20Z</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -7931,7 +7931,7 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
@@ -7985,12 +7985,12 @@
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:40Z</t>
+          <t>2026-10-21T11:46:20Z</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -8059,7 +8059,7 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
@@ -8113,12 +8113,12 @@
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:42Z</t>
+          <t>2026-10-21T11:46:22Z</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -8187,7 +8187,7 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
@@ -8241,12 +8241,12 @@
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:40Z</t>
+          <t>2026-10-21T11:46:20Z</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -8315,7 +8315,7 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
@@ -8369,12 +8369,12 @@
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:42Z</t>
+          <t>2026-10-21T11:46:22Z</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -8443,7 +8443,7 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
@@ -8497,12 +8497,12 @@
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:40Z</t>
+          <t>2026-10-21T11:46:20Z</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -8571,7 +8571,7 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
@@ -8625,12 +8625,12 @@
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:42Z</t>
+          <t>2026-10-21T11:46:22Z</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:40Z</t>
+          <t>2026-10-21T11:46:20Z</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -8827,7 +8827,7 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
@@ -8881,12 +8881,12 @@
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:40Z</t>
+          <t>2026-10-21T11:46:20Z</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -8955,7 +8955,7 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
@@ -9009,12 +9009,12 @@
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:40Z</t>
+          <t>2026-10-21T11:46:20Z</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -9083,7 +9083,7 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
@@ -9137,12 +9137,12 @@
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:42Z</t>
+          <t>2026-10-21T11:46:22Z</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -9211,7 +9211,7 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
@@ -9265,12 +9265,12 @@
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:40Z</t>
+          <t>2026-10-21T11:46:20Z</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -9339,7 +9339,7 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
@@ -9393,12 +9393,12 @@
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:40Z</t>
+          <t>2026-10-21T11:46:20Z</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -9467,7 +9467,7 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
@@ -9521,12 +9521,12 @@
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:42Z</t>
+          <t>2026-10-21T11:46:22Z</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -9595,7 +9595,7 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>-105</v>
+        <v>-106</v>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
@@ -9649,12 +9649,12 @@
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:42Z</t>
+          <t>2026-10-21T11:46:21Z</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -9723,7 +9723,7 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
@@ -9777,12 +9777,12 @@
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:40Z</t>
+          <t>2026-10-21T11:46:20Z</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -9851,7 +9851,7 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
@@ -9905,12 +9905,12 @@
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:40Z</t>
+          <t>2026-10-21T11:46:20Z</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -9979,7 +9979,7 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
@@ -10033,12 +10033,12 @@
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:40Z</t>
+          <t>2026-10-21T11:46:20Z</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -10107,7 +10107,7 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
@@ -10161,12 +10161,12 @@
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:40Z</t>
+          <t>2026-10-21T11:46:20Z</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -10235,7 +10235,7 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
@@ -10289,12 +10289,12 @@
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:40Z</t>
+          <t>2026-10-21T11:46:20Z</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -10363,7 +10363,7 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
@@ -10417,12 +10417,12 @@
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:40Z</t>
+          <t>2026-10-21T11:46:20Z</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -10491,7 +10491,7 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
@@ -10545,12 +10545,12 @@
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:40Z</t>
+          <t>2026-10-21T11:46:20Z</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -10619,7 +10619,7 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
@@ -10673,12 +10673,12 @@
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:42Z</t>
+          <t>2026-10-21T11:46:22Z</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -10747,7 +10747,7 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
@@ -10801,12 +10801,12 @@
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:42Z</t>
+          <t>2026-10-21T11:46:22Z</t>
         </is>
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -10875,7 +10875,7 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
@@ -10929,12 +10929,12 @@
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:42Z</t>
+          <t>2026-10-21T11:46:22Z</t>
         </is>
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -11003,7 +11003,7 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q83" t="inlineStr">
         <is>
@@ -11057,12 +11057,12 @@
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:40Z</t>
+          <t>2026-10-21T11:46:20Z</t>
         </is>
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -11131,7 +11131,7 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
@@ -11185,12 +11185,12 @@
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:42Z</t>
+          <t>2026-10-21T11:46:22Z</t>
         </is>
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -11259,11 +11259,11 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>Tier 1: High Urgency (&lt; 45 Days)</t>
+          <t>Statutory window may have passed — confirm with clerk</t>
         </is>
       </c>
       <c r="R85" t="inlineStr">
@@ -11313,12 +11313,12 @@
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:40Z</t>
+          <t>2026-10-21T11:46:20Z</t>
         </is>
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -11387,7 +11387,7 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q86" t="inlineStr">
         <is>
@@ -11441,12 +11441,12 @@
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:42Z</t>
+          <t>2026-10-21T11:46:22Z</t>
         </is>
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -11515,7 +11515,7 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
@@ -11569,12 +11569,12 @@
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:42Z</t>
+          <t>2026-10-21T11:46:22Z</t>
         </is>
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -11643,7 +11643,7 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
@@ -11697,12 +11697,12 @@
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:40Z</t>
+          <t>2026-10-21T11:46:20Z</t>
         </is>
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -11771,7 +11771,7 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
@@ -11825,12 +11825,12 @@
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:40Z</t>
+          <t>2026-10-21T11:46:20Z</t>
         </is>
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -11899,7 +11899,7 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
@@ -11953,12 +11953,12 @@
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:40Z</t>
+          <t>2026-10-21T11:46:20Z</t>
         </is>
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -12027,7 +12027,7 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
@@ -12081,12 +12081,12 @@
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:40Z</t>
+          <t>2026-10-21T11:46:20Z</t>
         </is>
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -12155,7 +12155,7 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q92" t="inlineStr">
         <is>
@@ -12209,12 +12209,12 @@
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:40Z</t>
+          <t>2026-10-21T11:46:20Z</t>
         </is>
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -12283,7 +12283,7 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
@@ -12337,12 +12337,12 @@
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:40Z</t>
+          <t>2026-10-21T11:46:20Z</t>
         </is>
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -12411,7 +12411,7 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q94" t="inlineStr">
         <is>
@@ -12465,12 +12465,12 @@
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:40Z</t>
+          <t>2026-10-21T11:46:20Z</t>
         </is>
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -12539,7 +12539,7 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q95" t="inlineStr">
         <is>
@@ -12593,12 +12593,12 @@
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:40Z</t>
+          <t>2026-10-21T11:46:20Z</t>
         </is>
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -12667,7 +12667,7 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
@@ -12721,12 +12721,12 @@
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:40Z</t>
+          <t>2026-10-21T11:46:20Z</t>
         </is>
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -12795,7 +12795,7 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q97" t="inlineStr">
         <is>
@@ -12849,12 +12849,12 @@
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:40Z</t>
+          <t>2026-10-21T11:46:20Z</t>
         </is>
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -12923,7 +12923,7 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q98" t="inlineStr">
         <is>
@@ -12977,12 +12977,12 @@
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:40Z</t>
+          <t>2026-10-21T11:46:20Z</t>
         </is>
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -13051,7 +13051,7 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q99" t="inlineStr">
         <is>
@@ -13105,12 +13105,12 @@
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:40Z</t>
+          <t>2026-10-21T11:46:20Z</t>
         </is>
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -13179,7 +13179,7 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q100" t="inlineStr">
         <is>
@@ -13233,12 +13233,12 @@
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:40Z</t>
+          <t>2026-10-21T11:46:20Z</t>
         </is>
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -13307,7 +13307,7 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q101" t="inlineStr">
         <is>
@@ -13361,12 +13361,12 @@
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:40Z</t>
+          <t>2026-10-21T11:46:20Z</t>
         </is>
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -13435,7 +13435,7 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q102" t="inlineStr">
         <is>
@@ -13489,12 +13489,12 @@
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:42Z</t>
+          <t>2026-10-21T11:46:22Z</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -13563,7 +13563,7 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
@@ -13617,12 +13617,12 @@
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:40Z</t>
+          <t>2026-10-21T11:46:20Z</t>
         </is>
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -13691,7 +13691,7 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q104" t="inlineStr">
         <is>
@@ -13745,12 +13745,12 @@
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:40Z</t>
+          <t>2026-10-21T11:46:20Z</t>
         </is>
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -13819,7 +13819,7 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q105" t="inlineStr">
         <is>
@@ -13873,12 +13873,12 @@
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:40Z</t>
+          <t>2026-10-21T11:46:20Z</t>
         </is>
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -13947,7 +13947,7 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q106" t="inlineStr">
         <is>
@@ -14001,12 +14001,12 @@
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:40Z</t>
+          <t>2026-10-21T11:46:20Z</t>
         </is>
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -14075,7 +14075,7 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q107" t="inlineStr">
         <is>
@@ -14129,12 +14129,12 @@
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:40Z</t>
+          <t>2026-10-21T11:46:20Z</t>
         </is>
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -14203,7 +14203,7 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q108" t="inlineStr">
         <is>
@@ -14257,12 +14257,12 @@
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:40Z</t>
+          <t>2026-10-21T11:46:20Z</t>
         </is>
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -14331,7 +14331,7 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q109" t="inlineStr">
         <is>
@@ -14385,12 +14385,12 @@
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:40Z</t>
+          <t>2026-10-21T11:46:20Z</t>
         </is>
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -14459,11 +14459,11 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="Q110" t="inlineStr">
         <is>
-          <t>Tier 1: High Urgency (&lt; 45 Days)</t>
+          <t>Statutory window may have passed — confirm with clerk</t>
         </is>
       </c>
       <c r="R110" t="inlineStr">
@@ -14513,12 +14513,12 @@
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:40Z</t>
+          <t>2026-10-21T11:46:20Z</t>
         </is>
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -14587,7 +14587,7 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q111" t="inlineStr">
         <is>
@@ -14641,12 +14641,12 @@
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:42Z</t>
+          <t>2026-10-21T11:46:22Z</t>
         </is>
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -14715,7 +14715,7 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q112" t="inlineStr">
         <is>
@@ -14769,12 +14769,12 @@
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:40Z</t>
+          <t>2026-10-21T11:46:20Z</t>
         </is>
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -14843,7 +14843,7 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q113" t="inlineStr">
         <is>
@@ -14897,12 +14897,12 @@
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:40Z</t>
+          <t>2026-10-21T11:46:20Z</t>
         </is>
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -14971,7 +14971,7 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q114" t="inlineStr">
         <is>
@@ -15025,12 +15025,12 @@
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:40Z</t>
+          <t>2026-10-21T11:46:20Z</t>
         </is>
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -15099,7 +15099,7 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q115" t="inlineStr">
         <is>
@@ -15153,12 +15153,12 @@
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:40Z</t>
+          <t>2026-10-21T11:46:20Z</t>
         </is>
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -15227,7 +15227,7 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q116" t="inlineStr">
         <is>
@@ -15281,12 +15281,12 @@
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:40Z</t>
+          <t>2026-10-21T11:46:20Z</t>
         </is>
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>

--- a/exports/California_Surplus_Feed.xlsx
+++ b/exports/California_Surplus_Feed.xlsx
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -689,12 +689,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:22Z</t>
+          <t>2026-10-20T11:33:42Z</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -763,7 +763,7 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -817,12 +817,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:22Z</t>
+          <t>2026-10-20T11:33:42Z</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -945,12 +945,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:22Z</t>
+          <t>2026-10-20T11:33:42Z</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:22Z</t>
+          <t>2026-10-20T11:33:42Z</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -1147,7 +1147,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1201,12 +1201,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:20Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -1275,7 +1275,7 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:20Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -1403,7 +1403,7 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -1457,12 +1457,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:22Z</t>
+          <t>2026-10-20T11:33:42Z</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:22Z</t>
+          <t>2026-10-20T11:33:42Z</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>-106</v>
+        <v>-105</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -1713,12 +1713,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:21Z</t>
+          <t>2026-10-20T11:33:42Z</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -1787,7 +1787,7 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -1841,12 +1841,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:22Z</t>
+          <t>2026-10-20T11:33:42Z</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -1915,7 +1915,7 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -1969,12 +1969,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:22Z</t>
+          <t>2026-10-20T11:33:42Z</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -2043,7 +2043,7 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>-106</v>
+        <v>-105</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:21Z</t>
+          <t>2026-10-20T11:33:42Z</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -2225,12 +2225,12 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:22Z</t>
+          <t>2026-10-20T11:33:42Z</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -2299,7 +2299,7 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -2353,12 +2353,12 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:20Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -2427,7 +2427,7 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
@@ -2481,12 +2481,12 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:22Z</t>
+          <t>2026-10-20T11:33:42Z</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -2609,12 +2609,12 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:20Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>-106</v>
+        <v>-105</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -2737,12 +2737,12 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:21Z</t>
+          <t>2026-10-20T11:33:42Z</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2811,7 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -2865,12 +2865,12 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:20Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -2939,7 +2939,7 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>-106</v>
+        <v>-105</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -2993,12 +2993,12 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:21Z</t>
+          <t>2026-10-20T11:33:42Z</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -3067,7 +3067,7 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -3121,12 +3121,12 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:20Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -3195,7 +3195,7 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -3249,12 +3249,12 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:22Z</t>
+          <t>2026-10-20T11:33:42Z</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -3323,7 +3323,7 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -3377,12 +3377,12 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:20Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -3505,12 +3505,12 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:20Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -3579,7 +3579,7 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -3633,12 +3633,12 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:20Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -3707,7 +3707,7 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -3761,12 +3761,12 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:20Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -3835,7 +3835,7 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -3889,12 +3889,12 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:20Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -3963,7 +3963,7 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>-106</v>
+        <v>-105</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
@@ -4017,12 +4017,12 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:21Z</t>
+          <t>2026-10-20T11:33:42Z</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -4091,7 +4091,7 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
@@ -4145,12 +4145,12 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:22Z</t>
+          <t>2026-10-20T11:33:42Z</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -4219,7 +4219,7 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
@@ -4273,12 +4273,12 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:20Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
@@ -4401,12 +4401,12 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:22Z</t>
+          <t>2026-10-20T11:33:42Z</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -4475,7 +4475,7 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
@@ -4529,12 +4529,12 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:22Z</t>
+          <t>2026-10-20T11:33:42Z</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -4603,7 +4603,7 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
@@ -4657,12 +4657,12 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:22Z</t>
+          <t>2026-10-20T11:33:42Z</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
@@ -4785,12 +4785,12 @@
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:22Z</t>
+          <t>2026-10-20T11:33:42Z</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -4859,7 +4859,7 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
@@ -4913,12 +4913,12 @@
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:20Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -4987,7 +4987,7 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
@@ -5041,12 +5041,12 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:22Z</t>
+          <t>2026-10-20T11:33:42Z</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -5115,7 +5115,7 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:20Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -5243,7 +5243,7 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
@@ -5297,12 +5297,12 @@
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:20Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -5371,7 +5371,7 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:20Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -5499,7 +5499,7 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
@@ -5553,12 +5553,12 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:20Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -5627,7 +5627,7 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
@@ -5681,12 +5681,12 @@
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:20Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -5755,7 +5755,7 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>-106</v>
+        <v>-105</v>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
@@ -5809,12 +5809,12 @@
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:21Z</t>
+          <t>2026-10-20T11:33:42Z</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -5883,7 +5883,7 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
@@ -5937,12 +5937,12 @@
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:20Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -6011,7 +6011,7 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
@@ -6065,12 +6065,12 @@
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:20Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -6139,7 +6139,7 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
@@ -6193,12 +6193,12 @@
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:22Z</t>
+          <t>2026-10-20T11:33:42Z</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -6267,7 +6267,7 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
@@ -6321,12 +6321,12 @@
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:20Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -6395,7 +6395,7 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
@@ -6449,12 +6449,12 @@
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:20Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -6523,7 +6523,7 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
@@ -6577,12 +6577,12 @@
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:20Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -6651,7 +6651,7 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
@@ -6705,12 +6705,12 @@
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:20Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -6779,7 +6779,7 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
@@ -6833,12 +6833,12 @@
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:20Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
@@ -6961,12 +6961,12 @@
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:20Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
@@ -7089,12 +7089,12 @@
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:20Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -7163,7 +7163,7 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
@@ -7217,12 +7217,12 @@
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:20Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -7291,7 +7291,7 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
@@ -7345,12 +7345,12 @@
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:22Z</t>
+          <t>2026-10-20T11:33:42Z</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -7419,7 +7419,7 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
@@ -7473,12 +7473,12 @@
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:20Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -7547,7 +7547,7 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
@@ -7601,12 +7601,12 @@
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:20Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -7675,7 +7675,7 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
@@ -7729,12 +7729,12 @@
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:20Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
@@ -7857,12 +7857,12 @@
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:20Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -7931,7 +7931,7 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
@@ -7985,12 +7985,12 @@
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:20Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -8059,7 +8059,7 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
@@ -8113,12 +8113,12 @@
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:22Z</t>
+          <t>2026-10-20T11:33:42Z</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -8187,7 +8187,7 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
@@ -8241,12 +8241,12 @@
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:20Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -8315,7 +8315,7 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
@@ -8369,12 +8369,12 @@
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:22Z</t>
+          <t>2026-10-20T11:33:42Z</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -8443,7 +8443,7 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
@@ -8497,12 +8497,12 @@
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:20Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -8571,7 +8571,7 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
@@ -8625,12 +8625,12 @@
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:22Z</t>
+          <t>2026-10-20T11:33:42Z</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:20Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -8827,7 +8827,7 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
@@ -8881,12 +8881,12 @@
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:20Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -8955,7 +8955,7 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
@@ -9009,12 +9009,12 @@
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:20Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -9083,7 +9083,7 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
@@ -9137,12 +9137,12 @@
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:22Z</t>
+          <t>2026-10-20T11:33:42Z</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -9211,7 +9211,7 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
@@ -9265,12 +9265,12 @@
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:20Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -9339,7 +9339,7 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
@@ -9393,12 +9393,12 @@
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:20Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -9467,7 +9467,7 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
@@ -9521,12 +9521,12 @@
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:22Z</t>
+          <t>2026-10-20T11:33:42Z</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -9595,7 +9595,7 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>-106</v>
+        <v>-105</v>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
@@ -9649,12 +9649,12 @@
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:21Z</t>
+          <t>2026-10-20T11:33:42Z</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -9723,7 +9723,7 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
@@ -9777,12 +9777,12 @@
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:20Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -9851,7 +9851,7 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
@@ -9905,12 +9905,12 @@
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:20Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -9979,7 +9979,7 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
@@ -10033,12 +10033,12 @@
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:20Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -10107,7 +10107,7 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
@@ -10161,12 +10161,12 @@
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:20Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -10235,7 +10235,7 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
@@ -10289,12 +10289,12 @@
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:20Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -10363,7 +10363,7 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
@@ -10417,12 +10417,12 @@
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:20Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -10491,7 +10491,7 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
@@ -10545,12 +10545,12 @@
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:20Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -10619,7 +10619,7 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
@@ -10673,12 +10673,12 @@
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:22Z</t>
+          <t>2026-10-20T11:33:42Z</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -10747,7 +10747,7 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
@@ -10801,12 +10801,12 @@
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:22Z</t>
+          <t>2026-10-20T11:33:42Z</t>
         </is>
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -10875,7 +10875,7 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
@@ -10929,12 +10929,12 @@
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:22Z</t>
+          <t>2026-10-20T11:33:42Z</t>
         </is>
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -11003,7 +11003,7 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q83" t="inlineStr">
         <is>
@@ -11057,12 +11057,12 @@
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:20Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -11131,7 +11131,7 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
@@ -11185,12 +11185,12 @@
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:22Z</t>
+          <t>2026-10-20T11:33:42Z</t>
         </is>
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -11259,11 +11259,11 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>Statutory window may have passed — confirm with clerk</t>
+          <t>Tier 1: High Urgency (&lt; 45 Days)</t>
         </is>
       </c>
       <c r="R85" t="inlineStr">
@@ -11313,12 +11313,12 @@
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:20Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -11387,7 +11387,7 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q86" t="inlineStr">
         <is>
@@ -11441,12 +11441,12 @@
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:22Z</t>
+          <t>2026-10-20T11:33:42Z</t>
         </is>
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -11515,7 +11515,7 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
@@ -11569,12 +11569,12 @@
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:22Z</t>
+          <t>2026-10-20T11:33:42Z</t>
         </is>
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -11643,7 +11643,7 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
@@ -11697,12 +11697,12 @@
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:20Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -11771,7 +11771,7 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
@@ -11825,12 +11825,12 @@
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:20Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -11899,7 +11899,7 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
@@ -11953,12 +11953,12 @@
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:20Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -12027,7 +12027,7 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
@@ -12081,12 +12081,12 @@
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:20Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -12155,7 +12155,7 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q92" t="inlineStr">
         <is>
@@ -12209,12 +12209,12 @@
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:20Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -12283,7 +12283,7 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
@@ -12337,12 +12337,12 @@
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:20Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -12411,7 +12411,7 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q94" t="inlineStr">
         <is>
@@ -12465,12 +12465,12 @@
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:20Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -12539,7 +12539,7 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q95" t="inlineStr">
         <is>
@@ -12593,12 +12593,12 @@
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:20Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -12667,7 +12667,7 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
@@ -12721,12 +12721,12 @@
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:20Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -12795,7 +12795,7 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q97" t="inlineStr">
         <is>
@@ -12849,12 +12849,12 @@
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:20Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -12923,7 +12923,7 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q98" t="inlineStr">
         <is>
@@ -12977,12 +12977,12 @@
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:20Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -13051,7 +13051,7 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q99" t="inlineStr">
         <is>
@@ -13105,12 +13105,12 @@
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:20Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -13179,7 +13179,7 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q100" t="inlineStr">
         <is>
@@ -13233,12 +13233,12 @@
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:20Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -13307,7 +13307,7 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q101" t="inlineStr">
         <is>
@@ -13361,12 +13361,12 @@
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:20Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -13435,7 +13435,7 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q102" t="inlineStr">
         <is>
@@ -13489,12 +13489,12 @@
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:22Z</t>
+          <t>2026-10-20T11:33:42Z</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -13563,7 +13563,7 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
@@ -13617,12 +13617,12 @@
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:20Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -13691,7 +13691,7 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q104" t="inlineStr">
         <is>
@@ -13745,12 +13745,12 @@
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:20Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -13819,7 +13819,7 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q105" t="inlineStr">
         <is>
@@ -13873,12 +13873,12 @@
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:20Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -13947,7 +13947,7 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q106" t="inlineStr">
         <is>
@@ -14001,12 +14001,12 @@
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:20Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -14075,7 +14075,7 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q107" t="inlineStr">
         <is>
@@ -14129,12 +14129,12 @@
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:20Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -14203,7 +14203,7 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q108" t="inlineStr">
         <is>
@@ -14257,12 +14257,12 @@
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:20Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -14331,7 +14331,7 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q109" t="inlineStr">
         <is>
@@ -14385,12 +14385,12 @@
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:20Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -14459,11 +14459,11 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Q110" t="inlineStr">
         <is>
-          <t>Statutory window may have passed — confirm with clerk</t>
+          <t>Tier 1: High Urgency (&lt; 45 Days)</t>
         </is>
       </c>
       <c r="R110" t="inlineStr">
@@ -14513,12 +14513,12 @@
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:20Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -14587,7 +14587,7 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q111" t="inlineStr">
         <is>
@@ -14641,12 +14641,12 @@
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:22Z</t>
+          <t>2026-10-20T11:33:42Z</t>
         </is>
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -14715,7 +14715,7 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q112" t="inlineStr">
         <is>
@@ -14769,12 +14769,12 @@
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:20Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -14843,7 +14843,7 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q113" t="inlineStr">
         <is>
@@ -14897,12 +14897,12 @@
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:20Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -14971,7 +14971,7 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q114" t="inlineStr">
         <is>
@@ -15025,12 +15025,12 @@
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:20Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -15099,7 +15099,7 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q115" t="inlineStr">
         <is>
@@ -15153,12 +15153,12 @@
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:20Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -15227,7 +15227,7 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q116" t="inlineStr">
         <is>
@@ -15281,12 +15281,12 @@
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:20Z</t>
+          <t>2026-10-20T11:33:40Z</t>
         </is>
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>

--- a/exports/California_Surplus_Feed.xlsx
+++ b/exports/California_Surplus_Feed.xlsx
@@ -605,7 +605,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Assessor Parcel 360-150-12-00, San Diego County, CA</t>
+          <t>4850 Jennifer Ct, San Diego, CA 92117</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -614,7 +614,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>881663.35</v>
+        <v>890100</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -622,7 +622,7 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>176332.67</v>
+        <v>178020</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>Listed on San Diego County TTC Final Report of Sale PA-7102 PDF — Item 0263, APN 360-150-12-00</t>
+          <t>Listed on San Diego County TTC Final Report of Sale PA-7102 PDF — Item 0263, APN 360-150-12-00 (Official Sale Price: $890,100.00 less $8,436.65 statutory deductions = $881,663.35 net excess proceeds)</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -689,12 +689,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:45Z</t>
+          <t>2026-10-23T09:19:01Z</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -763,7 +763,7 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -817,12 +817,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:45Z</t>
+          <t>2026-10-23T09:19:01Z</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -945,12 +945,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:45Z</t>
+          <t>2026-10-23T09:19:01Z</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:42Z</t>
+          <t>2026-10-23T09:18:59Z</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -1147,7 +1147,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1201,12 +1201,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:42Z</t>
+          <t>2026-10-23T09:18:59Z</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -1275,7 +1275,7 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:45Z</t>
+          <t>2026-10-23T09:19:01Z</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -1403,7 +1403,7 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>-107</v>
+        <v>-108</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -1457,12 +1457,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:44Z</t>
+          <t>2026-10-23T09:19:00Z</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:45Z</t>
+          <t>2026-10-23T09:19:01Z</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>-107</v>
+        <v>-108</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -1713,12 +1713,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:44Z</t>
+          <t>2026-10-23T09:19:00Z</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -1787,7 +1787,7 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -1841,12 +1841,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:45Z</t>
+          <t>2026-10-23T09:19:01Z</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -1915,7 +1915,7 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -1969,12 +1969,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:42Z</t>
+          <t>2026-10-23T09:18:59Z</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -2043,7 +2043,7 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:42Z</t>
+          <t>2026-10-23T09:18:59Z</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>-107</v>
+        <v>-108</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -2225,12 +2225,12 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:44Z</t>
+          <t>2026-10-23T09:19:00Z</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -2299,7 +2299,7 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -2353,12 +2353,12 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:42Z</t>
+          <t>2026-10-23T09:18:59Z</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -2427,7 +2427,7 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>-107</v>
+        <v>-108</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
@@ -2481,12 +2481,12 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:44Z</t>
+          <t>2026-10-23T09:19:00Z</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -2609,12 +2609,12 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:42Z</t>
+          <t>2026-10-23T09:18:59Z</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -2737,12 +2737,12 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:45Z</t>
+          <t>2026-10-23T09:19:01Z</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2811,7 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -2865,12 +2865,12 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:42Z</t>
+          <t>2026-10-23T09:18:59Z</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -2939,7 +2939,7 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -2993,12 +2993,12 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:42Z</t>
+          <t>2026-10-23T09:18:59Z</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -3067,7 +3067,7 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -3121,12 +3121,12 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:42Z</t>
+          <t>2026-10-23T09:18:59Z</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -3195,7 +3195,7 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -3249,12 +3249,12 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:42Z</t>
+          <t>2026-10-23T09:18:59Z</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -3323,7 +3323,7 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -3377,12 +3377,12 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:42Z</t>
+          <t>2026-10-23T09:18:59Z</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>-107</v>
+        <v>-108</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -3505,12 +3505,12 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:44Z</t>
+          <t>2026-10-23T09:19:00Z</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -3579,7 +3579,7 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -3633,12 +3633,12 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:42Z</t>
+          <t>2026-10-23T09:18:59Z</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -3707,7 +3707,7 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -3761,12 +3761,12 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:45Z</t>
+          <t>2026-10-23T09:19:01Z</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -3835,7 +3835,7 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -3889,12 +3889,12 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:45Z</t>
+          <t>2026-10-23T09:19:01Z</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -3963,7 +3963,7 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
@@ -4017,12 +4017,12 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:45Z</t>
+          <t>2026-10-23T09:19:01Z</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -4091,7 +4091,7 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
@@ -4145,12 +4145,12 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:42Z</t>
+          <t>2026-10-23T09:18:59Z</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -4219,7 +4219,7 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
@@ -4273,12 +4273,12 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:45Z</t>
+          <t>2026-10-23T09:19:01Z</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
@@ -4401,12 +4401,12 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:42Z</t>
+          <t>2026-10-23T09:18:59Z</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -4475,7 +4475,7 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
@@ -4529,12 +4529,12 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:42Z</t>
+          <t>2026-10-23T09:18:59Z</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -4603,7 +4603,7 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
@@ -4657,12 +4657,12 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:42Z</t>
+          <t>2026-10-23T09:18:59Z</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
@@ -4785,12 +4785,12 @@
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:42Z</t>
+          <t>2026-10-23T09:18:59Z</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -4859,7 +4859,7 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
@@ -4913,12 +4913,12 @@
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:42Z</t>
+          <t>2026-10-23T09:18:59Z</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -4987,7 +4987,7 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>-107</v>
+        <v>-108</v>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
@@ -5041,12 +5041,12 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:44Z</t>
+          <t>2026-10-23T09:19:00Z</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -5115,7 +5115,7 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:42Z</t>
+          <t>2026-10-23T09:18:59Z</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -5243,7 +5243,7 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
@@ -5297,12 +5297,12 @@
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:42Z</t>
+          <t>2026-10-23T09:18:59Z</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -5371,7 +5371,7 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:45Z</t>
+          <t>2026-10-23T09:19:01Z</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -5499,7 +5499,7 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
@@ -5553,12 +5553,12 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:42Z</t>
+          <t>2026-10-23T09:18:59Z</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -5627,7 +5627,7 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
@@ -5681,12 +5681,12 @@
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:42Z</t>
+          <t>2026-10-23T09:18:59Z</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -5755,7 +5755,7 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
@@ -5809,12 +5809,12 @@
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:42Z</t>
+          <t>2026-10-23T09:18:59Z</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -5883,7 +5883,7 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
@@ -5937,12 +5937,12 @@
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:42Z</t>
+          <t>2026-10-23T09:18:59Z</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -6011,7 +6011,7 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
@@ -6065,12 +6065,12 @@
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:42Z</t>
+          <t>2026-10-23T09:18:59Z</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -6139,7 +6139,7 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
@@ -6193,12 +6193,12 @@
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:42Z</t>
+          <t>2026-10-23T09:18:59Z</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -6267,7 +6267,7 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
@@ -6321,12 +6321,12 @@
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:42Z</t>
+          <t>2026-10-23T09:18:59Z</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -6395,7 +6395,7 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
@@ -6449,12 +6449,12 @@
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:42Z</t>
+          <t>2026-10-23T09:18:59Z</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -6523,7 +6523,7 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
@@ -6577,12 +6577,12 @@
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:45Z</t>
+          <t>2026-10-23T09:19:01Z</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -6651,7 +6651,7 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
@@ -6705,12 +6705,12 @@
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:42Z</t>
+          <t>2026-10-23T09:18:59Z</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -6779,7 +6779,7 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
@@ -6833,12 +6833,12 @@
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:42Z</t>
+          <t>2026-10-23T09:18:59Z</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
@@ -6961,12 +6961,12 @@
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:42Z</t>
+          <t>2026-10-23T09:18:59Z</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
@@ -7089,12 +7089,12 @@
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:42Z</t>
+          <t>2026-10-23T09:18:59Z</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -7163,7 +7163,7 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
@@ -7217,12 +7217,12 @@
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:42Z</t>
+          <t>2026-10-23T09:18:59Z</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -7291,7 +7291,7 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
@@ -7345,12 +7345,12 @@
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:45Z</t>
+          <t>2026-10-23T09:19:01Z</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -7419,7 +7419,7 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
@@ -7473,12 +7473,12 @@
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:42Z</t>
+          <t>2026-10-23T09:18:59Z</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -7547,7 +7547,7 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
@@ -7601,12 +7601,12 @@
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:45Z</t>
+          <t>2026-10-23T09:19:01Z</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -7675,7 +7675,7 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
@@ -7729,12 +7729,12 @@
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:42Z</t>
+          <t>2026-10-23T09:18:59Z</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
@@ -7857,12 +7857,12 @@
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:45Z</t>
+          <t>2026-10-23T09:19:01Z</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -7931,7 +7931,7 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
@@ -7985,12 +7985,12 @@
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:42Z</t>
+          <t>2026-10-23T09:18:59Z</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -8059,7 +8059,7 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
@@ -8113,12 +8113,12 @@
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:42Z</t>
+          <t>2026-10-23T09:18:59Z</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -8187,7 +8187,7 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
@@ -8241,12 +8241,12 @@
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:42Z</t>
+          <t>2026-10-23T09:18:59Z</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -8315,7 +8315,7 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
@@ -8369,12 +8369,12 @@
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:45Z</t>
+          <t>2026-10-23T09:19:01Z</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -8443,7 +8443,7 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
@@ -8497,12 +8497,12 @@
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:42Z</t>
+          <t>2026-10-23T09:18:59Z</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -8571,7 +8571,7 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
@@ -8625,12 +8625,12 @@
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:42Z</t>
+          <t>2026-10-23T09:18:59Z</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:45Z</t>
+          <t>2026-10-23T09:19:01Z</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -8827,7 +8827,7 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>-107</v>
+        <v>-108</v>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
@@ -8881,12 +8881,12 @@
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:44Z</t>
+          <t>2026-10-23T09:19:00Z</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -8955,7 +8955,7 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
@@ -9009,12 +9009,12 @@
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:42Z</t>
+          <t>2026-10-23T09:18:59Z</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -9083,7 +9083,7 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
@@ -9137,12 +9137,12 @@
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:42Z</t>
+          <t>2026-10-23T09:18:59Z</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -9211,7 +9211,7 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
@@ -9265,12 +9265,12 @@
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:42Z</t>
+          <t>2026-10-23T09:18:59Z</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -9339,7 +9339,7 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
@@ -9393,12 +9393,12 @@
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:42Z</t>
+          <t>2026-10-23T09:18:59Z</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -9467,7 +9467,7 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
@@ -9521,12 +9521,12 @@
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:42Z</t>
+          <t>2026-10-23T09:18:59Z</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -9595,7 +9595,7 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
@@ -9649,12 +9649,12 @@
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:42Z</t>
+          <t>2026-10-23T09:18:59Z</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -9723,7 +9723,7 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
@@ -9777,12 +9777,12 @@
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:42Z</t>
+          <t>2026-10-23T09:18:59Z</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -9851,7 +9851,7 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
@@ -9905,12 +9905,12 @@
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:45Z</t>
+          <t>2026-10-23T09:19:01Z</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -9979,7 +9979,7 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
@@ -10033,12 +10033,12 @@
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:45Z</t>
+          <t>2026-10-23T09:19:01Z</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -10107,7 +10107,7 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
@@ -10161,12 +10161,12 @@
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:45Z</t>
+          <t>2026-10-23T09:19:01Z</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -10235,7 +10235,7 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
@@ -10289,12 +10289,12 @@
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:42Z</t>
+          <t>2026-10-23T09:18:59Z</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -10363,7 +10363,7 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
@@ -10417,12 +10417,12 @@
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:45Z</t>
+          <t>2026-10-23T09:19:01Z</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -10491,7 +10491,7 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
@@ -10545,12 +10545,12 @@
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:42Z</t>
+          <t>2026-10-23T09:18:59Z</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -10619,7 +10619,7 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
@@ -10673,12 +10673,12 @@
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:45Z</t>
+          <t>2026-10-23T09:19:01Z</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -10747,7 +10747,7 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
@@ -10801,12 +10801,12 @@
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:45Z</t>
+          <t>2026-10-23T09:19:01Z</t>
         </is>
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -10875,7 +10875,7 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
@@ -10929,12 +10929,12 @@
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:42Z</t>
+          <t>2026-10-23T09:18:59Z</t>
         </is>
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -11003,7 +11003,7 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q83" t="inlineStr">
         <is>
@@ -11057,12 +11057,12 @@
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:42Z</t>
+          <t>2026-10-23T09:18:59Z</t>
         </is>
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -11131,7 +11131,7 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
@@ -11185,12 +11185,12 @@
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:42Z</t>
+          <t>2026-10-23T09:18:59Z</t>
         </is>
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -11259,7 +11259,7 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
@@ -11313,12 +11313,12 @@
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:42Z</t>
+          <t>2026-10-23T09:18:59Z</t>
         </is>
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -11387,7 +11387,7 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q86" t="inlineStr">
         <is>
@@ -11441,12 +11441,12 @@
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:42Z</t>
+          <t>2026-10-23T09:18:59Z</t>
         </is>
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -11515,7 +11515,7 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
@@ -11569,12 +11569,12 @@
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:42Z</t>
+          <t>2026-10-23T09:18:59Z</t>
         </is>
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -11643,7 +11643,7 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
@@ -11697,12 +11697,12 @@
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:42Z</t>
+          <t>2026-10-23T09:18:59Z</t>
         </is>
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -11771,7 +11771,7 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
@@ -11825,12 +11825,12 @@
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:42Z</t>
+          <t>2026-10-23T09:18:59Z</t>
         </is>
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -11899,7 +11899,7 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
@@ -11953,12 +11953,12 @@
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:42Z</t>
+          <t>2026-10-23T09:18:59Z</t>
         </is>
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -12027,7 +12027,7 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
@@ -12081,12 +12081,12 @@
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:42Z</t>
+          <t>2026-10-23T09:18:59Z</t>
         </is>
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -12155,7 +12155,7 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q92" t="inlineStr">
         <is>
@@ -12209,12 +12209,12 @@
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:42Z</t>
+          <t>2026-10-23T09:18:59Z</t>
         </is>
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -12283,7 +12283,7 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
@@ -12337,12 +12337,12 @@
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:42Z</t>
+          <t>2026-10-23T09:18:59Z</t>
         </is>
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -12411,7 +12411,7 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q94" t="inlineStr">
         <is>
@@ -12465,12 +12465,12 @@
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:42Z</t>
+          <t>2026-10-23T09:18:59Z</t>
         </is>
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -12539,7 +12539,7 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q95" t="inlineStr">
         <is>
@@ -12593,12 +12593,12 @@
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:42Z</t>
+          <t>2026-10-23T09:18:59Z</t>
         </is>
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -12667,7 +12667,7 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
@@ -12721,12 +12721,12 @@
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:45Z</t>
+          <t>2026-10-23T09:19:01Z</t>
         </is>
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -12795,7 +12795,7 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q97" t="inlineStr">
         <is>
@@ -12849,12 +12849,12 @@
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:42Z</t>
+          <t>2026-10-23T09:18:59Z</t>
         </is>
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -12923,7 +12923,7 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q98" t="inlineStr">
         <is>
@@ -12977,12 +12977,12 @@
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:42Z</t>
+          <t>2026-10-23T09:18:59Z</t>
         </is>
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -13051,7 +13051,7 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q99" t="inlineStr">
         <is>
@@ -13105,12 +13105,12 @@
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:42Z</t>
+          <t>2026-10-23T09:18:59Z</t>
         </is>
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -13179,7 +13179,7 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q100" t="inlineStr">
         <is>
@@ -13233,12 +13233,12 @@
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:42Z</t>
+          <t>2026-10-23T09:18:59Z</t>
         </is>
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -13307,7 +13307,7 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q101" t="inlineStr">
         <is>
@@ -13361,12 +13361,12 @@
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:42Z</t>
+          <t>2026-10-23T09:18:59Z</t>
         </is>
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -13435,7 +13435,7 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q102" t="inlineStr">
         <is>
@@ -13489,12 +13489,12 @@
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:42Z</t>
+          <t>2026-10-23T09:18:59Z</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -13563,7 +13563,7 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
@@ -13617,12 +13617,12 @@
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:42Z</t>
+          <t>2026-10-23T09:18:59Z</t>
         </is>
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -13691,7 +13691,7 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="Q104" t="inlineStr">
         <is>
@@ -13745,12 +13745,12 @@
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:42Z</t>
+          <t>2026-10-23T09:18:59Z</t>
         </is>
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -13819,7 +13819,7 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Q105" t="inlineStr">
         <is>
@@ -13873,12 +13873,12 @@
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:45Z</t>
+          <t>2026-10-23T09:19:01Z</t>
         </is>
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -13947,7 +13947,7 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q106" t="inlineStr">
         <is>
@@ -14001,12 +14001,12 @@
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:42Z</t>
+          <t>2026-10-23T09:18:59Z</t>
         </is>
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -14075,7 +14075,7 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q107" t="inlineStr">
         <is>
@@ -14129,12 +14129,12 @@
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:42Z</t>
+          <t>2026-10-23T09:18:59Z</t>
         </is>
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -14203,7 +14203,7 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q108" t="inlineStr">
         <is>
@@ -14257,12 +14257,12 @@
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:42Z</t>
+          <t>2026-10-23T09:18:59Z</t>
         </is>
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -14331,7 +14331,7 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q109" t="inlineStr">
         <is>
@@ -14385,12 +14385,12 @@
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:42Z</t>
+          <t>2026-10-23T09:18:59Z</t>
         </is>
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -14459,7 +14459,7 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q110" t="inlineStr">
         <is>
@@ -14513,12 +14513,12 @@
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:42Z</t>
+          <t>2026-10-23T09:18:59Z</t>
         </is>
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>

--- a/exports/California_Surplus_Feed.xlsx
+++ b/exports/California_Surplus_Feed.xlsx
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -689,12 +689,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-23T09:19:01Z</t>
+          <t>2026-10-24T08:50:39Z</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -763,7 +763,7 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -817,12 +817,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-23T09:19:01Z</t>
+          <t>2026-10-24T08:50:39Z</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -945,12 +945,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-23T09:19:01Z</t>
+          <t>2026-10-24T08:50:39Z</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:59Z</t>
+          <t>2026-10-24T08:50:38Z</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -1147,7 +1147,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1201,12 +1201,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:59Z</t>
+          <t>2026-10-24T08:50:38Z</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -1275,7 +1275,7 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-10-23T09:19:01Z</t>
+          <t>2026-10-24T08:50:39Z</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -1403,7 +1403,7 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>-108</v>
+        <v>-109</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -1457,12 +1457,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-10-23T09:19:00Z</t>
+          <t>2026-10-24T08:50:39Z</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-10-23T09:19:01Z</t>
+          <t>2026-10-24T08:50:39Z</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>-108</v>
+        <v>-109</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -1713,12 +1713,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-10-23T09:19:00Z</t>
+          <t>2026-10-24T08:50:39Z</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -1787,7 +1787,7 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -1841,12 +1841,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-10-23T09:19:01Z</t>
+          <t>2026-10-24T08:50:39Z</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -1915,7 +1915,7 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -1969,12 +1969,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:59Z</t>
+          <t>2026-10-24T08:50:38Z</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -2043,7 +2043,7 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:59Z</t>
+          <t>2026-10-24T08:50:38Z</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>-108</v>
+        <v>-109</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -2225,12 +2225,12 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-10-23T09:19:00Z</t>
+          <t>2026-10-24T08:50:39Z</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -2299,7 +2299,7 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -2353,12 +2353,12 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:59Z</t>
+          <t>2026-10-24T08:50:38Z</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -2427,7 +2427,7 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>-108</v>
+        <v>-109</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
@@ -2481,12 +2481,12 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-10-23T09:19:00Z</t>
+          <t>2026-10-24T08:50:39Z</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -2609,12 +2609,12 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:59Z</t>
+          <t>2026-10-24T08:50:38Z</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -2737,12 +2737,12 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-10-23T09:19:01Z</t>
+          <t>2026-10-24T08:50:39Z</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2811,7 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -2865,12 +2865,12 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:59Z</t>
+          <t>2026-10-24T08:50:38Z</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -2939,7 +2939,7 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -2993,12 +2993,12 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:59Z</t>
+          <t>2026-10-24T08:50:38Z</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -3067,7 +3067,7 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -3121,12 +3121,12 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:59Z</t>
+          <t>2026-10-24T08:50:38Z</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -3195,7 +3195,7 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -3249,12 +3249,12 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:59Z</t>
+          <t>2026-10-24T08:50:38Z</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -3323,7 +3323,7 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -3377,12 +3377,12 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:59Z</t>
+          <t>2026-10-24T08:50:38Z</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>-108</v>
+        <v>-109</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -3505,12 +3505,12 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-10-23T09:19:00Z</t>
+          <t>2026-10-24T08:50:39Z</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -3579,7 +3579,7 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -3633,12 +3633,12 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:59Z</t>
+          <t>2026-10-24T08:50:38Z</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -3707,7 +3707,7 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -3761,12 +3761,12 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-10-23T09:19:01Z</t>
+          <t>2026-10-24T08:50:39Z</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -3835,7 +3835,7 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -3889,12 +3889,12 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-10-23T09:19:01Z</t>
+          <t>2026-10-24T08:50:39Z</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -3963,7 +3963,7 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
@@ -4017,12 +4017,12 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-10-23T09:19:01Z</t>
+          <t>2026-10-24T08:50:39Z</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -4091,7 +4091,7 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
@@ -4145,12 +4145,12 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:59Z</t>
+          <t>2026-10-24T08:50:38Z</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -4219,7 +4219,7 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
@@ -4273,12 +4273,12 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-10-23T09:19:01Z</t>
+          <t>2026-10-24T08:50:39Z</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
@@ -4401,12 +4401,12 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:59Z</t>
+          <t>2026-10-24T08:50:38Z</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -4475,7 +4475,7 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
@@ -4529,12 +4529,12 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:59Z</t>
+          <t>2026-10-24T08:50:38Z</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -4603,7 +4603,7 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
@@ -4657,12 +4657,12 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:59Z</t>
+          <t>2026-10-24T08:50:38Z</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
@@ -4785,12 +4785,12 @@
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:59Z</t>
+          <t>2026-10-24T08:50:38Z</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -4859,7 +4859,7 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
@@ -4913,12 +4913,12 @@
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:59Z</t>
+          <t>2026-10-24T08:50:38Z</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -4987,7 +4987,7 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>-108</v>
+        <v>-109</v>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
@@ -5041,12 +5041,12 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-10-23T09:19:00Z</t>
+          <t>2026-10-24T08:50:39Z</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -5115,7 +5115,7 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:59Z</t>
+          <t>2026-10-24T08:50:38Z</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -5243,7 +5243,7 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
@@ -5297,12 +5297,12 @@
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:59Z</t>
+          <t>2026-10-24T08:50:38Z</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -5371,7 +5371,7 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-10-23T09:19:01Z</t>
+          <t>2026-10-24T08:50:39Z</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -5499,7 +5499,7 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
@@ -5553,12 +5553,12 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:59Z</t>
+          <t>2026-10-24T08:50:38Z</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -5627,7 +5627,7 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
@@ -5681,12 +5681,12 @@
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:59Z</t>
+          <t>2026-10-24T08:50:38Z</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -5755,7 +5755,7 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
@@ -5809,12 +5809,12 @@
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:59Z</t>
+          <t>2026-10-24T08:50:38Z</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -5883,7 +5883,7 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
@@ -5937,12 +5937,12 @@
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:59Z</t>
+          <t>2026-10-24T08:50:38Z</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -6011,7 +6011,7 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
@@ -6065,12 +6065,12 @@
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:59Z</t>
+          <t>2026-10-24T08:50:38Z</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -6139,7 +6139,7 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
@@ -6193,12 +6193,12 @@
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:59Z</t>
+          <t>2026-10-24T08:50:38Z</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -6267,7 +6267,7 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
@@ -6321,12 +6321,12 @@
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:59Z</t>
+          <t>2026-10-24T08:50:38Z</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -6395,7 +6395,7 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
@@ -6449,12 +6449,12 @@
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:59Z</t>
+          <t>2026-10-24T08:50:38Z</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -6523,7 +6523,7 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
@@ -6577,12 +6577,12 @@
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-10-23T09:19:01Z</t>
+          <t>2026-10-24T08:50:39Z</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -6651,7 +6651,7 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
@@ -6705,12 +6705,12 @@
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:59Z</t>
+          <t>2026-10-24T08:50:38Z</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -6779,7 +6779,7 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
@@ -6833,12 +6833,12 @@
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:59Z</t>
+          <t>2026-10-24T08:50:38Z</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
@@ -6961,12 +6961,12 @@
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:59Z</t>
+          <t>2026-10-24T08:50:38Z</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
@@ -7089,12 +7089,12 @@
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:59Z</t>
+          <t>2026-10-24T08:50:38Z</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -7163,7 +7163,7 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
@@ -7217,12 +7217,12 @@
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:59Z</t>
+          <t>2026-10-24T08:50:38Z</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -7291,7 +7291,7 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
@@ -7345,12 +7345,12 @@
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-10-23T09:19:01Z</t>
+          <t>2026-10-24T08:50:39Z</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -7419,7 +7419,7 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
@@ -7473,12 +7473,12 @@
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:59Z</t>
+          <t>2026-10-24T08:50:38Z</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -7547,7 +7547,7 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
@@ -7601,12 +7601,12 @@
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-10-23T09:19:01Z</t>
+          <t>2026-10-24T08:50:39Z</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -7675,7 +7675,7 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
@@ -7729,12 +7729,12 @@
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:59Z</t>
+          <t>2026-10-24T08:50:38Z</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
@@ -7857,12 +7857,12 @@
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-10-23T09:19:01Z</t>
+          <t>2026-10-24T08:50:39Z</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -7931,7 +7931,7 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
@@ -7985,12 +7985,12 @@
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:59Z</t>
+          <t>2026-10-24T08:50:38Z</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -8059,7 +8059,7 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
@@ -8113,12 +8113,12 @@
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:59Z</t>
+          <t>2026-10-24T08:50:38Z</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -8187,7 +8187,7 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
@@ -8241,12 +8241,12 @@
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:59Z</t>
+          <t>2026-10-24T08:50:38Z</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -8315,7 +8315,7 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
@@ -8369,12 +8369,12 @@
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-10-23T09:19:01Z</t>
+          <t>2026-10-24T08:50:39Z</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -8443,7 +8443,7 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
@@ -8497,12 +8497,12 @@
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:59Z</t>
+          <t>2026-10-24T08:50:38Z</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -8571,7 +8571,7 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
@@ -8625,12 +8625,12 @@
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:59Z</t>
+          <t>2026-10-24T08:50:38Z</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2026-10-23T09:19:01Z</t>
+          <t>2026-10-24T08:50:39Z</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -8827,7 +8827,7 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>-108</v>
+        <v>-109</v>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
@@ -8881,12 +8881,12 @@
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-10-23T09:19:00Z</t>
+          <t>2026-10-24T08:50:39Z</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -8955,7 +8955,7 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
@@ -9009,12 +9009,12 @@
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:59Z</t>
+          <t>2026-10-24T08:50:38Z</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -9083,7 +9083,7 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
@@ -9137,12 +9137,12 @@
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:59Z</t>
+          <t>2026-10-24T08:50:38Z</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -9211,7 +9211,7 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
@@ -9265,12 +9265,12 @@
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:59Z</t>
+          <t>2026-10-24T08:50:38Z</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -9339,7 +9339,7 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
@@ -9393,12 +9393,12 @@
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:59Z</t>
+          <t>2026-10-24T08:50:38Z</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -9467,7 +9467,7 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
@@ -9521,12 +9521,12 @@
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:59Z</t>
+          <t>2026-10-24T08:50:38Z</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -9595,7 +9595,7 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
@@ -9649,12 +9649,12 @@
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:59Z</t>
+          <t>2026-10-24T08:50:38Z</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -9723,7 +9723,7 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
@@ -9777,12 +9777,12 @@
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:59Z</t>
+          <t>2026-10-24T08:50:38Z</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -9851,7 +9851,7 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
@@ -9905,12 +9905,12 @@
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2026-10-23T09:19:01Z</t>
+          <t>2026-10-24T08:50:39Z</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -9979,7 +9979,7 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
@@ -10033,12 +10033,12 @@
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2026-10-23T09:19:01Z</t>
+          <t>2026-10-24T08:50:39Z</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -10107,7 +10107,7 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
@@ -10161,12 +10161,12 @@
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2026-10-23T09:19:01Z</t>
+          <t>2026-10-24T08:50:39Z</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -10235,7 +10235,7 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
@@ -10289,12 +10289,12 @@
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:59Z</t>
+          <t>2026-10-24T08:50:38Z</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -10363,7 +10363,7 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
@@ -10417,12 +10417,12 @@
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2026-10-23T09:19:01Z</t>
+          <t>2026-10-24T08:50:39Z</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -10491,7 +10491,7 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
@@ -10545,12 +10545,12 @@
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:59Z</t>
+          <t>2026-10-24T08:50:38Z</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -10619,7 +10619,7 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
@@ -10673,12 +10673,12 @@
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2026-10-23T09:19:01Z</t>
+          <t>2026-10-24T08:50:39Z</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -10747,7 +10747,7 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
@@ -10801,12 +10801,12 @@
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2026-10-23T09:19:01Z</t>
+          <t>2026-10-24T08:50:39Z</t>
         </is>
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -10875,7 +10875,7 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
@@ -10929,12 +10929,12 @@
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:59Z</t>
+          <t>2026-10-24T08:50:38Z</t>
         </is>
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -11003,7 +11003,7 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q83" t="inlineStr">
         <is>
@@ -11057,12 +11057,12 @@
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:59Z</t>
+          <t>2026-10-24T08:50:38Z</t>
         </is>
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -11131,7 +11131,7 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
@@ -11185,12 +11185,12 @@
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:59Z</t>
+          <t>2026-10-24T08:50:38Z</t>
         </is>
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -11259,7 +11259,7 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
@@ -11313,12 +11313,12 @@
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:59Z</t>
+          <t>2026-10-24T08:50:38Z</t>
         </is>
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -11387,7 +11387,7 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q86" t="inlineStr">
         <is>
@@ -11441,12 +11441,12 @@
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:59Z</t>
+          <t>2026-10-24T08:50:38Z</t>
         </is>
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -11515,7 +11515,7 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
@@ -11569,12 +11569,12 @@
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:59Z</t>
+          <t>2026-10-24T08:50:38Z</t>
         </is>
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -11643,7 +11643,7 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
@@ -11697,12 +11697,12 @@
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:59Z</t>
+          <t>2026-10-24T08:50:38Z</t>
         </is>
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -11771,7 +11771,7 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
@@ -11825,12 +11825,12 @@
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:59Z</t>
+          <t>2026-10-24T08:50:38Z</t>
         </is>
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -11899,7 +11899,7 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
@@ -11953,12 +11953,12 @@
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:59Z</t>
+          <t>2026-10-24T08:50:38Z</t>
         </is>
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -12027,7 +12027,7 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
@@ -12081,12 +12081,12 @@
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:59Z</t>
+          <t>2026-10-24T08:50:38Z</t>
         </is>
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -12155,7 +12155,7 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q92" t="inlineStr">
         <is>
@@ -12209,12 +12209,12 @@
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:59Z</t>
+          <t>2026-10-24T08:50:38Z</t>
         </is>
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -12283,7 +12283,7 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
@@ -12337,12 +12337,12 @@
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:59Z</t>
+          <t>2026-10-24T08:50:38Z</t>
         </is>
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -12411,7 +12411,7 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q94" t="inlineStr">
         <is>
@@ -12465,12 +12465,12 @@
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:59Z</t>
+          <t>2026-10-24T08:50:38Z</t>
         </is>
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -12539,7 +12539,7 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q95" t="inlineStr">
         <is>
@@ -12593,12 +12593,12 @@
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:59Z</t>
+          <t>2026-10-24T08:50:38Z</t>
         </is>
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -12667,7 +12667,7 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
@@ -12721,12 +12721,12 @@
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2026-10-23T09:19:01Z</t>
+          <t>2026-10-24T08:50:39Z</t>
         </is>
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -12795,7 +12795,7 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q97" t="inlineStr">
         <is>
@@ -12849,12 +12849,12 @@
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:59Z</t>
+          <t>2026-10-24T08:50:38Z</t>
         </is>
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -12923,7 +12923,7 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q98" t="inlineStr">
         <is>
@@ -12977,12 +12977,12 @@
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:59Z</t>
+          <t>2026-10-24T08:50:38Z</t>
         </is>
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -13051,7 +13051,7 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q99" t="inlineStr">
         <is>
@@ -13105,12 +13105,12 @@
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:59Z</t>
+          <t>2026-10-24T08:50:38Z</t>
         </is>
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -13179,7 +13179,7 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q100" t="inlineStr">
         <is>
@@ -13233,12 +13233,12 @@
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:59Z</t>
+          <t>2026-10-24T08:50:38Z</t>
         </is>
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -13307,7 +13307,7 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q101" t="inlineStr">
         <is>
@@ -13361,12 +13361,12 @@
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:59Z</t>
+          <t>2026-10-24T08:50:38Z</t>
         </is>
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -13435,7 +13435,7 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q102" t="inlineStr">
         <is>
@@ -13489,12 +13489,12 @@
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:59Z</t>
+          <t>2026-10-24T08:50:38Z</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -13563,7 +13563,7 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
@@ -13617,12 +13617,12 @@
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:59Z</t>
+          <t>2026-10-24T08:50:38Z</t>
         </is>
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -13691,7 +13691,7 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="Q104" t="inlineStr">
         <is>
@@ -13745,12 +13745,12 @@
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:59Z</t>
+          <t>2026-10-24T08:50:38Z</t>
         </is>
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -13819,7 +13819,7 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q105" t="inlineStr">
         <is>
@@ -13873,12 +13873,12 @@
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2026-10-23T09:19:01Z</t>
+          <t>2026-10-24T08:50:39Z</t>
         </is>
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -13947,7 +13947,7 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q106" t="inlineStr">
         <is>
@@ -14001,12 +14001,12 @@
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:59Z</t>
+          <t>2026-10-24T08:50:38Z</t>
         </is>
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -14075,7 +14075,7 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q107" t="inlineStr">
         <is>
@@ -14129,12 +14129,12 @@
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:59Z</t>
+          <t>2026-10-24T08:50:38Z</t>
         </is>
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -14203,7 +14203,7 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q108" t="inlineStr">
         <is>
@@ -14257,12 +14257,12 @@
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:59Z</t>
+          <t>2026-10-24T08:50:38Z</t>
         </is>
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -14331,7 +14331,7 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q109" t="inlineStr">
         <is>
@@ -14385,12 +14385,12 @@
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:59Z</t>
+          <t>2026-10-24T08:50:38Z</t>
         </is>
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -14459,7 +14459,7 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q110" t="inlineStr">
         <is>
@@ -14513,12 +14513,12 @@
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:59Z</t>
+          <t>2026-10-24T08:50:38Z</t>
         </is>
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>

--- a/exports/California_Surplus_Feed.xlsx
+++ b/exports/California_Surplus_Feed.xlsx
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -689,12 +689,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:39Z</t>
+          <t>2026-10-25T09:07:23Z</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -763,7 +763,7 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -817,12 +817,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:39Z</t>
+          <t>2026-10-25T09:07:23Z</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -945,12 +945,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:39Z</t>
+          <t>2026-10-25T09:07:23Z</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:38Z</t>
+          <t>2026-10-25T09:07:22Z</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -1147,7 +1147,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1201,12 +1201,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:38Z</t>
+          <t>2026-10-25T09:07:22Z</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -1275,7 +1275,7 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:39Z</t>
+          <t>2026-10-25T09:07:23Z</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -1403,7 +1403,7 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>-109</v>
+        <v>-110</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -1457,12 +1457,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:39Z</t>
+          <t>2026-10-25T09:07:23Z</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:39Z</t>
+          <t>2026-10-25T09:07:23Z</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>-109</v>
+        <v>-110</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -1713,12 +1713,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:39Z</t>
+          <t>2026-10-25T09:07:23Z</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -1787,7 +1787,7 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -1841,12 +1841,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:39Z</t>
+          <t>2026-10-25T09:07:23Z</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -1915,7 +1915,7 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -1969,12 +1969,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:38Z</t>
+          <t>2026-10-25T09:07:22Z</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -2043,7 +2043,7 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:38Z</t>
+          <t>2026-10-25T09:07:22Z</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>-109</v>
+        <v>-110</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -2225,12 +2225,12 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:39Z</t>
+          <t>2026-10-25T09:07:23Z</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -2299,7 +2299,7 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -2353,12 +2353,12 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:38Z</t>
+          <t>2026-10-25T09:07:22Z</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -2427,7 +2427,7 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>-109</v>
+        <v>-110</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
@@ -2481,12 +2481,12 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:39Z</t>
+          <t>2026-10-25T09:07:23Z</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -2609,12 +2609,12 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:38Z</t>
+          <t>2026-10-25T09:07:22Z</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -2737,12 +2737,12 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:39Z</t>
+          <t>2026-10-25T09:07:23Z</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2811,7 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -2865,12 +2865,12 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:38Z</t>
+          <t>2026-10-25T09:07:22Z</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -2939,7 +2939,7 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -2993,12 +2993,12 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:38Z</t>
+          <t>2026-10-25T09:07:22Z</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -3067,7 +3067,7 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -3121,12 +3121,12 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:38Z</t>
+          <t>2026-10-25T09:07:22Z</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -3195,7 +3195,7 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -3249,12 +3249,12 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:38Z</t>
+          <t>2026-10-25T09:07:22Z</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -3323,7 +3323,7 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -3377,12 +3377,12 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:38Z</t>
+          <t>2026-10-25T09:07:22Z</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>-109</v>
+        <v>-110</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -3505,12 +3505,12 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:39Z</t>
+          <t>2026-10-25T09:07:23Z</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -3579,7 +3579,7 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -3633,12 +3633,12 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:38Z</t>
+          <t>2026-10-25T09:07:22Z</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -3707,7 +3707,7 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -3761,12 +3761,12 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:39Z</t>
+          <t>2026-10-25T09:07:23Z</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -3835,7 +3835,7 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -3889,12 +3889,12 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:39Z</t>
+          <t>2026-10-25T09:07:23Z</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -3963,7 +3963,7 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
@@ -4017,12 +4017,12 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:39Z</t>
+          <t>2026-10-25T09:07:23Z</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -4091,7 +4091,7 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
@@ -4145,12 +4145,12 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:38Z</t>
+          <t>2026-10-25T09:07:22Z</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -4219,7 +4219,7 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
@@ -4273,12 +4273,12 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:39Z</t>
+          <t>2026-10-25T09:07:23Z</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
@@ -4401,12 +4401,12 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:38Z</t>
+          <t>2026-10-25T09:07:22Z</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -4475,7 +4475,7 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
@@ -4529,12 +4529,12 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:38Z</t>
+          <t>2026-10-25T09:07:22Z</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -4603,7 +4603,7 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
@@ -4657,12 +4657,12 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:38Z</t>
+          <t>2026-10-25T09:07:22Z</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
@@ -4785,12 +4785,12 @@
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:38Z</t>
+          <t>2026-10-25T09:07:22Z</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -4859,7 +4859,7 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
@@ -4913,12 +4913,12 @@
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:38Z</t>
+          <t>2026-10-25T09:07:22Z</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -4987,7 +4987,7 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>-109</v>
+        <v>-110</v>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
@@ -5041,12 +5041,12 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:39Z</t>
+          <t>2026-10-25T09:07:23Z</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -5115,7 +5115,7 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:38Z</t>
+          <t>2026-10-25T09:07:22Z</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -5243,7 +5243,7 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
@@ -5297,12 +5297,12 @@
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:38Z</t>
+          <t>2026-10-25T09:07:22Z</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -5371,7 +5371,7 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:39Z</t>
+          <t>2026-10-25T09:07:23Z</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -5499,7 +5499,7 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
@@ -5553,12 +5553,12 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:38Z</t>
+          <t>2026-10-25T09:07:22Z</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -5627,7 +5627,7 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
@@ -5681,12 +5681,12 @@
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:38Z</t>
+          <t>2026-10-25T09:07:22Z</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -5755,7 +5755,7 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
@@ -5809,12 +5809,12 @@
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:38Z</t>
+          <t>2026-10-25T09:07:22Z</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -5883,7 +5883,7 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
@@ -5937,12 +5937,12 @@
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:38Z</t>
+          <t>2026-10-25T09:07:22Z</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -6011,7 +6011,7 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
@@ -6065,12 +6065,12 @@
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:38Z</t>
+          <t>2026-10-25T09:07:22Z</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -6139,7 +6139,7 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
@@ -6193,12 +6193,12 @@
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:38Z</t>
+          <t>2026-10-25T09:07:22Z</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -6267,7 +6267,7 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
@@ -6321,12 +6321,12 @@
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:38Z</t>
+          <t>2026-10-25T09:07:22Z</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -6395,7 +6395,7 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
@@ -6449,12 +6449,12 @@
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:38Z</t>
+          <t>2026-10-25T09:07:22Z</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -6523,7 +6523,7 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
@@ -6577,12 +6577,12 @@
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:39Z</t>
+          <t>2026-10-25T09:07:23Z</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -6651,7 +6651,7 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
@@ -6705,12 +6705,12 @@
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:38Z</t>
+          <t>2026-10-25T09:07:22Z</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -6779,7 +6779,7 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
@@ -6833,12 +6833,12 @@
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:38Z</t>
+          <t>2026-10-25T09:07:22Z</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
@@ -6961,12 +6961,12 @@
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:38Z</t>
+          <t>2026-10-25T09:07:22Z</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
@@ -7089,12 +7089,12 @@
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:38Z</t>
+          <t>2026-10-25T09:07:22Z</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -7163,7 +7163,7 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
@@ -7217,12 +7217,12 @@
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:38Z</t>
+          <t>2026-10-25T09:07:22Z</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -7291,7 +7291,7 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
@@ -7345,12 +7345,12 @@
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:39Z</t>
+          <t>2026-10-25T09:07:23Z</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -7419,7 +7419,7 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
@@ -7473,12 +7473,12 @@
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:38Z</t>
+          <t>2026-10-25T09:07:22Z</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -7547,7 +7547,7 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
@@ -7601,12 +7601,12 @@
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:39Z</t>
+          <t>2026-10-25T09:07:23Z</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -7675,7 +7675,7 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
@@ -7729,12 +7729,12 @@
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:38Z</t>
+          <t>2026-10-25T09:07:22Z</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
@@ -7857,12 +7857,12 @@
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:39Z</t>
+          <t>2026-10-25T09:07:23Z</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -7931,7 +7931,7 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
@@ -7985,12 +7985,12 @@
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:38Z</t>
+          <t>2026-10-25T09:07:22Z</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -8059,7 +8059,7 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
@@ -8113,12 +8113,12 @@
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:38Z</t>
+          <t>2026-10-25T09:07:22Z</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -8187,7 +8187,7 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
@@ -8241,12 +8241,12 @@
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:38Z</t>
+          <t>2026-10-25T09:07:22Z</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -8315,7 +8315,7 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
@@ -8369,12 +8369,12 @@
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:39Z</t>
+          <t>2026-10-25T09:07:23Z</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -8443,7 +8443,7 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
@@ -8497,12 +8497,12 @@
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:38Z</t>
+          <t>2026-10-25T09:07:22Z</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -8571,7 +8571,7 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
@@ -8625,12 +8625,12 @@
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:38Z</t>
+          <t>2026-10-25T09:07:22Z</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:39Z</t>
+          <t>2026-10-25T09:07:23Z</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -8827,7 +8827,7 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>-109</v>
+        <v>-110</v>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
@@ -8881,12 +8881,12 @@
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:39Z</t>
+          <t>2026-10-25T09:07:23Z</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -8955,7 +8955,7 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
@@ -9009,12 +9009,12 @@
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:38Z</t>
+          <t>2026-10-25T09:07:22Z</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -9083,7 +9083,7 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
@@ -9137,12 +9137,12 @@
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:38Z</t>
+          <t>2026-10-25T09:07:22Z</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -9211,7 +9211,7 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
@@ -9265,12 +9265,12 @@
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:38Z</t>
+          <t>2026-10-25T09:07:22Z</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -9339,7 +9339,7 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
@@ -9393,12 +9393,12 @@
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:38Z</t>
+          <t>2026-10-25T09:07:22Z</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -9467,7 +9467,7 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
@@ -9521,12 +9521,12 @@
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:38Z</t>
+          <t>2026-10-25T09:07:22Z</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -9595,7 +9595,7 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
@@ -9649,12 +9649,12 @@
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:38Z</t>
+          <t>2026-10-25T09:07:22Z</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -9723,7 +9723,7 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
@@ -9777,12 +9777,12 @@
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:38Z</t>
+          <t>2026-10-25T09:07:22Z</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -9851,7 +9851,7 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
@@ -9905,12 +9905,12 @@
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:39Z</t>
+          <t>2026-10-25T09:07:23Z</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -9979,7 +9979,7 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
@@ -10033,12 +10033,12 @@
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:39Z</t>
+          <t>2026-10-25T09:07:23Z</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -10107,7 +10107,7 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
@@ -10161,12 +10161,12 @@
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:39Z</t>
+          <t>2026-10-25T09:07:23Z</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -10235,7 +10235,7 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
@@ -10289,12 +10289,12 @@
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:38Z</t>
+          <t>2026-10-25T09:07:22Z</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -10363,7 +10363,7 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
@@ -10417,12 +10417,12 @@
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:39Z</t>
+          <t>2026-10-25T09:07:23Z</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -10491,7 +10491,7 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
@@ -10545,12 +10545,12 @@
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:38Z</t>
+          <t>2026-10-25T09:07:22Z</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -10619,7 +10619,7 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
@@ -10673,12 +10673,12 @@
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:39Z</t>
+          <t>2026-10-25T09:07:23Z</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -10747,7 +10747,7 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
@@ -10801,12 +10801,12 @@
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:39Z</t>
+          <t>2026-10-25T09:07:23Z</t>
         </is>
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -10875,7 +10875,7 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
@@ -10929,12 +10929,12 @@
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:38Z</t>
+          <t>2026-10-25T09:07:22Z</t>
         </is>
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -11003,7 +11003,7 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q83" t="inlineStr">
         <is>
@@ -11057,12 +11057,12 @@
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:38Z</t>
+          <t>2026-10-25T09:07:22Z</t>
         </is>
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -11131,7 +11131,7 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
@@ -11185,12 +11185,12 @@
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:38Z</t>
+          <t>2026-10-25T09:07:22Z</t>
         </is>
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -11259,7 +11259,7 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
@@ -11313,12 +11313,12 @@
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:38Z</t>
+          <t>2026-10-25T09:07:22Z</t>
         </is>
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -11387,7 +11387,7 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q86" t="inlineStr">
         <is>
@@ -11441,12 +11441,12 @@
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:38Z</t>
+          <t>2026-10-25T09:07:22Z</t>
         </is>
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -11515,7 +11515,7 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
@@ -11569,12 +11569,12 @@
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:38Z</t>
+          <t>2026-10-25T09:07:22Z</t>
         </is>
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -11643,7 +11643,7 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
@@ -11697,12 +11697,12 @@
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:38Z</t>
+          <t>2026-10-25T09:07:22Z</t>
         </is>
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -11771,7 +11771,7 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
@@ -11825,12 +11825,12 @@
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:38Z</t>
+          <t>2026-10-25T09:07:22Z</t>
         </is>
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -11899,7 +11899,7 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
@@ -11953,12 +11953,12 @@
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:38Z</t>
+          <t>2026-10-25T09:07:22Z</t>
         </is>
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -12027,7 +12027,7 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
@@ -12081,12 +12081,12 @@
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:38Z</t>
+          <t>2026-10-25T09:07:22Z</t>
         </is>
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -12155,7 +12155,7 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q92" t="inlineStr">
         <is>
@@ -12209,12 +12209,12 @@
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:38Z</t>
+          <t>2026-10-25T09:07:22Z</t>
         </is>
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -12283,7 +12283,7 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
@@ -12337,12 +12337,12 @@
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:38Z</t>
+          <t>2026-10-25T09:07:22Z</t>
         </is>
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -12411,7 +12411,7 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q94" t="inlineStr">
         <is>
@@ -12465,12 +12465,12 @@
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:38Z</t>
+          <t>2026-10-25T09:07:22Z</t>
         </is>
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -12539,7 +12539,7 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q95" t="inlineStr">
         <is>
@@ -12593,12 +12593,12 @@
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:38Z</t>
+          <t>2026-10-25T09:07:22Z</t>
         </is>
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -12667,7 +12667,7 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
@@ -12721,12 +12721,12 @@
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:39Z</t>
+          <t>2026-10-25T09:07:23Z</t>
         </is>
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -12795,7 +12795,7 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q97" t="inlineStr">
         <is>
@@ -12849,12 +12849,12 @@
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:38Z</t>
+          <t>2026-10-25T09:07:22Z</t>
         </is>
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -12923,7 +12923,7 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q98" t="inlineStr">
         <is>
@@ -12977,12 +12977,12 @@
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:38Z</t>
+          <t>2026-10-25T09:07:22Z</t>
         </is>
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -13051,7 +13051,7 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q99" t="inlineStr">
         <is>
@@ -13105,12 +13105,12 @@
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:38Z</t>
+          <t>2026-10-25T09:07:22Z</t>
         </is>
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -13179,7 +13179,7 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q100" t="inlineStr">
         <is>
@@ -13233,12 +13233,12 @@
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:38Z</t>
+          <t>2026-10-25T09:07:22Z</t>
         </is>
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -13307,7 +13307,7 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q101" t="inlineStr">
         <is>
@@ -13361,12 +13361,12 @@
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:38Z</t>
+          <t>2026-10-25T09:07:22Z</t>
         </is>
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -13435,7 +13435,7 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q102" t="inlineStr">
         <is>
@@ -13489,12 +13489,12 @@
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:38Z</t>
+          <t>2026-10-25T09:07:22Z</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -13563,7 +13563,7 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
@@ -13617,12 +13617,12 @@
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:38Z</t>
+          <t>2026-10-25T09:07:22Z</t>
         </is>
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -13691,7 +13691,7 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="Q104" t="inlineStr">
         <is>
@@ -13745,12 +13745,12 @@
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:38Z</t>
+          <t>2026-10-25T09:07:22Z</t>
         </is>
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -13819,7 +13819,7 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q105" t="inlineStr">
         <is>
@@ -13873,12 +13873,12 @@
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:39Z</t>
+          <t>2026-10-25T09:07:23Z</t>
         </is>
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -13947,7 +13947,7 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q106" t="inlineStr">
         <is>
@@ -14001,12 +14001,12 @@
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:38Z</t>
+          <t>2026-10-25T09:07:22Z</t>
         </is>
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -14075,7 +14075,7 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q107" t="inlineStr">
         <is>
@@ -14129,12 +14129,12 @@
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:38Z</t>
+          <t>2026-10-25T09:07:22Z</t>
         </is>
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -14203,7 +14203,7 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q108" t="inlineStr">
         <is>
@@ -14257,12 +14257,12 @@
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:38Z</t>
+          <t>2026-10-25T09:07:22Z</t>
         </is>
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -14331,7 +14331,7 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q109" t="inlineStr">
         <is>
@@ -14385,12 +14385,12 @@
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:38Z</t>
+          <t>2026-10-25T09:07:22Z</t>
         </is>
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -14459,7 +14459,7 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q110" t="inlineStr">
         <is>
@@ -14513,12 +14513,12 @@
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:38Z</t>
+          <t>2026-10-25T09:07:22Z</t>
         </is>
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>

--- a/exports/California_Surplus_Feed.xlsx
+++ b/exports/California_Surplus_Feed.xlsx
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -689,12 +689,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:23Z</t>
+          <t>2026-10-26T10:03:14Z</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -763,7 +763,7 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -817,12 +817,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:23Z</t>
+          <t>2026-10-26T10:03:14Z</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -945,12 +945,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:23Z</t>
+          <t>2026-10-26T10:03:14Z</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:22Z</t>
+          <t>2026-10-26T10:03:13Z</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -1147,7 +1147,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1201,12 +1201,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:22Z</t>
+          <t>2026-10-26T10:03:13Z</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -1275,7 +1275,7 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:23Z</t>
+          <t>2026-10-26T10:03:14Z</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -1403,7 +1403,7 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>-110</v>
+        <v>-111</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -1457,12 +1457,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:23Z</t>
+          <t>2026-10-26T10:03:14Z</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:23Z</t>
+          <t>2026-10-26T10:03:14Z</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>-110</v>
+        <v>-111</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -1713,12 +1713,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:23Z</t>
+          <t>2026-10-26T10:03:14Z</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -1787,7 +1787,7 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -1841,12 +1841,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:23Z</t>
+          <t>2026-10-26T10:03:14Z</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -1915,7 +1915,7 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -1969,12 +1969,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:22Z</t>
+          <t>2026-10-26T10:03:13Z</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -2043,7 +2043,7 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:22Z</t>
+          <t>2026-10-26T10:03:13Z</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>-110</v>
+        <v>-111</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -2225,12 +2225,12 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:23Z</t>
+          <t>2026-10-26T10:03:14Z</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -2299,7 +2299,7 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -2353,12 +2353,12 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:22Z</t>
+          <t>2026-10-26T10:03:13Z</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -2427,7 +2427,7 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>-110</v>
+        <v>-111</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
@@ -2481,12 +2481,12 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:23Z</t>
+          <t>2026-10-26T10:03:14Z</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -2609,12 +2609,12 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:22Z</t>
+          <t>2026-10-26T10:03:13Z</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -2737,12 +2737,12 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:23Z</t>
+          <t>2026-10-26T10:03:14Z</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2811,7 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -2865,12 +2865,12 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:22Z</t>
+          <t>2026-10-26T10:03:13Z</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -2939,7 +2939,7 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -2993,12 +2993,12 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:22Z</t>
+          <t>2026-10-26T10:03:13Z</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -3067,7 +3067,7 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -3121,12 +3121,12 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:22Z</t>
+          <t>2026-10-26T10:03:13Z</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -3195,7 +3195,7 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -3249,12 +3249,12 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:22Z</t>
+          <t>2026-10-26T10:03:13Z</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -3323,7 +3323,7 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -3377,12 +3377,12 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:22Z</t>
+          <t>2026-10-26T10:03:13Z</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>-110</v>
+        <v>-111</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -3505,12 +3505,12 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:23Z</t>
+          <t>2026-10-26T10:03:14Z</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -3579,7 +3579,7 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -3633,12 +3633,12 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:22Z</t>
+          <t>2026-10-26T10:03:13Z</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -3707,7 +3707,7 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -3761,12 +3761,12 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:23Z</t>
+          <t>2026-10-26T10:03:14Z</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -3835,7 +3835,7 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -3889,12 +3889,12 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:23Z</t>
+          <t>2026-10-26T10:03:14Z</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -3963,7 +3963,7 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
@@ -4017,12 +4017,12 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:23Z</t>
+          <t>2026-10-26T10:03:14Z</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -4091,7 +4091,7 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
@@ -4145,12 +4145,12 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:22Z</t>
+          <t>2026-10-26T10:03:13Z</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -4219,7 +4219,7 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
@@ -4273,12 +4273,12 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:23Z</t>
+          <t>2026-10-26T10:03:14Z</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
@@ -4401,12 +4401,12 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:22Z</t>
+          <t>2026-10-26T10:03:13Z</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -4475,7 +4475,7 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
@@ -4529,12 +4529,12 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:22Z</t>
+          <t>2026-10-26T10:03:13Z</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -4603,7 +4603,7 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
@@ -4657,12 +4657,12 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:22Z</t>
+          <t>2026-10-26T10:03:13Z</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
@@ -4785,12 +4785,12 @@
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:22Z</t>
+          <t>2026-10-26T10:03:13Z</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -4859,7 +4859,7 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
@@ -4913,12 +4913,12 @@
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:22Z</t>
+          <t>2026-10-26T10:03:13Z</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -4987,7 +4987,7 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>-110</v>
+        <v>-111</v>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
@@ -5041,12 +5041,12 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:23Z</t>
+          <t>2026-10-26T10:03:14Z</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -5115,7 +5115,7 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:22Z</t>
+          <t>2026-10-26T10:03:13Z</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -5243,7 +5243,7 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
@@ -5297,12 +5297,12 @@
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:22Z</t>
+          <t>2026-10-26T10:03:13Z</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -5371,7 +5371,7 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:23Z</t>
+          <t>2026-10-26T10:03:14Z</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -5499,7 +5499,7 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
@@ -5553,12 +5553,12 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:22Z</t>
+          <t>2026-10-26T10:03:13Z</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -5627,7 +5627,7 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
@@ -5681,12 +5681,12 @@
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:22Z</t>
+          <t>2026-10-26T10:03:13Z</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -5755,7 +5755,7 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
@@ -5809,12 +5809,12 @@
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:22Z</t>
+          <t>2026-10-26T10:03:13Z</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -5883,7 +5883,7 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
@@ -5937,12 +5937,12 @@
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:22Z</t>
+          <t>2026-10-26T10:03:13Z</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -6011,7 +6011,7 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
@@ -6065,12 +6065,12 @@
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:22Z</t>
+          <t>2026-10-26T10:03:13Z</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -6139,7 +6139,7 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
@@ -6193,12 +6193,12 @@
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:22Z</t>
+          <t>2026-10-26T10:03:13Z</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -6267,7 +6267,7 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
@@ -6321,12 +6321,12 @@
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:22Z</t>
+          <t>2026-10-26T10:03:13Z</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -6395,7 +6395,7 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
@@ -6449,12 +6449,12 @@
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:22Z</t>
+          <t>2026-10-26T10:03:13Z</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -6523,7 +6523,7 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
@@ -6577,12 +6577,12 @@
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:23Z</t>
+          <t>2026-10-26T10:03:14Z</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -6651,7 +6651,7 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
@@ -6705,12 +6705,12 @@
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:22Z</t>
+          <t>2026-10-26T10:03:13Z</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -6779,7 +6779,7 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
@@ -6833,12 +6833,12 @@
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:22Z</t>
+          <t>2026-10-26T10:03:13Z</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
@@ -6961,12 +6961,12 @@
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:22Z</t>
+          <t>2026-10-26T10:03:13Z</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
@@ -7089,12 +7089,12 @@
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:22Z</t>
+          <t>2026-10-26T10:03:13Z</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -7163,7 +7163,7 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
@@ -7217,12 +7217,12 @@
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:22Z</t>
+          <t>2026-10-26T10:03:13Z</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -7291,7 +7291,7 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
@@ -7345,12 +7345,12 @@
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:23Z</t>
+          <t>2026-10-26T10:03:14Z</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -7419,7 +7419,7 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
@@ -7473,12 +7473,12 @@
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:22Z</t>
+          <t>2026-10-26T10:03:13Z</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -7547,7 +7547,7 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
@@ -7601,12 +7601,12 @@
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:23Z</t>
+          <t>2026-10-26T10:03:14Z</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -7675,7 +7675,7 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
@@ -7729,12 +7729,12 @@
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:22Z</t>
+          <t>2026-10-26T10:03:13Z</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
@@ -7857,12 +7857,12 @@
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:23Z</t>
+          <t>2026-10-26T10:03:14Z</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -7931,7 +7931,7 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
@@ -7985,12 +7985,12 @@
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:22Z</t>
+          <t>2026-10-26T10:03:13Z</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -8059,7 +8059,7 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
@@ -8113,12 +8113,12 @@
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:22Z</t>
+          <t>2026-10-26T10:03:13Z</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -8187,7 +8187,7 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
@@ -8241,12 +8241,12 @@
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:22Z</t>
+          <t>2026-10-26T10:03:13Z</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -8315,7 +8315,7 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
@@ -8369,12 +8369,12 @@
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:23Z</t>
+          <t>2026-10-26T10:03:14Z</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -8443,7 +8443,7 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
@@ -8497,12 +8497,12 @@
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:22Z</t>
+          <t>2026-10-26T10:03:13Z</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -8571,7 +8571,7 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
@@ -8625,12 +8625,12 @@
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:22Z</t>
+          <t>2026-10-26T10:03:13Z</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:23Z</t>
+          <t>2026-10-26T10:03:14Z</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -8827,7 +8827,7 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>-110</v>
+        <v>-111</v>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
@@ -8881,12 +8881,12 @@
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:23Z</t>
+          <t>2026-10-26T10:03:14Z</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -8955,7 +8955,7 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
@@ -9009,12 +9009,12 @@
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:22Z</t>
+          <t>2026-10-26T10:03:13Z</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -9083,7 +9083,7 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
@@ -9137,12 +9137,12 @@
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:22Z</t>
+          <t>2026-10-26T10:03:13Z</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -9211,7 +9211,7 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
@@ -9265,12 +9265,12 @@
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:22Z</t>
+          <t>2026-10-26T10:03:13Z</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -9339,7 +9339,7 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
@@ -9393,12 +9393,12 @@
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:22Z</t>
+          <t>2026-10-26T10:03:13Z</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -9467,7 +9467,7 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
@@ -9521,12 +9521,12 @@
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:22Z</t>
+          <t>2026-10-26T10:03:13Z</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -9595,7 +9595,7 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
@@ -9649,12 +9649,12 @@
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:22Z</t>
+          <t>2026-10-26T10:03:13Z</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -9723,7 +9723,7 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
@@ -9777,12 +9777,12 @@
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:22Z</t>
+          <t>2026-10-26T10:03:13Z</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -9851,7 +9851,7 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
@@ -9905,12 +9905,12 @@
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:23Z</t>
+          <t>2026-10-26T10:03:14Z</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -9979,7 +9979,7 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
@@ -10033,12 +10033,12 @@
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:23Z</t>
+          <t>2026-10-26T10:03:14Z</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -10107,7 +10107,7 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
@@ -10161,12 +10161,12 @@
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:23Z</t>
+          <t>2026-10-26T10:03:14Z</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -10235,7 +10235,7 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
@@ -10289,12 +10289,12 @@
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:22Z</t>
+          <t>2026-10-26T10:03:13Z</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -10363,7 +10363,7 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
@@ -10417,12 +10417,12 @@
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:23Z</t>
+          <t>2026-10-26T10:03:14Z</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -10491,7 +10491,7 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
@@ -10545,12 +10545,12 @@
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:22Z</t>
+          <t>2026-10-26T10:03:13Z</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -10619,7 +10619,7 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
@@ -10673,12 +10673,12 @@
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:23Z</t>
+          <t>2026-10-26T10:03:14Z</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -10747,7 +10747,7 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
@@ -10801,12 +10801,12 @@
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:23Z</t>
+          <t>2026-10-26T10:03:14Z</t>
         </is>
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -10875,7 +10875,7 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
@@ -10929,12 +10929,12 @@
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:22Z</t>
+          <t>2026-10-26T10:03:13Z</t>
         </is>
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -11003,7 +11003,7 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q83" t="inlineStr">
         <is>
@@ -11057,12 +11057,12 @@
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:22Z</t>
+          <t>2026-10-26T10:03:13Z</t>
         </is>
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -11131,7 +11131,7 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
@@ -11185,12 +11185,12 @@
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:22Z</t>
+          <t>2026-10-26T10:03:13Z</t>
         </is>
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -11259,7 +11259,7 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
@@ -11313,12 +11313,12 @@
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:22Z</t>
+          <t>2026-10-26T10:03:13Z</t>
         </is>
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -11387,7 +11387,7 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q86" t="inlineStr">
         <is>
@@ -11441,12 +11441,12 @@
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:22Z</t>
+          <t>2026-10-26T10:03:13Z</t>
         </is>
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -11515,7 +11515,7 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
@@ -11569,12 +11569,12 @@
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:22Z</t>
+          <t>2026-10-26T10:03:13Z</t>
         </is>
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -11643,7 +11643,7 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
@@ -11697,12 +11697,12 @@
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:22Z</t>
+          <t>2026-10-26T10:03:13Z</t>
         </is>
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -11771,7 +11771,7 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
@@ -11825,12 +11825,12 @@
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:22Z</t>
+          <t>2026-10-26T10:03:13Z</t>
         </is>
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -11899,7 +11899,7 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
@@ -11953,12 +11953,12 @@
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:22Z</t>
+          <t>2026-10-26T10:03:13Z</t>
         </is>
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -12027,7 +12027,7 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
@@ -12081,12 +12081,12 @@
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:22Z</t>
+          <t>2026-10-26T10:03:13Z</t>
         </is>
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -12155,7 +12155,7 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q92" t="inlineStr">
         <is>
@@ -12209,12 +12209,12 @@
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:22Z</t>
+          <t>2026-10-26T10:03:13Z</t>
         </is>
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -12283,7 +12283,7 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
@@ -12337,12 +12337,12 @@
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:22Z</t>
+          <t>2026-10-26T10:03:13Z</t>
         </is>
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -12411,7 +12411,7 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q94" t="inlineStr">
         <is>
@@ -12465,12 +12465,12 @@
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:22Z</t>
+          <t>2026-10-26T10:03:13Z</t>
         </is>
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -12539,7 +12539,7 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q95" t="inlineStr">
         <is>
@@ -12593,12 +12593,12 @@
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:22Z</t>
+          <t>2026-10-26T10:03:13Z</t>
         </is>
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -12667,7 +12667,7 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
@@ -12721,12 +12721,12 @@
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:23Z</t>
+          <t>2026-10-26T10:03:14Z</t>
         </is>
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -12795,7 +12795,7 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q97" t="inlineStr">
         <is>
@@ -12849,12 +12849,12 @@
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:22Z</t>
+          <t>2026-10-26T10:03:13Z</t>
         </is>
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -12923,7 +12923,7 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q98" t="inlineStr">
         <is>
@@ -12977,12 +12977,12 @@
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:22Z</t>
+          <t>2026-10-26T10:03:13Z</t>
         </is>
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -13051,7 +13051,7 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q99" t="inlineStr">
         <is>
@@ -13105,12 +13105,12 @@
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:22Z</t>
+          <t>2026-10-26T10:03:13Z</t>
         </is>
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -13179,7 +13179,7 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q100" t="inlineStr">
         <is>
@@ -13233,12 +13233,12 @@
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:22Z</t>
+          <t>2026-10-26T10:03:13Z</t>
         </is>
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -13307,7 +13307,7 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q101" t="inlineStr">
         <is>
@@ -13361,12 +13361,12 @@
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:22Z</t>
+          <t>2026-10-26T10:03:13Z</t>
         </is>
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -13435,7 +13435,7 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q102" t="inlineStr">
         <is>
@@ -13489,12 +13489,12 @@
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:22Z</t>
+          <t>2026-10-26T10:03:13Z</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -13563,7 +13563,7 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
@@ -13617,12 +13617,12 @@
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:22Z</t>
+          <t>2026-10-26T10:03:13Z</t>
         </is>
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -13691,7 +13691,7 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="Q104" t="inlineStr">
         <is>
@@ -13745,12 +13745,12 @@
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:22Z</t>
+          <t>2026-10-26T10:03:13Z</t>
         </is>
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -13819,7 +13819,7 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q105" t="inlineStr">
         <is>
@@ -13873,12 +13873,12 @@
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:23Z</t>
+          <t>2026-10-26T10:03:14Z</t>
         </is>
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -13947,7 +13947,7 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q106" t="inlineStr">
         <is>
@@ -14001,12 +14001,12 @@
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:22Z</t>
+          <t>2026-10-26T10:03:13Z</t>
         </is>
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -14075,7 +14075,7 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q107" t="inlineStr">
         <is>
@@ -14129,12 +14129,12 @@
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:22Z</t>
+          <t>2026-10-26T10:03:13Z</t>
         </is>
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -14203,7 +14203,7 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q108" t="inlineStr">
         <is>
@@ -14257,12 +14257,12 @@
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:22Z</t>
+          <t>2026-10-26T10:03:13Z</t>
         </is>
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -14331,7 +14331,7 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q109" t="inlineStr">
         <is>
@@ -14385,12 +14385,12 @@
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:22Z</t>
+          <t>2026-10-26T10:03:13Z</t>
         </is>
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -14459,7 +14459,7 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q110" t="inlineStr">
         <is>
@@ -14513,12 +14513,12 @@
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:22Z</t>
+          <t>2026-10-26T10:03:13Z</t>
         </is>
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>

--- a/exports/California_Surplus_Feed.xlsx
+++ b/exports/California_Surplus_Feed.xlsx
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -689,12 +689,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:14Z</t>
+          <t>2026-10-27T09:47:14Z</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -763,7 +763,7 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -817,12 +817,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:14Z</t>
+          <t>2026-10-27T09:47:14Z</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -945,12 +945,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:14Z</t>
+          <t>2026-10-27T09:47:14Z</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:13Z</t>
+          <t>2026-10-27T09:47:12Z</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -1147,7 +1147,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1201,12 +1201,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:13Z</t>
+          <t>2026-10-27T09:47:12Z</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -1275,7 +1275,7 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:14Z</t>
+          <t>2026-10-27T09:47:14Z</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -1403,7 +1403,7 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>-111</v>
+        <v>-112</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -1457,12 +1457,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:14Z</t>
+          <t>2026-10-27T09:47:14Z</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:14Z</t>
+          <t>2026-10-27T09:47:14Z</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>-111</v>
+        <v>-112</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -1713,12 +1713,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:14Z</t>
+          <t>2026-10-27T09:47:14Z</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -1787,7 +1787,7 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -1841,12 +1841,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:14Z</t>
+          <t>2026-10-27T09:47:14Z</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -1915,7 +1915,7 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -1969,12 +1969,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:13Z</t>
+          <t>2026-10-27T09:47:12Z</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -2043,7 +2043,7 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:13Z</t>
+          <t>2026-10-27T09:47:12Z</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>-111</v>
+        <v>-112</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -2225,12 +2225,12 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:14Z</t>
+          <t>2026-10-27T09:47:14Z</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -2299,7 +2299,7 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -2353,12 +2353,12 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:13Z</t>
+          <t>2026-10-27T09:47:12Z</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -2427,7 +2427,7 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>-111</v>
+        <v>-112</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
@@ -2481,12 +2481,12 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:14Z</t>
+          <t>2026-10-27T09:47:14Z</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -2609,12 +2609,12 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:13Z</t>
+          <t>2026-10-27T09:47:12Z</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -2737,12 +2737,12 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:14Z</t>
+          <t>2026-10-27T09:47:14Z</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2811,7 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -2865,12 +2865,12 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:13Z</t>
+          <t>2026-10-27T09:47:12Z</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -2939,7 +2939,7 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -2993,12 +2993,12 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:13Z</t>
+          <t>2026-10-27T09:47:12Z</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -3067,7 +3067,7 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -3121,12 +3121,12 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:13Z</t>
+          <t>2026-10-27T09:47:12Z</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -3195,7 +3195,7 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -3249,12 +3249,12 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:13Z</t>
+          <t>2026-10-27T09:47:12Z</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -3323,7 +3323,7 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -3377,12 +3377,12 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:13Z</t>
+          <t>2026-10-27T09:47:12Z</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>-111</v>
+        <v>-112</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -3505,12 +3505,12 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:14Z</t>
+          <t>2026-10-27T09:47:14Z</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -3579,7 +3579,7 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -3633,12 +3633,12 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:13Z</t>
+          <t>2026-10-27T09:47:12Z</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -3707,7 +3707,7 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -3761,12 +3761,12 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:14Z</t>
+          <t>2026-10-27T09:47:14Z</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -3835,7 +3835,7 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -3889,12 +3889,12 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:14Z</t>
+          <t>2026-10-27T09:47:14Z</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -3963,7 +3963,7 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
@@ -4017,12 +4017,12 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:14Z</t>
+          <t>2026-10-27T09:47:14Z</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -4091,7 +4091,7 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
@@ -4145,12 +4145,12 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:13Z</t>
+          <t>2026-10-27T09:47:12Z</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -4219,7 +4219,7 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
@@ -4273,12 +4273,12 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:14Z</t>
+          <t>2026-10-27T09:47:14Z</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
@@ -4401,12 +4401,12 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:13Z</t>
+          <t>2026-10-27T09:47:12Z</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -4475,7 +4475,7 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
@@ -4529,12 +4529,12 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:13Z</t>
+          <t>2026-10-27T09:47:12Z</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -4603,7 +4603,7 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
@@ -4657,12 +4657,12 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:13Z</t>
+          <t>2026-10-27T09:47:12Z</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
@@ -4785,12 +4785,12 @@
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:13Z</t>
+          <t>2026-10-27T09:47:12Z</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -4859,7 +4859,7 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
@@ -4913,12 +4913,12 @@
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:13Z</t>
+          <t>2026-10-27T09:47:12Z</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -4987,7 +4987,7 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>-111</v>
+        <v>-112</v>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
@@ -5041,12 +5041,12 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:14Z</t>
+          <t>2026-10-27T09:47:14Z</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -5115,7 +5115,7 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:13Z</t>
+          <t>2026-10-27T09:47:12Z</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -5243,7 +5243,7 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
@@ -5297,12 +5297,12 @@
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:13Z</t>
+          <t>2026-10-27T09:47:12Z</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -5371,7 +5371,7 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:14Z</t>
+          <t>2026-10-27T09:47:14Z</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -5499,7 +5499,7 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
@@ -5553,12 +5553,12 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:13Z</t>
+          <t>2026-10-27T09:47:12Z</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -5627,7 +5627,7 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
@@ -5681,12 +5681,12 @@
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:13Z</t>
+          <t>2026-10-27T09:47:12Z</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -5755,7 +5755,7 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
@@ -5809,12 +5809,12 @@
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:13Z</t>
+          <t>2026-10-27T09:47:12Z</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -5883,7 +5883,7 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
@@ -5937,12 +5937,12 @@
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:13Z</t>
+          <t>2026-10-27T09:47:12Z</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -6011,7 +6011,7 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
@@ -6065,12 +6065,12 @@
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:13Z</t>
+          <t>2026-10-27T09:47:12Z</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -6139,7 +6139,7 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
@@ -6193,12 +6193,12 @@
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:13Z</t>
+          <t>2026-10-27T09:47:12Z</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -6267,7 +6267,7 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
@@ -6321,12 +6321,12 @@
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:13Z</t>
+          <t>2026-10-27T09:47:12Z</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -6395,7 +6395,7 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
@@ -6449,12 +6449,12 @@
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:13Z</t>
+          <t>2026-10-27T09:47:12Z</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -6523,7 +6523,7 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
@@ -6577,12 +6577,12 @@
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:14Z</t>
+          <t>2026-10-27T09:47:14Z</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -6651,7 +6651,7 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
@@ -6705,12 +6705,12 @@
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:13Z</t>
+          <t>2026-10-27T09:47:12Z</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -6779,7 +6779,7 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
@@ -6833,12 +6833,12 @@
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:13Z</t>
+          <t>2026-10-27T09:47:12Z</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
@@ -6961,12 +6961,12 @@
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:13Z</t>
+          <t>2026-10-27T09:47:12Z</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
@@ -7089,12 +7089,12 @@
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:13Z</t>
+          <t>2026-10-27T09:47:12Z</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -7163,7 +7163,7 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
@@ -7217,12 +7217,12 @@
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:13Z</t>
+          <t>2026-10-27T09:47:12Z</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -7291,7 +7291,7 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
@@ -7345,12 +7345,12 @@
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:14Z</t>
+          <t>2026-10-27T09:47:14Z</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -7419,7 +7419,7 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
@@ -7473,12 +7473,12 @@
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:13Z</t>
+          <t>2026-10-27T09:47:12Z</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -7547,7 +7547,7 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
@@ -7601,12 +7601,12 @@
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:14Z</t>
+          <t>2026-10-27T09:47:14Z</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -7675,7 +7675,7 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
@@ -7729,12 +7729,12 @@
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:13Z</t>
+          <t>2026-10-27T09:47:12Z</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
@@ -7857,12 +7857,12 @@
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:14Z</t>
+          <t>2026-10-27T09:47:14Z</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -7931,7 +7931,7 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
@@ -7985,12 +7985,12 @@
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:13Z</t>
+          <t>2026-10-27T09:47:12Z</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -8059,7 +8059,7 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
@@ -8113,12 +8113,12 @@
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:13Z</t>
+          <t>2026-10-27T09:47:12Z</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -8187,7 +8187,7 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
@@ -8241,12 +8241,12 @@
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:13Z</t>
+          <t>2026-10-27T09:47:12Z</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -8315,7 +8315,7 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
@@ -8369,12 +8369,12 @@
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:14Z</t>
+          <t>2026-10-27T09:47:14Z</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -8443,7 +8443,7 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
@@ -8497,12 +8497,12 @@
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:13Z</t>
+          <t>2026-10-27T09:47:12Z</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -8571,7 +8571,7 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
@@ -8625,12 +8625,12 @@
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:13Z</t>
+          <t>2026-10-27T09:47:12Z</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:14Z</t>
+          <t>2026-10-27T09:47:14Z</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -8827,7 +8827,7 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>-111</v>
+        <v>-112</v>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
@@ -8881,12 +8881,12 @@
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:14Z</t>
+          <t>2026-10-27T09:47:14Z</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -8955,7 +8955,7 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
@@ -9009,12 +9009,12 @@
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:13Z</t>
+          <t>2026-10-27T09:47:12Z</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -9083,7 +9083,7 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
@@ -9137,12 +9137,12 @@
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:13Z</t>
+          <t>2026-10-27T09:47:12Z</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -9211,7 +9211,7 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
@@ -9265,12 +9265,12 @@
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:13Z</t>
+          <t>2026-10-27T09:47:12Z</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -9339,7 +9339,7 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
@@ -9393,12 +9393,12 @@
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:13Z</t>
+          <t>2026-10-27T09:47:12Z</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -9467,7 +9467,7 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
@@ -9521,12 +9521,12 @@
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:13Z</t>
+          <t>2026-10-27T09:47:12Z</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -9595,7 +9595,7 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
@@ -9649,12 +9649,12 @@
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:13Z</t>
+          <t>2026-10-27T09:47:12Z</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -9723,7 +9723,7 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
@@ -9777,12 +9777,12 @@
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:13Z</t>
+          <t>2026-10-27T09:47:12Z</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -9851,7 +9851,7 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
@@ -9905,12 +9905,12 @@
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:14Z</t>
+          <t>2026-10-27T09:47:14Z</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -9979,7 +9979,7 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
@@ -10033,12 +10033,12 @@
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:14Z</t>
+          <t>2026-10-27T09:47:14Z</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -10107,7 +10107,7 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
@@ -10161,12 +10161,12 @@
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:14Z</t>
+          <t>2026-10-27T09:47:14Z</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -10235,7 +10235,7 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
@@ -10289,12 +10289,12 @@
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:13Z</t>
+          <t>2026-10-27T09:47:12Z</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -10363,7 +10363,7 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
@@ -10417,12 +10417,12 @@
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:14Z</t>
+          <t>2026-10-27T09:47:14Z</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -10491,7 +10491,7 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
@@ -10545,12 +10545,12 @@
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:13Z</t>
+          <t>2026-10-27T09:47:12Z</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -10619,7 +10619,7 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
@@ -10673,12 +10673,12 @@
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:14Z</t>
+          <t>2026-10-27T09:47:14Z</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -10747,7 +10747,7 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
@@ -10801,12 +10801,12 @@
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:14Z</t>
+          <t>2026-10-27T09:47:14Z</t>
         </is>
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -10875,7 +10875,7 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
@@ -10929,12 +10929,12 @@
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:13Z</t>
+          <t>2026-10-27T09:47:12Z</t>
         </is>
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -11003,7 +11003,7 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q83" t="inlineStr">
         <is>
@@ -11057,12 +11057,12 @@
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:13Z</t>
+          <t>2026-10-27T09:47:12Z</t>
         </is>
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -11131,7 +11131,7 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
@@ -11185,12 +11185,12 @@
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:13Z</t>
+          <t>2026-10-27T09:47:12Z</t>
         </is>
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -11259,7 +11259,7 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
@@ -11313,12 +11313,12 @@
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:13Z</t>
+          <t>2026-10-27T09:47:12Z</t>
         </is>
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -11387,7 +11387,7 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q86" t="inlineStr">
         <is>
@@ -11441,12 +11441,12 @@
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:13Z</t>
+          <t>2026-10-27T09:47:12Z</t>
         </is>
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -11515,7 +11515,7 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
@@ -11569,12 +11569,12 @@
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:13Z</t>
+          <t>2026-10-27T09:47:12Z</t>
         </is>
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -11643,7 +11643,7 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
@@ -11697,12 +11697,12 @@
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:13Z</t>
+          <t>2026-10-27T09:47:12Z</t>
         </is>
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -11771,7 +11771,7 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
@@ -11825,12 +11825,12 @@
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:13Z</t>
+          <t>2026-10-27T09:47:12Z</t>
         </is>
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -11899,7 +11899,7 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
@@ -11953,12 +11953,12 @@
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:13Z</t>
+          <t>2026-10-27T09:47:12Z</t>
         </is>
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -12027,7 +12027,7 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
@@ -12081,12 +12081,12 @@
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:13Z</t>
+          <t>2026-10-27T09:47:12Z</t>
         </is>
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -12155,7 +12155,7 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q92" t="inlineStr">
         <is>
@@ -12209,12 +12209,12 @@
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:13Z</t>
+          <t>2026-10-27T09:47:12Z</t>
         </is>
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -12283,7 +12283,7 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
@@ -12337,12 +12337,12 @@
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:13Z</t>
+          <t>2026-10-27T09:47:12Z</t>
         </is>
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -12411,7 +12411,7 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q94" t="inlineStr">
         <is>
@@ -12465,12 +12465,12 @@
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:13Z</t>
+          <t>2026-10-27T09:47:12Z</t>
         </is>
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -12539,7 +12539,7 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q95" t="inlineStr">
         <is>
@@ -12593,12 +12593,12 @@
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:13Z</t>
+          <t>2026-10-27T09:47:12Z</t>
         </is>
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -12667,7 +12667,7 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
@@ -12721,12 +12721,12 @@
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:14Z</t>
+          <t>2026-10-27T09:47:14Z</t>
         </is>
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -12795,7 +12795,7 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q97" t="inlineStr">
         <is>
@@ -12849,12 +12849,12 @@
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:13Z</t>
+          <t>2026-10-27T09:47:12Z</t>
         </is>
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -12923,7 +12923,7 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q98" t="inlineStr">
         <is>
@@ -12977,12 +12977,12 @@
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:13Z</t>
+          <t>2026-10-27T09:47:12Z</t>
         </is>
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -13051,7 +13051,7 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q99" t="inlineStr">
         <is>
@@ -13105,12 +13105,12 @@
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:13Z</t>
+          <t>2026-10-27T09:47:12Z</t>
         </is>
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -13179,7 +13179,7 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q100" t="inlineStr">
         <is>
@@ -13233,12 +13233,12 @@
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:13Z</t>
+          <t>2026-10-27T09:47:12Z</t>
         </is>
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -13307,7 +13307,7 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q101" t="inlineStr">
         <is>
@@ -13361,12 +13361,12 @@
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:13Z</t>
+          <t>2026-10-27T09:47:12Z</t>
         </is>
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -13435,7 +13435,7 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q102" t="inlineStr">
         <is>
@@ -13489,12 +13489,12 @@
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:13Z</t>
+          <t>2026-10-27T09:47:12Z</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -13563,7 +13563,7 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
@@ -13617,12 +13617,12 @@
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:13Z</t>
+          <t>2026-10-27T09:47:12Z</t>
         </is>
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -13691,7 +13691,7 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="Q104" t="inlineStr">
         <is>
@@ -13745,12 +13745,12 @@
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:13Z</t>
+          <t>2026-10-27T09:47:12Z</t>
         </is>
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -13819,7 +13819,7 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q105" t="inlineStr">
         <is>
@@ -13873,12 +13873,12 @@
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:14Z</t>
+          <t>2026-10-27T09:47:14Z</t>
         </is>
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -13947,7 +13947,7 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q106" t="inlineStr">
         <is>
@@ -14001,12 +14001,12 @@
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:13Z</t>
+          <t>2026-10-27T09:47:12Z</t>
         </is>
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -14075,7 +14075,7 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q107" t="inlineStr">
         <is>
@@ -14129,12 +14129,12 @@
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:13Z</t>
+          <t>2026-10-27T09:47:12Z</t>
         </is>
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -14203,7 +14203,7 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q108" t="inlineStr">
         <is>
@@ -14257,12 +14257,12 @@
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:13Z</t>
+          <t>2026-10-27T09:47:12Z</t>
         </is>
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -14331,7 +14331,7 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q109" t="inlineStr">
         <is>
@@ -14385,12 +14385,12 @@
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:13Z</t>
+          <t>2026-10-27T09:47:12Z</t>
         </is>
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -14459,7 +14459,7 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q110" t="inlineStr">
         <is>
@@ -14513,12 +14513,12 @@
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:13Z</t>
+          <t>2026-10-27T09:47:12Z</t>
         </is>
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>

--- a/exports/California_Surplus_Feed.xlsx
+++ b/exports/California_Surplus_Feed.xlsx
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -689,12 +689,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:14Z</t>
+          <t>2026-10-28T10:32:11Z</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -763,7 +763,7 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -817,12 +817,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:14Z</t>
+          <t>2026-10-28T10:32:11Z</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -945,12 +945,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:14Z</t>
+          <t>2026-10-28T10:32:11Z</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:12Z</t>
+          <t>2026-10-28T10:32:10Z</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -1147,7 +1147,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1201,12 +1201,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:12Z</t>
+          <t>2026-10-28T10:32:10Z</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -1275,7 +1275,7 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:14Z</t>
+          <t>2026-10-28T10:32:11Z</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -1403,7 +1403,7 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>-112</v>
+        <v>-113</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -1457,12 +1457,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:14Z</t>
+          <t>2026-10-28T10:32:11Z</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:14Z</t>
+          <t>2026-10-28T10:32:11Z</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>-112</v>
+        <v>-113</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -1713,12 +1713,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:14Z</t>
+          <t>2026-10-28T10:32:11Z</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -1787,7 +1787,7 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -1841,12 +1841,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:14Z</t>
+          <t>2026-10-28T10:32:11Z</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -1915,7 +1915,7 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -1969,12 +1969,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:12Z</t>
+          <t>2026-10-28T10:32:10Z</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -2043,7 +2043,7 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:12Z</t>
+          <t>2026-10-28T10:32:10Z</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>-112</v>
+        <v>-113</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -2225,12 +2225,12 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:14Z</t>
+          <t>2026-10-28T10:32:11Z</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -2299,7 +2299,7 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -2353,12 +2353,12 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:12Z</t>
+          <t>2026-10-28T10:32:10Z</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -2427,7 +2427,7 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>-112</v>
+        <v>-113</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
@@ -2481,12 +2481,12 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:14Z</t>
+          <t>2026-10-28T10:32:11Z</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -2609,12 +2609,12 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:12Z</t>
+          <t>2026-10-28T10:32:10Z</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -2737,12 +2737,12 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:14Z</t>
+          <t>2026-10-28T10:32:11Z</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2811,7 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -2865,12 +2865,12 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:12Z</t>
+          <t>2026-10-28T10:32:10Z</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -2939,7 +2939,7 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -2993,12 +2993,12 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:12Z</t>
+          <t>2026-10-28T10:32:10Z</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -3067,7 +3067,7 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -3121,12 +3121,12 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:12Z</t>
+          <t>2026-10-28T10:32:10Z</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -3195,7 +3195,7 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -3249,12 +3249,12 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:12Z</t>
+          <t>2026-10-28T10:32:10Z</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -3323,7 +3323,7 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -3377,12 +3377,12 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:12Z</t>
+          <t>2026-10-28T10:32:10Z</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>-112</v>
+        <v>-113</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -3505,12 +3505,12 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:14Z</t>
+          <t>2026-10-28T10:32:11Z</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -3579,7 +3579,7 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -3633,12 +3633,12 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:12Z</t>
+          <t>2026-10-28T10:32:10Z</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -3707,7 +3707,7 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -3761,12 +3761,12 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:14Z</t>
+          <t>2026-10-28T10:32:11Z</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -3835,7 +3835,7 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -3889,12 +3889,12 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:14Z</t>
+          <t>2026-10-28T10:32:11Z</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -3963,7 +3963,7 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
@@ -4017,12 +4017,12 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:14Z</t>
+          <t>2026-10-28T10:32:11Z</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -4091,7 +4091,7 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
@@ -4145,12 +4145,12 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:12Z</t>
+          <t>2026-10-28T10:32:10Z</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -4219,7 +4219,7 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
@@ -4273,12 +4273,12 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:14Z</t>
+          <t>2026-10-28T10:32:11Z</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
@@ -4401,12 +4401,12 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:12Z</t>
+          <t>2026-10-28T10:32:10Z</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -4475,7 +4475,7 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
@@ -4529,12 +4529,12 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:12Z</t>
+          <t>2026-10-28T10:32:10Z</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -4603,7 +4603,7 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
@@ -4657,12 +4657,12 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:12Z</t>
+          <t>2026-10-28T10:32:10Z</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
@@ -4785,12 +4785,12 @@
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:12Z</t>
+          <t>2026-10-28T10:32:10Z</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -4859,7 +4859,7 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
@@ -4913,12 +4913,12 @@
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:12Z</t>
+          <t>2026-10-28T10:32:10Z</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -4987,7 +4987,7 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>-112</v>
+        <v>-113</v>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
@@ -5041,12 +5041,12 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:14Z</t>
+          <t>2026-10-28T10:32:11Z</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -5115,7 +5115,7 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:12Z</t>
+          <t>2026-10-28T10:32:10Z</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -5243,7 +5243,7 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
@@ -5297,12 +5297,12 @@
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:12Z</t>
+          <t>2026-10-28T10:32:10Z</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -5371,7 +5371,7 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:14Z</t>
+          <t>2026-10-28T10:32:11Z</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -5499,7 +5499,7 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
@@ -5553,12 +5553,12 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:12Z</t>
+          <t>2026-10-28T10:32:10Z</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -5627,7 +5627,7 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
@@ -5681,12 +5681,12 @@
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:12Z</t>
+          <t>2026-10-28T10:32:10Z</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -5755,7 +5755,7 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
@@ -5809,12 +5809,12 @@
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:12Z</t>
+          <t>2026-10-28T10:32:10Z</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -5883,7 +5883,7 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
@@ -5937,12 +5937,12 @@
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:12Z</t>
+          <t>2026-10-28T10:32:10Z</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -6011,7 +6011,7 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
@@ -6065,12 +6065,12 @@
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:12Z</t>
+          <t>2026-10-28T10:32:10Z</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -6139,7 +6139,7 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
@@ -6193,12 +6193,12 @@
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:12Z</t>
+          <t>2026-10-28T10:32:10Z</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -6267,7 +6267,7 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
@@ -6321,12 +6321,12 @@
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:12Z</t>
+          <t>2026-10-28T10:32:10Z</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -6395,7 +6395,7 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
@@ -6449,12 +6449,12 @@
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:12Z</t>
+          <t>2026-10-28T10:32:10Z</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -6523,7 +6523,7 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
@@ -6577,12 +6577,12 @@
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:14Z</t>
+          <t>2026-10-28T10:32:11Z</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -6651,7 +6651,7 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
@@ -6705,12 +6705,12 @@
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:12Z</t>
+          <t>2026-10-28T10:32:10Z</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -6779,7 +6779,7 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
@@ -6833,12 +6833,12 @@
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:12Z</t>
+          <t>2026-10-28T10:32:10Z</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
@@ -6961,12 +6961,12 @@
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:12Z</t>
+          <t>2026-10-28T10:32:10Z</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
@@ -7089,12 +7089,12 @@
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:12Z</t>
+          <t>2026-10-28T10:32:10Z</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -7163,7 +7163,7 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
@@ -7217,12 +7217,12 @@
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:12Z</t>
+          <t>2026-10-28T10:32:10Z</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -7291,7 +7291,7 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
@@ -7345,12 +7345,12 @@
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:14Z</t>
+          <t>2026-10-28T10:32:11Z</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -7419,7 +7419,7 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
@@ -7473,12 +7473,12 @@
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:12Z</t>
+          <t>2026-10-28T10:32:10Z</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -7547,7 +7547,7 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
@@ -7601,12 +7601,12 @@
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:14Z</t>
+          <t>2026-10-28T10:32:11Z</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -7675,7 +7675,7 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
@@ -7729,12 +7729,12 @@
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:12Z</t>
+          <t>2026-10-28T10:32:10Z</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
@@ -7857,12 +7857,12 @@
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:14Z</t>
+          <t>2026-10-28T10:32:11Z</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -7931,7 +7931,7 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
@@ -7985,12 +7985,12 @@
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:12Z</t>
+          <t>2026-10-28T10:32:10Z</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -8059,7 +8059,7 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
@@ -8113,12 +8113,12 @@
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:12Z</t>
+          <t>2026-10-28T10:32:10Z</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -8187,7 +8187,7 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
@@ -8241,12 +8241,12 @@
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:12Z</t>
+          <t>2026-10-28T10:32:10Z</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -8315,7 +8315,7 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
@@ -8369,12 +8369,12 @@
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:14Z</t>
+          <t>2026-10-28T10:32:11Z</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -8443,7 +8443,7 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
@@ -8497,12 +8497,12 @@
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:12Z</t>
+          <t>2026-10-28T10:32:10Z</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -8571,7 +8571,7 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
@@ -8625,12 +8625,12 @@
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:12Z</t>
+          <t>2026-10-28T10:32:10Z</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:14Z</t>
+          <t>2026-10-28T10:32:11Z</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -8827,7 +8827,7 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>-112</v>
+        <v>-113</v>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
@@ -8881,12 +8881,12 @@
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:14Z</t>
+          <t>2026-10-28T10:32:11Z</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -8955,7 +8955,7 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
@@ -9009,12 +9009,12 @@
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:12Z</t>
+          <t>2026-10-28T10:32:10Z</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -9083,7 +9083,7 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
@@ -9137,12 +9137,12 @@
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:12Z</t>
+          <t>2026-10-28T10:32:10Z</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -9211,7 +9211,7 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
@@ -9265,12 +9265,12 @@
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:12Z</t>
+          <t>2026-10-28T10:32:10Z</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -9339,7 +9339,7 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
@@ -9393,12 +9393,12 @@
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:12Z</t>
+          <t>2026-10-28T10:32:10Z</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -9467,7 +9467,7 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
@@ -9521,12 +9521,12 @@
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:12Z</t>
+          <t>2026-10-28T10:32:10Z</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -9595,7 +9595,7 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
@@ -9649,12 +9649,12 @@
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:12Z</t>
+          <t>2026-10-28T10:32:10Z</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -9723,7 +9723,7 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
@@ -9777,12 +9777,12 @@
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:12Z</t>
+          <t>2026-10-28T10:32:10Z</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -9851,7 +9851,7 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
@@ -9905,12 +9905,12 @@
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:14Z</t>
+          <t>2026-10-28T10:32:11Z</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -9979,7 +9979,7 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
@@ -10033,12 +10033,12 @@
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:14Z</t>
+          <t>2026-10-28T10:32:11Z</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -10107,7 +10107,7 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
@@ -10161,12 +10161,12 @@
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:14Z</t>
+          <t>2026-10-28T10:32:11Z</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -10235,7 +10235,7 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
@@ -10289,12 +10289,12 @@
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:12Z</t>
+          <t>2026-10-28T10:32:10Z</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -10363,7 +10363,7 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
@@ -10417,12 +10417,12 @@
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:14Z</t>
+          <t>2026-10-28T10:32:11Z</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -10491,7 +10491,7 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
@@ -10545,12 +10545,12 @@
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:12Z</t>
+          <t>2026-10-28T10:32:10Z</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -10619,7 +10619,7 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
@@ -10673,12 +10673,12 @@
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:14Z</t>
+          <t>2026-10-28T10:32:11Z</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -10747,7 +10747,7 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
@@ -10801,12 +10801,12 @@
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:14Z</t>
+          <t>2026-10-28T10:32:11Z</t>
         </is>
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -10875,7 +10875,7 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
@@ -10929,12 +10929,12 @@
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:12Z</t>
+          <t>2026-10-28T10:32:10Z</t>
         </is>
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -11003,7 +11003,7 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q83" t="inlineStr">
         <is>
@@ -11057,12 +11057,12 @@
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:12Z</t>
+          <t>2026-10-28T10:32:10Z</t>
         </is>
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -11131,7 +11131,7 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
@@ -11185,12 +11185,12 @@
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:12Z</t>
+          <t>2026-10-28T10:32:10Z</t>
         </is>
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -11259,7 +11259,7 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
@@ -11313,12 +11313,12 @@
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:12Z</t>
+          <t>2026-10-28T10:32:10Z</t>
         </is>
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -11387,7 +11387,7 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q86" t="inlineStr">
         <is>
@@ -11441,12 +11441,12 @@
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:12Z</t>
+          <t>2026-10-28T10:32:10Z</t>
         </is>
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -11515,7 +11515,7 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
@@ -11569,12 +11569,12 @@
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:12Z</t>
+          <t>2026-10-28T10:32:10Z</t>
         </is>
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -11643,7 +11643,7 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
@@ -11697,12 +11697,12 @@
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:12Z</t>
+          <t>2026-10-28T10:32:10Z</t>
         </is>
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -11771,7 +11771,7 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
@@ -11825,12 +11825,12 @@
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:12Z</t>
+          <t>2026-10-28T10:32:10Z</t>
         </is>
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -11899,7 +11899,7 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
@@ -11953,12 +11953,12 @@
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:12Z</t>
+          <t>2026-10-28T10:32:10Z</t>
         </is>
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -12027,7 +12027,7 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
@@ -12081,12 +12081,12 @@
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:12Z</t>
+          <t>2026-10-28T10:32:10Z</t>
         </is>
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -12155,7 +12155,7 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q92" t="inlineStr">
         <is>
@@ -12209,12 +12209,12 @@
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:12Z</t>
+          <t>2026-10-28T10:32:10Z</t>
         </is>
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -12283,7 +12283,7 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
@@ -12337,12 +12337,12 @@
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:12Z</t>
+          <t>2026-10-28T10:32:10Z</t>
         </is>
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -12411,7 +12411,7 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q94" t="inlineStr">
         <is>
@@ -12465,12 +12465,12 @@
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:12Z</t>
+          <t>2026-10-28T10:32:10Z</t>
         </is>
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -12539,7 +12539,7 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q95" t="inlineStr">
         <is>
@@ -12593,12 +12593,12 @@
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:12Z</t>
+          <t>2026-10-28T10:32:10Z</t>
         </is>
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -12667,7 +12667,7 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
@@ -12721,12 +12721,12 @@
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:14Z</t>
+          <t>2026-10-28T10:32:11Z</t>
         </is>
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -12795,7 +12795,7 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q97" t="inlineStr">
         <is>
@@ -12849,12 +12849,12 @@
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:12Z</t>
+          <t>2026-10-28T10:32:10Z</t>
         </is>
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -12923,7 +12923,7 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q98" t="inlineStr">
         <is>
@@ -12977,12 +12977,12 @@
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:12Z</t>
+          <t>2026-10-28T10:32:10Z</t>
         </is>
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -13051,7 +13051,7 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q99" t="inlineStr">
         <is>
@@ -13105,12 +13105,12 @@
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:12Z</t>
+          <t>2026-10-28T10:32:10Z</t>
         </is>
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -13179,7 +13179,7 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q100" t="inlineStr">
         <is>
@@ -13233,12 +13233,12 @@
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:12Z</t>
+          <t>2026-10-28T10:32:10Z</t>
         </is>
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -13307,7 +13307,7 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q101" t="inlineStr">
         <is>
@@ -13361,12 +13361,12 @@
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:12Z</t>
+          <t>2026-10-28T10:32:10Z</t>
         </is>
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -13435,7 +13435,7 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q102" t="inlineStr">
         <is>
@@ -13489,12 +13489,12 @@
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:12Z</t>
+          <t>2026-10-28T10:32:10Z</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -13563,7 +13563,7 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
@@ -13617,12 +13617,12 @@
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:12Z</t>
+          <t>2026-10-28T10:32:10Z</t>
         </is>
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -13691,7 +13691,7 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="Q104" t="inlineStr">
         <is>
@@ -13745,12 +13745,12 @@
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:12Z</t>
+          <t>2026-10-28T10:32:10Z</t>
         </is>
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -13819,7 +13819,7 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q105" t="inlineStr">
         <is>
@@ -13873,12 +13873,12 @@
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:14Z</t>
+          <t>2026-10-28T10:32:11Z</t>
         </is>
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -13947,7 +13947,7 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q106" t="inlineStr">
         <is>
@@ -14001,12 +14001,12 @@
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:12Z</t>
+          <t>2026-10-28T10:32:10Z</t>
         </is>
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -14075,7 +14075,7 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q107" t="inlineStr">
         <is>
@@ -14129,12 +14129,12 @@
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:12Z</t>
+          <t>2026-10-28T10:32:10Z</t>
         </is>
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -14203,7 +14203,7 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q108" t="inlineStr">
         <is>
@@ -14257,12 +14257,12 @@
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:12Z</t>
+          <t>2026-10-28T10:32:10Z</t>
         </is>
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -14331,7 +14331,7 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q109" t="inlineStr">
         <is>
@@ -14385,12 +14385,12 @@
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:12Z</t>
+          <t>2026-10-28T10:32:10Z</t>
         </is>
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -14459,7 +14459,7 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q110" t="inlineStr">
         <is>
@@ -14513,12 +14513,12 @@
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:12Z</t>
+          <t>2026-10-28T10:32:10Z</t>
         </is>
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>

--- a/exports/California_Surplus_Feed.xlsx
+++ b/exports/California_Surplus_Feed.xlsx
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -689,12 +689,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:11Z</t>
+          <t>2026-10-29T10:51:41Z</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -763,7 +763,7 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -817,12 +817,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:11Z</t>
+          <t>2026-10-29T10:51:41Z</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -945,12 +945,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:11Z</t>
+          <t>2026-10-29T10:51:41Z</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:10Z</t>
+          <t>2026-10-29T10:51:39Z</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -1147,7 +1147,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1201,12 +1201,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:10Z</t>
+          <t>2026-10-29T10:51:39Z</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -1275,7 +1275,7 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:11Z</t>
+          <t>2026-10-29T10:51:41Z</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -1403,7 +1403,7 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>-113</v>
+        <v>-114</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -1457,12 +1457,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:11Z</t>
+          <t>2026-10-29T10:51:40Z</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:11Z</t>
+          <t>2026-10-29T10:51:41Z</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>-113</v>
+        <v>-114</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -1713,12 +1713,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:11Z</t>
+          <t>2026-10-29T10:51:40Z</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -1787,7 +1787,7 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -1841,12 +1841,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:11Z</t>
+          <t>2026-10-29T10:51:41Z</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -1915,7 +1915,7 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -1969,12 +1969,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:10Z</t>
+          <t>2026-10-29T10:51:39Z</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -2043,7 +2043,7 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:10Z</t>
+          <t>2026-10-29T10:51:39Z</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>-113</v>
+        <v>-114</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -2225,12 +2225,12 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:11Z</t>
+          <t>2026-10-29T10:51:40Z</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -2299,7 +2299,7 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -2353,12 +2353,12 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:10Z</t>
+          <t>2026-10-29T10:51:39Z</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -2427,7 +2427,7 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>-113</v>
+        <v>-114</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
@@ -2481,12 +2481,12 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:11Z</t>
+          <t>2026-10-29T10:51:40Z</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -2609,12 +2609,12 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:10Z</t>
+          <t>2026-10-29T10:51:39Z</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -2737,12 +2737,12 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:11Z</t>
+          <t>2026-10-29T10:51:41Z</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2811,7 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -2865,12 +2865,12 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:10Z</t>
+          <t>2026-10-29T10:51:39Z</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -2939,7 +2939,7 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -2993,12 +2993,12 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:10Z</t>
+          <t>2026-10-29T10:51:39Z</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -3067,7 +3067,7 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -3121,12 +3121,12 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:10Z</t>
+          <t>2026-10-29T10:51:39Z</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -3195,7 +3195,7 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -3249,12 +3249,12 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:10Z</t>
+          <t>2026-10-29T10:51:39Z</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -3323,7 +3323,7 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -3377,12 +3377,12 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:10Z</t>
+          <t>2026-10-29T10:51:39Z</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>-113</v>
+        <v>-114</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -3505,12 +3505,12 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:11Z</t>
+          <t>2026-10-29T10:51:40Z</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -3579,7 +3579,7 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -3633,12 +3633,12 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:10Z</t>
+          <t>2026-10-29T10:51:39Z</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -3707,7 +3707,7 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -3761,12 +3761,12 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:11Z</t>
+          <t>2026-10-29T10:51:41Z</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -3835,7 +3835,7 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -3889,12 +3889,12 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:11Z</t>
+          <t>2026-10-29T10:51:41Z</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -3963,7 +3963,7 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
@@ -4017,12 +4017,12 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:11Z</t>
+          <t>2026-10-29T10:51:41Z</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -4091,7 +4091,7 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
@@ -4145,12 +4145,12 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:10Z</t>
+          <t>2026-10-29T10:51:39Z</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -4219,7 +4219,7 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
@@ -4273,12 +4273,12 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:11Z</t>
+          <t>2026-10-29T10:51:41Z</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
@@ -4401,12 +4401,12 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:10Z</t>
+          <t>2026-10-29T10:51:39Z</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -4475,7 +4475,7 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
@@ -4529,12 +4529,12 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:10Z</t>
+          <t>2026-10-29T10:51:39Z</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -4603,7 +4603,7 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
@@ -4657,12 +4657,12 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:10Z</t>
+          <t>2026-10-29T10:51:39Z</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
@@ -4785,12 +4785,12 @@
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:10Z</t>
+          <t>2026-10-29T10:51:39Z</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -4859,7 +4859,7 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
@@ -4913,12 +4913,12 @@
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:10Z</t>
+          <t>2026-10-29T10:51:39Z</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -4987,7 +4987,7 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>-113</v>
+        <v>-114</v>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
@@ -5041,12 +5041,12 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:11Z</t>
+          <t>2026-10-29T10:51:40Z</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -5115,7 +5115,7 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:10Z</t>
+          <t>2026-10-29T10:51:39Z</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -5243,7 +5243,7 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
@@ -5297,12 +5297,12 @@
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:10Z</t>
+          <t>2026-10-29T10:51:39Z</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -5371,7 +5371,7 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:11Z</t>
+          <t>2026-10-29T10:51:41Z</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -5499,7 +5499,7 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
@@ -5553,12 +5553,12 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:10Z</t>
+          <t>2026-10-29T10:51:39Z</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -5627,7 +5627,7 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
@@ -5681,12 +5681,12 @@
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:10Z</t>
+          <t>2026-10-29T10:51:39Z</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -5755,7 +5755,7 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
@@ -5809,12 +5809,12 @@
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:10Z</t>
+          <t>2026-10-29T10:51:39Z</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -5883,7 +5883,7 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
@@ -5937,12 +5937,12 @@
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:10Z</t>
+          <t>2026-10-29T10:51:39Z</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -6011,7 +6011,7 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
@@ -6065,12 +6065,12 @@
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:10Z</t>
+          <t>2026-10-29T10:51:39Z</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -6139,7 +6139,7 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
@@ -6193,12 +6193,12 @@
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:10Z</t>
+          <t>2026-10-29T10:51:39Z</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -6267,7 +6267,7 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
@@ -6321,12 +6321,12 @@
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:10Z</t>
+          <t>2026-10-29T10:51:39Z</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -6395,7 +6395,7 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
@@ -6449,12 +6449,12 @@
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:10Z</t>
+          <t>2026-10-29T10:51:39Z</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -6523,7 +6523,7 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
@@ -6577,12 +6577,12 @@
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:11Z</t>
+          <t>2026-10-29T10:51:41Z</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -6651,7 +6651,7 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
@@ -6705,12 +6705,12 @@
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:10Z</t>
+          <t>2026-10-29T10:51:39Z</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -6779,7 +6779,7 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
@@ -6833,12 +6833,12 @@
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:10Z</t>
+          <t>2026-10-29T10:51:39Z</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
@@ -6961,12 +6961,12 @@
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:10Z</t>
+          <t>2026-10-29T10:51:39Z</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
@@ -7089,12 +7089,12 @@
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:10Z</t>
+          <t>2026-10-29T10:51:39Z</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -7163,7 +7163,7 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
@@ -7217,12 +7217,12 @@
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:10Z</t>
+          <t>2026-10-29T10:51:39Z</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -7291,7 +7291,7 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
@@ -7345,12 +7345,12 @@
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:11Z</t>
+          <t>2026-10-29T10:51:41Z</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -7419,7 +7419,7 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
@@ -7473,12 +7473,12 @@
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:10Z</t>
+          <t>2026-10-29T10:51:39Z</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -7547,7 +7547,7 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
@@ -7601,12 +7601,12 @@
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:11Z</t>
+          <t>2026-10-29T10:51:41Z</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -7675,7 +7675,7 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
@@ -7729,12 +7729,12 @@
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:10Z</t>
+          <t>2026-10-29T10:51:39Z</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
@@ -7857,12 +7857,12 @@
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:11Z</t>
+          <t>2026-10-29T10:51:41Z</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -7931,7 +7931,7 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
@@ -7985,12 +7985,12 @@
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:10Z</t>
+          <t>2026-10-29T10:51:39Z</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -8059,7 +8059,7 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
@@ -8113,12 +8113,12 @@
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:10Z</t>
+          <t>2026-10-29T10:51:39Z</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -8187,7 +8187,7 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
@@ -8241,12 +8241,12 @@
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:10Z</t>
+          <t>2026-10-29T10:51:39Z</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -8315,7 +8315,7 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
@@ -8369,12 +8369,12 @@
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:11Z</t>
+          <t>2026-10-29T10:51:41Z</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -8443,7 +8443,7 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
@@ -8497,12 +8497,12 @@
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:10Z</t>
+          <t>2026-10-29T10:51:39Z</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -8571,7 +8571,7 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
@@ -8625,12 +8625,12 @@
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:10Z</t>
+          <t>2026-10-29T10:51:39Z</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:11Z</t>
+          <t>2026-10-29T10:51:41Z</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -8827,7 +8827,7 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>-113</v>
+        <v>-114</v>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
@@ -8881,12 +8881,12 @@
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:11Z</t>
+          <t>2026-10-29T10:51:40Z</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -8955,7 +8955,7 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
@@ -9009,12 +9009,12 @@
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:10Z</t>
+          <t>2026-10-29T10:51:39Z</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -9083,7 +9083,7 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
@@ -9137,12 +9137,12 @@
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:10Z</t>
+          <t>2026-10-29T10:51:39Z</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -9211,7 +9211,7 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
@@ -9265,12 +9265,12 @@
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:10Z</t>
+          <t>2026-10-29T10:51:39Z</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -9339,7 +9339,7 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
@@ -9393,12 +9393,12 @@
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:10Z</t>
+          <t>2026-10-29T10:51:39Z</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -9467,7 +9467,7 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
@@ -9521,12 +9521,12 @@
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:10Z</t>
+          <t>2026-10-29T10:51:39Z</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -9595,7 +9595,7 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
@@ -9649,12 +9649,12 @@
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:10Z</t>
+          <t>2026-10-29T10:51:39Z</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -9723,7 +9723,7 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
@@ -9777,12 +9777,12 @@
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:10Z</t>
+          <t>2026-10-29T10:51:39Z</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -9851,7 +9851,7 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
@@ -9905,12 +9905,12 @@
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:11Z</t>
+          <t>2026-10-29T10:51:41Z</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -9979,7 +9979,7 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
@@ -10033,12 +10033,12 @@
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:11Z</t>
+          <t>2026-10-29T10:51:41Z</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -10107,7 +10107,7 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
@@ -10161,12 +10161,12 @@
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:11Z</t>
+          <t>2026-10-29T10:51:41Z</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -10235,7 +10235,7 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
@@ -10289,12 +10289,12 @@
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:10Z</t>
+          <t>2026-10-29T10:51:39Z</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -10363,7 +10363,7 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
@@ -10417,12 +10417,12 @@
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:11Z</t>
+          <t>2026-10-29T10:51:41Z</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -10491,7 +10491,7 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
@@ -10545,12 +10545,12 @@
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:10Z</t>
+          <t>2026-10-29T10:51:39Z</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -10619,7 +10619,7 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
@@ -10673,12 +10673,12 @@
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:11Z</t>
+          <t>2026-10-29T10:51:41Z</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -10747,7 +10747,7 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
@@ -10801,12 +10801,12 @@
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:11Z</t>
+          <t>2026-10-29T10:51:41Z</t>
         </is>
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -10875,7 +10875,7 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
@@ -10929,12 +10929,12 @@
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:10Z</t>
+          <t>2026-10-29T10:51:39Z</t>
         </is>
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -11003,7 +11003,7 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q83" t="inlineStr">
         <is>
@@ -11057,12 +11057,12 @@
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:10Z</t>
+          <t>2026-10-29T10:51:39Z</t>
         </is>
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -11131,7 +11131,7 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
@@ -11185,12 +11185,12 @@
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:10Z</t>
+          <t>2026-10-29T10:51:39Z</t>
         </is>
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -11259,7 +11259,7 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
@@ -11313,12 +11313,12 @@
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:10Z</t>
+          <t>2026-10-29T10:51:39Z</t>
         </is>
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -11387,7 +11387,7 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q86" t="inlineStr">
         <is>
@@ -11441,12 +11441,12 @@
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:10Z</t>
+          <t>2026-10-29T10:51:39Z</t>
         </is>
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -11515,7 +11515,7 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
@@ -11569,12 +11569,12 @@
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:10Z</t>
+          <t>2026-10-29T10:51:39Z</t>
         </is>
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -11643,7 +11643,7 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
@@ -11697,12 +11697,12 @@
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:10Z</t>
+          <t>2026-10-29T10:51:39Z</t>
         </is>
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -11771,7 +11771,7 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
@@ -11825,12 +11825,12 @@
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:10Z</t>
+          <t>2026-10-29T10:51:39Z</t>
         </is>
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -11899,7 +11899,7 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
@@ -11953,12 +11953,12 @@
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:10Z</t>
+          <t>2026-10-29T10:51:39Z</t>
         </is>
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -12027,7 +12027,7 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
@@ -12081,12 +12081,12 @@
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:10Z</t>
+          <t>2026-10-29T10:51:39Z</t>
         </is>
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -12155,7 +12155,7 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q92" t="inlineStr">
         <is>
@@ -12209,12 +12209,12 @@
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:10Z</t>
+          <t>2026-10-29T10:51:39Z</t>
         </is>
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -12283,7 +12283,7 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
@@ -12337,12 +12337,12 @@
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:10Z</t>
+          <t>2026-10-29T10:51:39Z</t>
         </is>
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -12411,7 +12411,7 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q94" t="inlineStr">
         <is>
@@ -12465,12 +12465,12 @@
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:10Z</t>
+          <t>2026-10-29T10:51:39Z</t>
         </is>
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -12539,7 +12539,7 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q95" t="inlineStr">
         <is>
@@ -12593,12 +12593,12 @@
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:10Z</t>
+          <t>2026-10-29T10:51:39Z</t>
         </is>
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -12667,7 +12667,7 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
@@ -12721,12 +12721,12 @@
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:11Z</t>
+          <t>2026-10-29T10:51:41Z</t>
         </is>
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -12795,7 +12795,7 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q97" t="inlineStr">
         <is>
@@ -12849,12 +12849,12 @@
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:10Z</t>
+          <t>2026-10-29T10:51:39Z</t>
         </is>
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -12923,7 +12923,7 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q98" t="inlineStr">
         <is>
@@ -12977,12 +12977,12 @@
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:10Z</t>
+          <t>2026-10-29T10:51:39Z</t>
         </is>
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -13051,7 +13051,7 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q99" t="inlineStr">
         <is>
@@ -13105,12 +13105,12 @@
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:10Z</t>
+          <t>2026-10-29T10:51:39Z</t>
         </is>
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -13179,7 +13179,7 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q100" t="inlineStr">
         <is>
@@ -13233,12 +13233,12 @@
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:10Z</t>
+          <t>2026-10-29T10:51:39Z</t>
         </is>
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -13307,7 +13307,7 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q101" t="inlineStr">
         <is>
@@ -13361,12 +13361,12 @@
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:10Z</t>
+          <t>2026-10-29T10:51:39Z</t>
         </is>
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -13435,7 +13435,7 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q102" t="inlineStr">
         <is>
@@ -13489,12 +13489,12 @@
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:10Z</t>
+          <t>2026-10-29T10:51:39Z</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -13563,7 +13563,7 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
@@ -13617,12 +13617,12 @@
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:10Z</t>
+          <t>2026-10-29T10:51:39Z</t>
         </is>
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -13691,7 +13691,7 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="Q104" t="inlineStr">
         <is>
@@ -13745,12 +13745,12 @@
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:10Z</t>
+          <t>2026-10-29T10:51:39Z</t>
         </is>
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -13819,7 +13819,7 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q105" t="inlineStr">
         <is>
@@ -13873,12 +13873,12 @@
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:11Z</t>
+          <t>2026-10-29T10:51:41Z</t>
         </is>
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -13947,7 +13947,7 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q106" t="inlineStr">
         <is>
@@ -14001,12 +14001,12 @@
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:10Z</t>
+          <t>2026-10-29T10:51:39Z</t>
         </is>
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -14075,7 +14075,7 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q107" t="inlineStr">
         <is>
@@ -14129,12 +14129,12 @@
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:10Z</t>
+          <t>2026-10-29T10:51:39Z</t>
         </is>
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -14203,7 +14203,7 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q108" t="inlineStr">
         <is>
@@ -14257,12 +14257,12 @@
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:10Z</t>
+          <t>2026-10-29T10:51:39Z</t>
         </is>
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -14331,7 +14331,7 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q109" t="inlineStr">
         <is>
@@ -14385,12 +14385,12 @@
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:10Z</t>
+          <t>2026-10-29T10:51:39Z</t>
         </is>
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -14459,7 +14459,7 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q110" t="inlineStr">
         <is>
@@ -14513,12 +14513,12 @@
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:10Z</t>
+          <t>2026-10-29T10:51:39Z</t>
         </is>
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>

--- a/exports/California_Surplus_Feed.xlsx
+++ b/exports/California_Surplus_Feed.xlsx
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -689,12 +689,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:41Z</t>
+          <t>2026-10-30T10:50:43Z</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -763,7 +763,7 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -817,12 +817,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:41Z</t>
+          <t>2026-10-30T10:50:43Z</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -945,12 +945,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:41Z</t>
+          <t>2026-10-30T10:50:43Z</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:39Z</t>
+          <t>2026-10-30T10:50:42Z</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -1147,7 +1147,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1201,12 +1201,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:39Z</t>
+          <t>2026-10-30T10:50:42Z</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -1275,7 +1275,7 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:41Z</t>
+          <t>2026-10-30T10:50:43Z</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -1403,7 +1403,7 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>-114</v>
+        <v>-115</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -1457,12 +1457,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:40Z</t>
+          <t>2026-10-30T10:50:43Z</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:41Z</t>
+          <t>2026-10-30T10:50:43Z</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>-114</v>
+        <v>-115</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -1713,12 +1713,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:40Z</t>
+          <t>2026-10-30T10:50:43Z</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -1787,7 +1787,7 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -1841,12 +1841,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:41Z</t>
+          <t>2026-10-30T10:50:43Z</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -1915,7 +1915,7 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -1969,12 +1969,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:39Z</t>
+          <t>2026-10-30T10:50:42Z</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -2043,7 +2043,7 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:39Z</t>
+          <t>2026-10-30T10:50:42Z</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>-114</v>
+        <v>-115</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -2225,12 +2225,12 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:40Z</t>
+          <t>2026-10-30T10:50:43Z</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -2299,7 +2299,7 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -2353,12 +2353,12 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:39Z</t>
+          <t>2026-10-30T10:50:42Z</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -2427,7 +2427,7 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>-114</v>
+        <v>-115</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
@@ -2481,12 +2481,12 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:40Z</t>
+          <t>2026-10-30T10:50:43Z</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -2609,12 +2609,12 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:39Z</t>
+          <t>2026-10-30T10:50:42Z</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -2737,12 +2737,12 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:41Z</t>
+          <t>2026-10-30T10:50:43Z</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2811,7 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -2865,12 +2865,12 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:39Z</t>
+          <t>2026-10-30T10:50:42Z</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -2939,7 +2939,7 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -2993,12 +2993,12 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:39Z</t>
+          <t>2026-10-30T10:50:42Z</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -3067,7 +3067,7 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -3121,12 +3121,12 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:39Z</t>
+          <t>2026-10-30T10:50:42Z</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -3195,7 +3195,7 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -3249,12 +3249,12 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:39Z</t>
+          <t>2026-10-30T10:50:42Z</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -3323,7 +3323,7 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -3377,12 +3377,12 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:39Z</t>
+          <t>2026-10-30T10:50:42Z</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>-114</v>
+        <v>-115</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -3505,12 +3505,12 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:40Z</t>
+          <t>2026-10-30T10:50:43Z</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -3579,7 +3579,7 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -3633,12 +3633,12 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:39Z</t>
+          <t>2026-10-30T10:50:42Z</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -3707,7 +3707,7 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -3761,12 +3761,12 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:41Z</t>
+          <t>2026-10-30T10:50:43Z</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -3835,7 +3835,7 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -3889,12 +3889,12 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:41Z</t>
+          <t>2026-10-30T10:50:43Z</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -3963,7 +3963,7 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
@@ -4017,12 +4017,12 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:41Z</t>
+          <t>2026-10-30T10:50:43Z</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -4091,7 +4091,7 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
@@ -4145,12 +4145,12 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:39Z</t>
+          <t>2026-10-30T10:50:42Z</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -4219,7 +4219,7 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
@@ -4273,12 +4273,12 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:41Z</t>
+          <t>2026-10-30T10:50:43Z</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
@@ -4401,12 +4401,12 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:39Z</t>
+          <t>2026-10-30T10:50:42Z</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -4475,7 +4475,7 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
@@ -4529,12 +4529,12 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:39Z</t>
+          <t>2026-10-30T10:50:42Z</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -4603,7 +4603,7 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
@@ -4657,12 +4657,12 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:39Z</t>
+          <t>2026-10-30T10:50:42Z</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
@@ -4785,12 +4785,12 @@
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:39Z</t>
+          <t>2026-10-30T10:50:42Z</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -4859,7 +4859,7 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
@@ -4913,12 +4913,12 @@
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:39Z</t>
+          <t>2026-10-30T10:50:42Z</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -4987,7 +4987,7 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>-114</v>
+        <v>-115</v>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
@@ -5041,12 +5041,12 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:40Z</t>
+          <t>2026-10-30T10:50:43Z</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -5115,7 +5115,7 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:39Z</t>
+          <t>2026-10-30T10:50:42Z</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -5243,7 +5243,7 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
@@ -5297,12 +5297,12 @@
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:39Z</t>
+          <t>2026-10-30T10:50:42Z</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -5371,7 +5371,7 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:41Z</t>
+          <t>2026-10-30T10:50:43Z</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -5499,7 +5499,7 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
@@ -5553,12 +5553,12 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:39Z</t>
+          <t>2026-10-30T10:50:42Z</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -5627,7 +5627,7 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
@@ -5681,12 +5681,12 @@
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:39Z</t>
+          <t>2026-10-30T10:50:42Z</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -5755,7 +5755,7 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
@@ -5809,12 +5809,12 @@
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:39Z</t>
+          <t>2026-10-30T10:50:42Z</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -5883,7 +5883,7 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
@@ -5937,12 +5937,12 @@
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:39Z</t>
+          <t>2026-10-30T10:50:42Z</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -6011,7 +6011,7 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
@@ -6065,12 +6065,12 @@
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:39Z</t>
+          <t>2026-10-30T10:50:42Z</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -6139,7 +6139,7 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
@@ -6193,12 +6193,12 @@
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:39Z</t>
+          <t>2026-10-30T10:50:42Z</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -6267,7 +6267,7 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
@@ -6321,12 +6321,12 @@
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:39Z</t>
+          <t>2026-10-30T10:50:42Z</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -6395,7 +6395,7 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
@@ -6449,12 +6449,12 @@
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:39Z</t>
+          <t>2026-10-30T10:50:42Z</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -6523,7 +6523,7 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
@@ -6577,12 +6577,12 @@
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:41Z</t>
+          <t>2026-10-30T10:50:43Z</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -6651,7 +6651,7 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
@@ -6705,12 +6705,12 @@
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:39Z</t>
+          <t>2026-10-30T10:50:42Z</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -6779,7 +6779,7 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
@@ -6833,12 +6833,12 @@
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:39Z</t>
+          <t>2026-10-30T10:50:42Z</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
@@ -6961,12 +6961,12 @@
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:39Z</t>
+          <t>2026-10-30T10:50:42Z</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
@@ -7089,12 +7089,12 @@
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:39Z</t>
+          <t>2026-10-30T10:50:42Z</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -7163,7 +7163,7 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
@@ -7217,12 +7217,12 @@
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:39Z</t>
+          <t>2026-10-30T10:50:42Z</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -7291,7 +7291,7 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
@@ -7345,12 +7345,12 @@
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:41Z</t>
+          <t>2026-10-30T10:50:43Z</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -7419,7 +7419,7 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
@@ -7473,12 +7473,12 @@
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:39Z</t>
+          <t>2026-10-30T10:50:42Z</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -7547,7 +7547,7 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
@@ -7601,12 +7601,12 @@
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:41Z</t>
+          <t>2026-10-30T10:50:43Z</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -7675,7 +7675,7 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
@@ -7729,12 +7729,12 @@
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:39Z</t>
+          <t>2026-10-30T10:50:42Z</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
@@ -7857,12 +7857,12 @@
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:41Z</t>
+          <t>2026-10-30T10:50:43Z</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -7931,7 +7931,7 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
@@ -7985,12 +7985,12 @@
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:39Z</t>
+          <t>2026-10-30T10:50:42Z</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -8059,7 +8059,7 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
@@ -8113,12 +8113,12 @@
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:39Z</t>
+          <t>2026-10-30T10:50:42Z</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -8187,7 +8187,7 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
@@ -8241,12 +8241,12 @@
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:39Z</t>
+          <t>2026-10-30T10:50:42Z</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -8315,7 +8315,7 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
@@ -8369,12 +8369,12 @@
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:41Z</t>
+          <t>2026-10-30T10:50:43Z</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -8443,7 +8443,7 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
@@ -8497,12 +8497,12 @@
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:39Z</t>
+          <t>2026-10-30T10:50:42Z</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -8571,7 +8571,7 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
@@ -8625,12 +8625,12 @@
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:39Z</t>
+          <t>2026-10-30T10:50:42Z</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:41Z</t>
+          <t>2026-10-30T10:50:43Z</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -8827,7 +8827,7 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>-114</v>
+        <v>-115</v>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
@@ -8881,12 +8881,12 @@
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:40Z</t>
+          <t>2026-10-30T10:50:43Z</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -8955,7 +8955,7 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
@@ -9009,12 +9009,12 @@
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:39Z</t>
+          <t>2026-10-30T10:50:42Z</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -9083,7 +9083,7 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
@@ -9137,12 +9137,12 @@
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:39Z</t>
+          <t>2026-10-30T10:50:42Z</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -9211,7 +9211,7 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
@@ -9265,12 +9265,12 @@
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:39Z</t>
+          <t>2026-10-30T10:50:42Z</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -9339,7 +9339,7 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
@@ -9393,12 +9393,12 @@
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:39Z</t>
+          <t>2026-10-30T10:50:42Z</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -9467,7 +9467,7 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
@@ -9521,12 +9521,12 @@
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:39Z</t>
+          <t>2026-10-30T10:50:42Z</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -9595,7 +9595,7 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
@@ -9649,12 +9649,12 @@
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:39Z</t>
+          <t>2026-10-30T10:50:42Z</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -9723,7 +9723,7 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
@@ -9777,12 +9777,12 @@
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:39Z</t>
+          <t>2026-10-30T10:50:42Z</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -9851,7 +9851,7 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
@@ -9905,12 +9905,12 @@
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:41Z</t>
+          <t>2026-10-30T10:50:43Z</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -9979,7 +9979,7 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
@@ -10033,12 +10033,12 @@
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:41Z</t>
+          <t>2026-10-30T10:50:43Z</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -10107,7 +10107,7 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
@@ -10161,12 +10161,12 @@
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:41Z</t>
+          <t>2026-10-30T10:50:43Z</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -10235,7 +10235,7 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
@@ -10289,12 +10289,12 @@
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:39Z</t>
+          <t>2026-10-30T10:50:42Z</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -10363,7 +10363,7 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
@@ -10417,12 +10417,12 @@
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:41Z</t>
+          <t>2026-10-30T10:50:43Z</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -10491,7 +10491,7 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
@@ -10545,12 +10545,12 @@
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:39Z</t>
+          <t>2026-10-30T10:50:42Z</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -10619,7 +10619,7 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
@@ -10673,12 +10673,12 @@
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:41Z</t>
+          <t>2026-10-30T10:50:43Z</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -10747,7 +10747,7 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
@@ -10801,12 +10801,12 @@
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:41Z</t>
+          <t>2026-10-30T10:50:43Z</t>
         </is>
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -10875,7 +10875,7 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
@@ -10929,12 +10929,12 @@
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:39Z</t>
+          <t>2026-10-30T10:50:42Z</t>
         </is>
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -11003,7 +11003,7 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q83" t="inlineStr">
         <is>
@@ -11057,12 +11057,12 @@
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:39Z</t>
+          <t>2026-10-30T10:50:42Z</t>
         </is>
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -11131,7 +11131,7 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
@@ -11185,12 +11185,12 @@
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:39Z</t>
+          <t>2026-10-30T10:50:42Z</t>
         </is>
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -11259,7 +11259,7 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
@@ -11313,12 +11313,12 @@
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:39Z</t>
+          <t>2026-10-30T10:50:42Z</t>
         </is>
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -11387,7 +11387,7 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q86" t="inlineStr">
         <is>
@@ -11441,12 +11441,12 @@
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:39Z</t>
+          <t>2026-10-30T10:50:42Z</t>
         </is>
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -11515,7 +11515,7 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
@@ -11569,12 +11569,12 @@
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:39Z</t>
+          <t>2026-10-30T10:50:42Z</t>
         </is>
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -11643,7 +11643,7 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
@@ -11697,12 +11697,12 @@
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:39Z</t>
+          <t>2026-10-30T10:50:42Z</t>
         </is>
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -11771,7 +11771,7 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
@@ -11825,12 +11825,12 @@
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:39Z</t>
+          <t>2026-10-30T10:50:42Z</t>
         </is>
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -11899,7 +11899,7 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
@@ -11953,12 +11953,12 @@
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:39Z</t>
+          <t>2026-10-30T10:50:42Z</t>
         </is>
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -12027,7 +12027,7 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
@@ -12081,12 +12081,12 @@
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:39Z</t>
+          <t>2026-10-30T10:50:42Z</t>
         </is>
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -12155,7 +12155,7 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q92" t="inlineStr">
         <is>
@@ -12209,12 +12209,12 @@
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:39Z</t>
+          <t>2026-10-30T10:50:42Z</t>
         </is>
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -12283,7 +12283,7 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
@@ -12337,12 +12337,12 @@
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:39Z</t>
+          <t>2026-10-30T10:50:42Z</t>
         </is>
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -12411,7 +12411,7 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q94" t="inlineStr">
         <is>
@@ -12465,12 +12465,12 @@
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:39Z</t>
+          <t>2026-10-30T10:50:42Z</t>
         </is>
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -12539,7 +12539,7 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q95" t="inlineStr">
         <is>
@@ -12593,12 +12593,12 @@
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:39Z</t>
+          <t>2026-10-30T10:50:42Z</t>
         </is>
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -12667,7 +12667,7 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
@@ -12721,12 +12721,12 @@
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:41Z</t>
+          <t>2026-10-30T10:50:43Z</t>
         </is>
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -12795,7 +12795,7 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q97" t="inlineStr">
         <is>
@@ -12849,12 +12849,12 @@
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:39Z</t>
+          <t>2026-10-30T10:50:42Z</t>
         </is>
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -12923,7 +12923,7 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q98" t="inlineStr">
         <is>
@@ -12977,12 +12977,12 @@
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:39Z</t>
+          <t>2026-10-30T10:50:42Z</t>
         </is>
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -13051,7 +13051,7 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q99" t="inlineStr">
         <is>
@@ -13105,12 +13105,12 @@
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:39Z</t>
+          <t>2026-10-30T10:50:42Z</t>
         </is>
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -13179,7 +13179,7 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q100" t="inlineStr">
         <is>
@@ -13233,12 +13233,12 @@
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:39Z</t>
+          <t>2026-10-30T10:50:42Z</t>
         </is>
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -13307,7 +13307,7 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q101" t="inlineStr">
         <is>
@@ -13361,12 +13361,12 @@
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:39Z</t>
+          <t>2026-10-30T10:50:42Z</t>
         </is>
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -13435,7 +13435,7 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q102" t="inlineStr">
         <is>
@@ -13489,12 +13489,12 @@
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:39Z</t>
+          <t>2026-10-30T10:50:42Z</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -13563,7 +13563,7 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
@@ -13617,12 +13617,12 @@
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:39Z</t>
+          <t>2026-10-30T10:50:42Z</t>
         </is>
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -13691,7 +13691,7 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="Q104" t="inlineStr">
         <is>
@@ -13745,12 +13745,12 @@
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:39Z</t>
+          <t>2026-10-30T10:50:42Z</t>
         </is>
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -13819,7 +13819,7 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q105" t="inlineStr">
         <is>
@@ -13873,12 +13873,12 @@
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:41Z</t>
+          <t>2026-10-30T10:50:43Z</t>
         </is>
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -13947,7 +13947,7 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q106" t="inlineStr">
         <is>
@@ -14001,12 +14001,12 @@
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:39Z</t>
+          <t>2026-10-30T10:50:42Z</t>
         </is>
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -14075,7 +14075,7 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q107" t="inlineStr">
         <is>
@@ -14129,12 +14129,12 @@
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:39Z</t>
+          <t>2026-10-30T10:50:42Z</t>
         </is>
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -14203,7 +14203,7 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q108" t="inlineStr">
         <is>
@@ -14257,12 +14257,12 @@
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:39Z</t>
+          <t>2026-10-30T10:50:42Z</t>
         </is>
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -14331,7 +14331,7 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q109" t="inlineStr">
         <is>
@@ -14385,12 +14385,12 @@
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:39Z</t>
+          <t>2026-10-30T10:50:42Z</t>
         </is>
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -14459,7 +14459,7 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q110" t="inlineStr">
         <is>
@@ -14513,12 +14513,12 @@
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:39Z</t>
+          <t>2026-10-30T10:50:42Z</t>
         </is>
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>

--- a/exports/California_Surplus_Feed.xlsx
+++ b/exports/California_Surplus_Feed.xlsx
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -689,12 +689,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:43Z</t>
+          <t>2026-10-31T10:21:12Z</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -763,7 +763,7 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -817,12 +817,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:43Z</t>
+          <t>2026-10-31T10:21:12Z</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -945,12 +945,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:43Z</t>
+          <t>2026-10-31T10:21:12Z</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:42Z</t>
+          <t>2026-10-31T10:21:11Z</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -1147,7 +1147,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1201,12 +1201,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:42Z</t>
+          <t>2026-10-31T10:21:11Z</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -1275,7 +1275,7 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:43Z</t>
+          <t>2026-10-31T10:21:12Z</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -1403,7 +1403,7 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>-115</v>
+        <v>-116</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -1457,12 +1457,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:43Z</t>
+          <t>2026-10-31T10:21:12Z</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:43Z</t>
+          <t>2026-10-31T10:21:12Z</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>-115</v>
+        <v>-116</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -1713,12 +1713,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:43Z</t>
+          <t>2026-10-31T10:21:12Z</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -1787,7 +1787,7 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -1841,12 +1841,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:43Z</t>
+          <t>2026-10-31T10:21:12Z</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -1915,7 +1915,7 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -1969,12 +1969,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:42Z</t>
+          <t>2026-10-31T10:21:11Z</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -2043,7 +2043,7 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:42Z</t>
+          <t>2026-10-31T10:21:11Z</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>-115</v>
+        <v>-116</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -2225,12 +2225,12 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:43Z</t>
+          <t>2026-10-31T10:21:12Z</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -2299,7 +2299,7 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -2353,12 +2353,12 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:42Z</t>
+          <t>2026-10-31T10:21:11Z</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -2427,7 +2427,7 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>-115</v>
+        <v>-116</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
@@ -2481,12 +2481,12 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:43Z</t>
+          <t>2026-10-31T10:21:12Z</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -2609,12 +2609,12 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:42Z</t>
+          <t>2026-10-31T10:21:11Z</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -2737,12 +2737,12 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:43Z</t>
+          <t>2026-10-31T10:21:12Z</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2811,7 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -2865,12 +2865,12 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:42Z</t>
+          <t>2026-10-31T10:21:11Z</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -2939,7 +2939,7 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -2993,12 +2993,12 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:42Z</t>
+          <t>2026-10-31T10:21:11Z</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -3067,7 +3067,7 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -3121,12 +3121,12 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:42Z</t>
+          <t>2026-10-31T10:21:11Z</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -3195,7 +3195,7 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -3249,12 +3249,12 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:42Z</t>
+          <t>2026-10-31T10:21:11Z</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -3323,7 +3323,7 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -3377,12 +3377,12 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:42Z</t>
+          <t>2026-10-31T10:21:11Z</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>-115</v>
+        <v>-116</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -3505,12 +3505,12 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:43Z</t>
+          <t>2026-10-31T10:21:12Z</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -3579,7 +3579,7 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -3633,12 +3633,12 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:42Z</t>
+          <t>2026-10-31T10:21:11Z</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -3707,7 +3707,7 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -3761,12 +3761,12 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:43Z</t>
+          <t>2026-10-31T10:21:12Z</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -3835,7 +3835,7 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -3889,12 +3889,12 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:43Z</t>
+          <t>2026-10-31T10:21:12Z</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -3963,7 +3963,7 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
@@ -4017,12 +4017,12 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:43Z</t>
+          <t>2026-10-31T10:21:12Z</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -4091,7 +4091,7 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
@@ -4145,12 +4145,12 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:42Z</t>
+          <t>2026-10-31T10:21:11Z</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -4219,7 +4219,7 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
@@ -4273,12 +4273,12 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:43Z</t>
+          <t>2026-10-31T10:21:12Z</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
@@ -4401,12 +4401,12 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:42Z</t>
+          <t>2026-10-31T10:21:11Z</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -4475,7 +4475,7 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
@@ -4529,12 +4529,12 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:42Z</t>
+          <t>2026-10-31T10:21:11Z</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -4603,7 +4603,7 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
@@ -4657,12 +4657,12 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:42Z</t>
+          <t>2026-10-31T10:21:11Z</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
@@ -4785,12 +4785,12 @@
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:42Z</t>
+          <t>2026-10-31T10:21:11Z</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -4859,7 +4859,7 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
@@ -4913,12 +4913,12 @@
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:42Z</t>
+          <t>2026-10-31T10:21:11Z</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -4987,7 +4987,7 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>-115</v>
+        <v>-116</v>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
@@ -5041,12 +5041,12 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:43Z</t>
+          <t>2026-10-31T10:21:12Z</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -5115,7 +5115,7 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:42Z</t>
+          <t>2026-10-31T10:21:11Z</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -5243,7 +5243,7 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
@@ -5297,12 +5297,12 @@
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:42Z</t>
+          <t>2026-10-31T10:21:11Z</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -5371,7 +5371,7 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:43Z</t>
+          <t>2026-10-31T10:21:12Z</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -5499,7 +5499,7 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
@@ -5553,12 +5553,12 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:42Z</t>
+          <t>2026-10-31T10:21:11Z</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -5627,7 +5627,7 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
@@ -5681,12 +5681,12 @@
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:42Z</t>
+          <t>2026-10-31T10:21:11Z</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -5755,7 +5755,7 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
@@ -5809,12 +5809,12 @@
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:42Z</t>
+          <t>2026-10-31T10:21:11Z</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -5883,7 +5883,7 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
@@ -5937,12 +5937,12 @@
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:42Z</t>
+          <t>2026-10-31T10:21:11Z</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -6011,7 +6011,7 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
@@ -6065,12 +6065,12 @@
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:42Z</t>
+          <t>2026-10-31T10:21:11Z</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -6139,7 +6139,7 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
@@ -6193,12 +6193,12 @@
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:42Z</t>
+          <t>2026-10-31T10:21:11Z</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -6267,7 +6267,7 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
@@ -6321,12 +6321,12 @@
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:42Z</t>
+          <t>2026-10-31T10:21:11Z</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -6395,7 +6395,7 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
@@ -6449,12 +6449,12 @@
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:42Z</t>
+          <t>2026-10-31T10:21:11Z</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -6523,7 +6523,7 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
@@ -6577,12 +6577,12 @@
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:43Z</t>
+          <t>2026-10-31T10:21:12Z</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -6651,7 +6651,7 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
@@ -6705,12 +6705,12 @@
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:42Z</t>
+          <t>2026-10-31T10:21:11Z</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -6779,7 +6779,7 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
@@ -6833,12 +6833,12 @@
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:42Z</t>
+          <t>2026-10-31T10:21:11Z</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
@@ -6961,12 +6961,12 @@
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:42Z</t>
+          <t>2026-10-31T10:21:11Z</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
@@ -7089,12 +7089,12 @@
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:42Z</t>
+          <t>2026-10-31T10:21:11Z</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -7163,7 +7163,7 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
@@ -7217,12 +7217,12 @@
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:42Z</t>
+          <t>2026-10-31T10:21:11Z</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -7291,7 +7291,7 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
@@ -7345,12 +7345,12 @@
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:43Z</t>
+          <t>2026-10-31T10:21:12Z</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -7419,7 +7419,7 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
@@ -7473,12 +7473,12 @@
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:42Z</t>
+          <t>2026-10-31T10:21:11Z</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -7547,7 +7547,7 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
@@ -7601,12 +7601,12 @@
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:43Z</t>
+          <t>2026-10-31T10:21:12Z</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -7675,7 +7675,7 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
@@ -7729,12 +7729,12 @@
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:42Z</t>
+          <t>2026-10-31T10:21:11Z</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
@@ -7857,12 +7857,12 @@
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:43Z</t>
+          <t>2026-10-31T10:21:12Z</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -7931,7 +7931,7 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
@@ -7985,12 +7985,12 @@
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:42Z</t>
+          <t>2026-10-31T10:21:11Z</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -8059,7 +8059,7 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
@@ -8113,12 +8113,12 @@
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:42Z</t>
+          <t>2026-10-31T10:21:11Z</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -8187,7 +8187,7 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
@@ -8241,12 +8241,12 @@
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:42Z</t>
+          <t>2026-10-31T10:21:11Z</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -8315,7 +8315,7 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
@@ -8369,12 +8369,12 @@
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:43Z</t>
+          <t>2026-10-31T10:21:12Z</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -8443,7 +8443,7 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
@@ -8497,12 +8497,12 @@
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:42Z</t>
+          <t>2026-10-31T10:21:11Z</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -8571,7 +8571,7 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
@@ -8625,12 +8625,12 @@
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:42Z</t>
+          <t>2026-10-31T10:21:11Z</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:43Z</t>
+          <t>2026-10-31T10:21:12Z</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -8827,7 +8827,7 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>-115</v>
+        <v>-116</v>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
@@ -8881,12 +8881,12 @@
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:43Z</t>
+          <t>2026-10-31T10:21:12Z</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -8955,7 +8955,7 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
@@ -9009,12 +9009,12 @@
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:42Z</t>
+          <t>2026-10-31T10:21:11Z</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -9083,7 +9083,7 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
@@ -9137,12 +9137,12 @@
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:42Z</t>
+          <t>2026-10-31T10:21:11Z</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -9211,7 +9211,7 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
@@ -9265,12 +9265,12 @@
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:42Z</t>
+          <t>2026-10-31T10:21:11Z</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -9339,7 +9339,7 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
@@ -9393,12 +9393,12 @@
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:42Z</t>
+          <t>2026-10-31T10:21:11Z</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -9467,7 +9467,7 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
@@ -9521,12 +9521,12 @@
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:42Z</t>
+          <t>2026-10-31T10:21:11Z</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -9595,7 +9595,7 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
@@ -9649,12 +9649,12 @@
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:42Z</t>
+          <t>2026-10-31T10:21:11Z</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -9723,7 +9723,7 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
@@ -9777,12 +9777,12 @@
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:42Z</t>
+          <t>2026-10-31T10:21:11Z</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -9851,7 +9851,7 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
@@ -9905,12 +9905,12 @@
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:43Z</t>
+          <t>2026-10-31T10:21:12Z</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -9979,7 +9979,7 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
@@ -10033,12 +10033,12 @@
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:43Z</t>
+          <t>2026-10-31T10:21:12Z</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -10107,7 +10107,7 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
@@ -10161,12 +10161,12 @@
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:43Z</t>
+          <t>2026-10-31T10:21:12Z</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -10235,7 +10235,7 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
@@ -10289,12 +10289,12 @@
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:42Z</t>
+          <t>2026-10-31T10:21:11Z</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -10363,7 +10363,7 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
@@ -10417,12 +10417,12 @@
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:43Z</t>
+          <t>2026-10-31T10:21:12Z</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -10491,7 +10491,7 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>-10</v>
+        <v>-11</v>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
@@ -10545,12 +10545,12 @@
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:42Z</t>
+          <t>2026-10-31T10:21:11Z</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -10619,7 +10619,7 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
@@ -10673,12 +10673,12 @@
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:43Z</t>
+          <t>2026-10-31T10:21:12Z</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -10747,7 +10747,7 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
@@ -10801,12 +10801,12 @@
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:43Z</t>
+          <t>2026-10-31T10:21:12Z</t>
         </is>
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -10875,7 +10875,7 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
@@ -10929,12 +10929,12 @@
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:42Z</t>
+          <t>2026-10-31T10:21:11Z</t>
         </is>
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -11003,7 +11003,7 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q83" t="inlineStr">
         <is>
@@ -11057,12 +11057,12 @@
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:42Z</t>
+          <t>2026-10-31T10:21:11Z</t>
         </is>
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -11131,7 +11131,7 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
@@ -11185,12 +11185,12 @@
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:42Z</t>
+          <t>2026-10-31T10:21:11Z</t>
         </is>
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -11259,7 +11259,7 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
@@ -11313,12 +11313,12 @@
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:42Z</t>
+          <t>2026-10-31T10:21:11Z</t>
         </is>
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -11387,7 +11387,7 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q86" t="inlineStr">
         <is>
@@ -11441,12 +11441,12 @@
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:42Z</t>
+          <t>2026-10-31T10:21:11Z</t>
         </is>
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -11515,7 +11515,7 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
@@ -11569,12 +11569,12 @@
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:42Z</t>
+          <t>2026-10-31T10:21:11Z</t>
         </is>
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -11643,7 +11643,7 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
@@ -11697,12 +11697,12 @@
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:42Z</t>
+          <t>2026-10-31T10:21:11Z</t>
         </is>
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -11771,7 +11771,7 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
@@ -11825,12 +11825,12 @@
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:42Z</t>
+          <t>2026-10-31T10:21:11Z</t>
         </is>
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -11899,7 +11899,7 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
@@ -11953,12 +11953,12 @@
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:42Z</t>
+          <t>2026-10-31T10:21:11Z</t>
         </is>
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -12027,7 +12027,7 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
@@ -12081,12 +12081,12 @@
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:42Z</t>
+          <t>2026-10-31T10:21:11Z</t>
         </is>
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -12155,7 +12155,7 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q92" t="inlineStr">
         <is>
@@ -12209,12 +12209,12 @@
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:42Z</t>
+          <t>2026-10-31T10:21:11Z</t>
         </is>
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -12283,7 +12283,7 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
@@ -12337,12 +12337,12 @@
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:42Z</t>
+          <t>2026-10-31T10:21:11Z</t>
         </is>
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -12411,7 +12411,7 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q94" t="inlineStr">
         <is>
@@ -12465,12 +12465,12 @@
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:42Z</t>
+          <t>2026-10-31T10:21:11Z</t>
         </is>
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -12539,7 +12539,7 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q95" t="inlineStr">
         <is>
@@ -12593,12 +12593,12 @@
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:42Z</t>
+          <t>2026-10-31T10:21:11Z</t>
         </is>
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -12667,7 +12667,7 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
@@ -12721,12 +12721,12 @@
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:43Z</t>
+          <t>2026-10-31T10:21:12Z</t>
         </is>
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -12795,7 +12795,7 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q97" t="inlineStr">
         <is>
@@ -12849,12 +12849,12 @@
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:42Z</t>
+          <t>2026-10-31T10:21:11Z</t>
         </is>
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -12923,7 +12923,7 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q98" t="inlineStr">
         <is>
@@ -12977,12 +12977,12 @@
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:42Z</t>
+          <t>2026-10-31T10:21:11Z</t>
         </is>
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -13051,7 +13051,7 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q99" t="inlineStr">
         <is>
@@ -13105,12 +13105,12 @@
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:42Z</t>
+          <t>2026-10-31T10:21:11Z</t>
         </is>
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -13179,7 +13179,7 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q100" t="inlineStr">
         <is>
@@ -13233,12 +13233,12 @@
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:42Z</t>
+          <t>2026-10-31T10:21:11Z</t>
         </is>
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -13307,7 +13307,7 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q101" t="inlineStr">
         <is>
@@ -13361,12 +13361,12 @@
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:42Z</t>
+          <t>2026-10-31T10:21:11Z</t>
         </is>
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -13435,7 +13435,7 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q102" t="inlineStr">
         <is>
@@ -13489,12 +13489,12 @@
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:42Z</t>
+          <t>2026-10-31T10:21:11Z</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -13563,7 +13563,7 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
@@ -13617,12 +13617,12 @@
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:42Z</t>
+          <t>2026-10-31T10:21:11Z</t>
         </is>
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -13691,7 +13691,7 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>-10</v>
+        <v>-11</v>
       </c>
       <c r="Q104" t="inlineStr">
         <is>
@@ -13745,12 +13745,12 @@
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:42Z</t>
+          <t>2026-10-31T10:21:11Z</t>
         </is>
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -13819,7 +13819,7 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q105" t="inlineStr">
         <is>
@@ -13873,12 +13873,12 @@
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:43Z</t>
+          <t>2026-10-31T10:21:12Z</t>
         </is>
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -13947,7 +13947,7 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q106" t="inlineStr">
         <is>
@@ -14001,12 +14001,12 @@
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:42Z</t>
+          <t>2026-10-31T10:21:11Z</t>
         </is>
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -14075,7 +14075,7 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q107" t="inlineStr">
         <is>
@@ -14129,12 +14129,12 @@
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:42Z</t>
+          <t>2026-10-31T10:21:11Z</t>
         </is>
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -14203,7 +14203,7 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q108" t="inlineStr">
         <is>
@@ -14257,12 +14257,12 @@
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:42Z</t>
+          <t>2026-10-31T10:21:11Z</t>
         </is>
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -14331,7 +14331,7 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q109" t="inlineStr">
         <is>
@@ -14385,12 +14385,12 @@
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:42Z</t>
+          <t>2026-10-31T10:21:11Z</t>
         </is>
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -14459,7 +14459,7 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q110" t="inlineStr">
         <is>
@@ -14513,12 +14513,12 @@
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:42Z</t>
+          <t>2026-10-31T10:21:11Z</t>
         </is>
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
